--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0011.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0011.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Một số chướng ngại vật bị xói mòn bởi Wutherons không thể phá hủy bằng phương pháp thông thường. Chỉ có thể phá vỡ chúng bằng cách dùng Levitator nhặt Tacetite Fulminates gần đó và Dodgem vào để kích nổ.</t>
+          <t>Một số chướng ngại vật bị xói mòn bởi Wutherons không thể phá hủy bằng phương pháp thông thường. Chỉ có thể phá vỡ chúng bằng cách dùng Levitator nhặt Tacetite Fulminates gần đó và ném vào để kích nổ.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Outro Skill &amp; Intro Skill</t>
+          <t>Kỹ Năng Hồi Kết &amp; Kỹ Năng Khai Chiến</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Resonance Nexus</t>
+          <t>Mạng Lưới Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Mục Tiêu Bay Lượn</t>
+          <t>Mục Tiêu Bay Lơ Lửng</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Kỹ Năng Special</t>
+          <t>Kỹ Năng Đặc Biệt</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Basic Attack: Blade Sheath&lt;/color&gt;
+          <t>&lt;color=yellow&gt;Basic Attack: Kiếm Bao&lt;/color&gt;
 Thực hiện tối đa 4 nhát chém liên tiếp, nhát chém thứ 3 có thể triển khai [Hắc Quy Lĩnh Giới], gây hiệu ứng Chậm AOE và hồi HP cho tất cả thành viên trong đội.</t>
         </is>
       </c>
@@ -1227,8 +1227,8 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Black Tortoise Counterattack&lt;/color&gt;
-Khi Taoqi thực hiện Heavy Attack, nếu hành động bị gián đoạn, cô có thể tiêu hao 1 điểm Thượng Năng để thực hiện [Phản Công Hắc Quy] bằng Basic Attack, kích hoạt [Hắc Quy U Minh Giới].</t>
+          <t>&lt;color=yellow&gt;Phản Công Hắc Quy&lt;/color&gt;
+Khi Taoqi thực hiện Tấn Công Mạnh, nếu hành động bị gián đoạn, cô có thể tiêu hao 1 điểm Thượng Năng để thực hiện [Phản Công Hắc Quy] bằng Basic Attack, kích hoạt [Hắc Quy U Minh Giới].</t>
         </is>
       </c>
     </row>
@@ -1302,15 +1302,15 @@
         <is>
           <t>[
 Điều Kiện Mở Khóa]
-Đạt SOL3 Giai đoạn 3.
+Đạt Giai Đoạn SOL3 3.
 [
 Phần Thưởng Gấp Đôi]
 Cậu có thể tiêu thụ số lượng Waveplate gấp đôi để nhận phần thưởng gấp đôi sau khi hoàn thành một số thử thách nhất định.
 Hiệu ứng này giờ đây có thể cộng dồn với Bountiful Crescendo và Chord Cleansing.
 Nếu cả hai sự kiện này đang diễn ra và số lần nhận thưởng gấp đôi tương ứng lớn hơn 2, thì 2 lần sẽ được sử dụng để nhận phần thưởng gấp bốn. Nếu chỉ còn 1 lần nhận thưởng gấp đôi tương ứng, thì lần đó sẽ được dùng để nhận phần thưởng gấp ba.
 [
-Challenges Áp Dụng]
-Challenges Giả Mạo, Challenges Mô Phỏng, Tacet Suppression và Fantasies of the Thousand Gateways.</t>
+Thử Thách Áp Dụng]
+Thử Thách Giả Mạo, Thử Thách Mô Phỏng, Đàn Áp Tacet và Ảo Ảnh Ngàn Cánh Cổng.</t>
         </is>
       </c>
     </row>
@@ -1376,8 +1376,8 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Resonance Skill: Black Tortoise Wall Guard&lt;/color&gt;
-Sau khi Resonance Skill được kích hoạt, gây Havoc DMG diện rộng, nhận 1 điểm Thượng Năng và tạo ra 3 [Giáp Black Tortoise] để giảm sát thương nhận vào. Khi hiệu ứng kết thúc, [Giáp Black Tortoise] chưa vỡ sẽ biến thành [Thượng Năng].</t>
+          <t>&lt;color=yellow&gt;Resonance Skill: Hộ Giáp Huyền Vũ&lt;/color&gt;
+Sau khi Resonance Skill được kích hoạt, gây DMG Havoc diện rộng, nhận 1 điểm Thượng Năng và tạo ra 3 [Giáp Huyền Vũ] để giảm DMG nhận vào. Khi hiệu ứng kết thúc, [Giáp Huyền Vũ] chưa vỡ sẽ biến thành [Thượng Năng].</t>
         </is>
       </c>
     </row>
@@ -1443,8 +1443,8 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Resonance Liberation: Time Stop Slash&lt;/color&gt;
-Sau khi Resonance Liberation được kích hoạt, gây Havoc DMG diện rộng và hiệu ứng Làm Chậm diện rộng, đồng thời tiêu hao toàn bộ [Thượng Năng]. Hồi phục HP cho tất cả thành viên trong đội dựa trên số điểm Thượng Năng đã tiêu hao.</t>
+          <t>&lt;color=yellow&gt;Resonance Liberation: Kiếm Phá Thời Gian&lt;/color&gt;
+Sau khi Resonance Liberation được kích hoạt, gây DMG Havoc diện rộng và hiệu ứng Làm Chậm diện rộng, đồng thời tiêu hao toàn bộ [Thượng Năng]. Hồi phục HP cho tất cả thành viên trong đội dựa trên số điểm Thượng Năng đã tiêu hao.</t>
         </is>
       </c>
     </row>
@@ -1581,10 +1581,10 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Lunite Subscription
-1. Mua Lunite Subscription để nhận ngay Lunite x300 và gia hạn thời gian đăng ký thêm 30 ngày.
-2. Trước khi Lunite Subscription hết hạn, bạn có thể nhận Astrite x90 mỗi ngày khi đăng nhập. Phần thưởng này sẽ được làm mới vào 04:00 AM theo giờ máy chủ hàng ngày.
-3. Trước khi Lunite Subscription hết hạn, phần thưởng hàng ngày chưa nhận trong những ngày bạn không đăng nhập sẽ không được bù lại.
+          <t>Gói Đăng Ký Lunite
+1. Mua Gói Đăng Ký Lunite để nhận ngay Lunite x300 và gia hạn thời gian đăng ký thêm 30 ngày.
+2. Trước khi Gói Đăng Ký Lunite hết hạn, bạn có thể nhận Astrite x90 mỗi ngày khi đăng nhập. Phần thưởng này sẽ được làm mới vào 04:00 AM theo giờ máy chủ hàng ngày.
+3. Trước khi Gói Đăng Ký Lunite hết hạn, phần thưởng hàng ngày chưa nhận trong những ngày bạn không đăng nhập sẽ không được bù lại.
 [Lưu ý]
 1. Khi thời gian đăng ký Gói Lunite hiện tại của bạn ≤180 ngày, mỗi lần mua Gói Đăng Ký sẽ gia hạn thêm 30 ngày.
 2. Khi thời gian đăng ký Gói Lunite hiện tại &gt;180 ngày, bạn không thể gia hạn thêm.
@@ -1658,10 +1658,10 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>Số điểm mở khóa sẽ được làm mới hàng ngày.
-Điểm mở khóa có thể dùng để mở khóa các Câu Chuyện Character quan trọng, với điều kiện sau:
-I. Hiện tại có ít hơn 3 Câu Chuyện Character quan trọng đang tiến hành
-II. Điều kiện tiên quyết để mở khóa Câu Chuyện Character đã được đáp ứng
-III. Số điểm mở khóa còn lại đủ để mở khóa nhiệm vụ Character mục tiêu.</t>
+Điểm mở khóa có thể dùng để mở khóa các Câu Chuyện Nhân Vật quan trọng, với điều kiện sau:
+I. Hiện tại có ít hơn 3 Câu Chuyện Nhân Vật quan trọng đang tiến hành
+II. Điều kiện tiên quyết để mở khóa Câu Chuyện Nhân Vật đã được đáp ứng
+III. Số điểm mở khóa còn lại đủ để mở khóa nhiệm vụ Nhân Vật mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -1727,8 +1727,8 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Basic Attack: Photosynthesis&lt;/color&gt;
-Verina có thể thực hiện tối đa VI đòn tấn công, gây sát thương phản ứng Spectro. Basic Attack thứ 6 của cô sẽ gieo một Bông Hoa Drop trên mục tiêu. Verina tự động nhặt các Bông Hoa Drop gần đó, chuyển hóa chúng thành Photosynthesis Energy. Verina có thể tích lũy tối đa 4 tầng Photosynthesis Energy.</t>
+          <t>&lt;color=yellow&gt;Basic Attack: Quang Hợp&lt;/color&gt;
+Verina có thể thực hiện tối đa VI đòn tấn công, gây DMG phản ứng Spectro. Đòn Basic Attack thứ 6 của cô sẽ gieo một Bông Hoa Rơi trên mục tiêu. Verina tự động nhặt các Bông Hoa Rơi gần đó, chuyển hóa chúng thành Năng Lượng Quang Hợp. Verina có thể tích lũy tối đa 4 tầng Năng Lượng Quang Hợp.</t>
         </is>
       </c>
     </row>
@@ -1794,8 +1794,8 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Chain Attack: Photon Bomb&lt;/color&gt;
-Khi Verina dùng Heavy Attack trúng mục tiêu, nếu cô có năng lượng quang hợp, cô sẽ tự động tiêu hao 1 tầng Năng Lượng Quang Hợp, kích nổ một vùng gây sát thương phản ứng Spectro và hồi HP cho cả đội tương đương 50% Attack của Verina.</t>
+          <t>&lt;color=yellow&gt;Chuỗi ATK: Bom Photon&lt;/color&gt;
+Khi Verina dùng ATK Mạnh trúng mục tiêu, nếu cô có năng lượng quang hợp, cô sẽ tự động tiêu hao 1 tầng Năng Lượng Quang Hợp, kích nổ một vùng gây sát thương phản ứng Spectro và hồi HP cho cả đội tương đương 50% ATK của Verina.</t>
         </is>
       </c>
     </row>
@@ -1861,8 +1861,8 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Resonance Skill: Green Vine Bloom&lt;/color&gt;
-Verina tập trung năng lượng phía trước, khiến thực vật mọc nhanh, gây sát thương phản ứng Spectro trong phạm vi, và hấp thụ các hạt hoa trên mục tiêu gần đó, ngẫu nhiên gắn 1 hạt hoa lên 1 mục tiêu trong phạm vi kỹ năng.</t>
+          <t>&lt;color=yellow&gt;Resonance Skill: Hoa Dây Leo Nở Rộ&lt;/color&gt;
+Verina tập trung năng lượng phía trước, khiến thực vật mọc nhanh, gây DMG phản ứng Spectro trong phạm vi, và hấp thụ các hạt hoa trên mục tiêu gần đó, ngẫu nhiên gắn 1 hạt hoa lên 1 mục tiêu trong phạm vi kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -1929,9 +1929,9 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Resonance Liberation: Incandescent Light&lt;/color&gt;
+          <t>&lt;color=yellow&gt;Resonance Liberation: Ánh Sáng Rực Rỡ&lt;/color&gt;
 Verina gây sát thương phạm vi và gắn dấu quang hợp lên các mục tiêu xung quanh.
-Khi tấn công mục tiêu đang mang dấu quang hợp, sẽ gây thêm sát thương bằng X% Tấn Công của Verina, và hồi phục X% Tấn Công của Verina cho nhân vật gây sát thương.</t>
+Khi tấn công mục tiêu đang mang dấu quang hợp, sẽ gây thêm sát thương bằng X% ATK của Verina, và hồi phục X% ATK của Verina cho nhân vật gây sát thương.</t>
         </is>
       </c>
     </row>
@@ -1997,8 +1997,8 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Character Pairing Tutorial (Example):&lt;/color&gt;
-Tích lũy sát thương nguyên tố thông qua Resonance Skill thuộc tính ánh sáng, sau khi kích hoạt Intro Skill, Verina sẽ gây sát thương cao.</t>
+          <t>&lt;color=yellow&gt;Hướng Dẫn Ghép Cặp Nhân Vật (Ví Dụ): &lt;/color&gt;
+Tích lũy sát thương nguyên tố thông qua Resonance Skill thuộc tính ánh sáng, sau khi kích hoạt Kỹ Năng Khởi Động, Verina sẽ gây sát thương cao.</t>
         </is>
       </c>
     </row>
@@ -2143,22 +2143,22 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>[&lt;color=#c19f51&gt;Đội Selection&lt;/color&gt;]
-Sau khi học viên lập đội, có thể bắt đầu thử thách. Số lượng Resonators tối thiểu trong một đội là &lt;color=#c19f51&gt;1&lt;/color&gt;, tối đa là &lt;color=#c19f51&gt;3&lt;/color&gt;. Đội hình sẽ ghi nhận trạng thái phát triển của Resonators đã chọn, và sẽ không thay đổi trong suốt quá trình huấn luyện quy mô lớn.
+          <t>[&lt;color=#c19f51&gt;Lựa Chọn Đội Hình&lt;/color&gt;]
+Sau khi học viên lập đội, có thể bắt đầu thử thách. Số lượng Resonator tối thiểu trong một đội là &lt;color=#c19f51&gt;1&lt;/color&gt;, tối đa là &lt;color=#c19f51&gt;3&lt;/color&gt;. Đội hình sẽ ghi nhận trạng thái phát triển của các Resonator đã chọn, và sẽ không thay đổi trong suốt quá trình huấn luyện quy mô lớn.
 Bắt đầu từ huấn luyện cấp &lt;color=#c19f51&gt;3&lt;/color&gt; - Mô Phỏng Thực Cảnh, học viên cần lập &lt;color=#c19f51&gt;2&lt;/color&gt; đội để tham gia thử thách trước khi bắt đầu.
-[&lt;color=#c19f51&gt;Training Purpose&lt;/color&gt;]
+[&lt;color=#c19f51&gt;Mục Đích Huấn Luyện&lt;/color&gt;]
 Nếu học viên tiêu diệt hết kẻ địch trong thời gian giới hạn, buổi huấn luyện được coi là thành công. Chỉ sau khi thành công, học viên mới có thể tiến vào buổi huấn luyện tiếp theo. Nếu hoàn thành tất cả các buổi huấn luyện nhỏ trong một đợt huấn luyện quy mô lớn, đợt huấn luyện đó được coi là thành công.
-Trong huấn luyện quy mô lớn, trạng thái của Resonators sẽ được kế thừa. Học viên cần đảm bảo ít nhất &lt;color=#c19f51&gt;1&lt;/color&gt; Resonators trong đội còn sống sót, như vậy mới được coi là vượt qua đợt huấn luyện quy mô lớn.
-[&lt;color=#c19f51&gt;Training Subjects&lt;/color&gt;]
+Trong huấn luyện quy mô lớn, trạng thái của Resonator sẽ được kế thừa. Học viên cần đảm bảo ít nhất &lt;color=#c19f51&gt;1&lt;/color&gt; Resonator trong đội còn sống sót, như vậy mới được coi là vượt qua đợt huấn luyện quy mô lớn.
+[&lt;color=#c19f51&gt;Nội Dung Huấn Luyện&lt;/color&gt;]
 Toàn bộ quá trình bao gồm &lt;color=#c19f51&gt;4&lt;/color&gt; đợt huấn luyện quy mô lớn. Trong &lt;color=#c19f51&gt;3&lt;/color&gt; đợt huấn luyện quy mô lớn đầu tiên, mỗi đợt có &lt;color=#c19f51&gt;4&lt;/color&gt; buổi huấn luyện nhỏ. Đợt huấn luyện quy mô lớn thứ &lt;color=#c19f51&gt;4&lt;/color&gt; chỉ có &lt;color=#c19f51&gt;1&lt;/color&gt; buổi huấn luyện.
-Học viên có thể tạm rời Tower of Adversity sau khi hoàn thành một buổi huấn luyện, tiến độ huấn luyện sẽ được ghi lại. Sau đó, học viên có thể chọn tiếp tục hoặc đặt lại tiến độ.
+Học viên có thể tạm rời Tháp Nghịch Cảnh sau khi hoàn thành một buổi huấn luyện, tiến độ huấn luyện sẽ được ghi lại. Sau đó, học viên có thể chọn tiếp tục hoặc đặt lại tiến độ.
 Ngoại trừ việc tiếp tục huấn luyện, học viên chỉ có thể bắt đầu lại từ buổi huấn luyện đầu tiên của đợt huấn luyện quy mô lớn.
-[&lt;color=#c19f51&gt;Ability Limitations&lt;/color&gt;]
-Trong Tower of Adversity, học viên không thể phát triển Resonators, sử dụng vật phẩm, thay đổi trang bị và Echo trong quá trình huấn luyện, một số chức năng hệ thống cũng sẽ bị vô hiệu hóa.
-[&lt;color=#c19f51&gt;Guardian of the Giọng nói&lt;/color&gt;]
-Trong Tower of Adversity, các buổi huấn luyện khác nhau có thể mang lại hiệu ứng buff khác nhau. Học viên có thể điều chỉnh đội hình, trang bị hoặc Echo dựa trên hiệu ứng buff.
-[&lt;color=#c19f51&gt;Reward Rules&lt;/color&gt;]
-Khi vượt qua một buổi huấn luyện lần đầu, học viên sẽ nhận được phần thưởng sau khi kết thúc. &lt;color=#c19f51&gt;Repeatedly passing the cleared training will not receive the reward again&lt;/color&gt;.</t>
+[&lt;color=#c19f51&gt;Hạn Chế Năng Lực&lt;/color&gt;]
+Trong Tháp Nghịch Cảnh, học viên không thể phát triển Resonator, sử dụng vật phẩm, thay đổi trang bị và Echo trong quá trình huấn luyện, một số chức năng hệ thống cũng sẽ bị vô hiệu hóa.
+[&lt;color=#c19f51&gt;Người Bảo Hộ Âm Thanh&lt;/color&gt;]
+Trong Tháp Nghịch Cảnh, các buổi huấn luyện khác nhau có thể mang lại hiệu ứng buff khác nhau. Học viên có thể điều chỉnh đội hình, trang bị hoặc Echo dựa trên hiệu ứng buff.
+[&lt;color=#c19f51&gt;Quy Tắc Phần Thưởng&lt;/color&gt;]
+Khi vượt qua một buổi huấn luyện lần đầu, học viên sẽ nhận được phần thưởng sau khi kết thúc. &lt;color=#c19f51&gt;Vượt qua buổi huấn luyện đã hoàn thành trước đó sẽ không nhận lại phần thưởng&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2225,9 +2225,9 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Yangyang's Unique Ability: Listening to the Wind&lt;/color&gt;
-Khi Yangyang sử dụng [Heavy Attack], cô có thể tiêu hao 1 lớp [Echo] để thực hiện lại [Basic Attack], gây sát thương thuộc tính gió.
-[Echo] có thể tích lũy thông qua [Chuỗi Basic Attack], [Intro Skill], [Phát Kích Feather] và [Effect Gió Bắc].</t>
+          <t>&lt;color=yellow&gt;Kỹ năng đặc biệt của Yangyang: Lắng nghe gió&lt;/color&gt;
+Khi Yangyang sử dụng [Đòn Heavy Attack], cô có thể tiêu hao 1 lớp [Tiếng Vọng] để thực hiện lại [Đòn Basic Attack], gây sát thương thuộc tính gió.
+[Tiếng Vọng] có thể tích lũy thông qua [Chuỗi Đòn Basic Attack], [Kỹ Năng Khởi Động], [Phát Kích Lông Vũ] và [Hiệu Ứng Gió Bắc].</t>
         </is>
       </c>
     </row>
@@ -2293,8 +2293,8 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Đội-up Guide:&lt;/color&gt;
-Resonance Skill "Phá Gió Feather" và Kỹ Năng Bùng Nổ "Effect Gió Bắc" của Yangyang đều có thể tạo hiệu ứng tập trung quái vật, tăng đáng kể hiệu suất tấn công.</t>
+          <t>&lt;color=yellow&gt;Hướng dẫn phối hợp: &lt;/color&gt;
+Resonance Skill "Phá Gió Lông Vũ" và Kỹ Năng Bùng Nổ "Hiệu Ứng Gió Bắc" của Yangyang đều có thể tạo hiệu ứng tập trung quái vật, tăng đáng kể hiệu suất tấn công.</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2368,12 @@
         <is>
           <t>&lt;color=yellow&gt;Basic Attack&lt;/color&gt;
 Thực hiện tối đa 4 đòn chém kiếm liên tiếp. Nếu đòn thứ 4 trúng mục tiêu, bạn sẽ nhận được 1 tầng Echo.
-&lt;color=yellow&gt;Heavy Attack&lt;/color&gt;
-Tiêu hao STA để lao về phía trước và gây Aero DMG.
-&lt;color=yellow&gt;Mid-air Attack&lt;/color&gt;
-Tiêu hao STA để bật lên không và đâm xuống đất, gây sát thương diện rộng.
-&lt;color=yellow&gt;Chain Attack: Galesong&lt;/color&gt;
-Sử dụng Basic Attack trong một khoảng thời gian nhất định sau Heavy Attack sẽ tiêu hao 1 tầng Aria để triệu hồi lưỡi kiếm gió, gây Aero DMG.</t>
+&lt;color=yellow&gt;Tấn Công Mạnh&lt;/color&gt;
+Tiêu hao STA để lao về phía trước và gây DMG Aero.
+&lt;color=yellow&gt;Tấn Công Giữa Không&lt;/color&gt;
+Tiêu hao STA để bật lên không và đâm xuống đất, gây DMG diện rộng.
+&lt;color=yellow&gt;Chuỗi Tấn Công: Khúc Ca Gió&lt;/color&gt;
+Sử dụng Basic Attack trong một khoảng thời gian nhất định sau Tấn Công Mạnh sẽ tiêu hao 1 tầng Aria để triệu hồi lưỡi kiếm gió, gây DMG Aero.</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Resonance Skill: Wind Feather Break&lt;/color&gt;
+          <t>&lt;color=yellow&gt;Resonance Skill: Phá Gió Lông Vũ&lt;/color&gt;
 Sử dụng kiếm pháp sắc bén tạo ra trường gió, kéo kẻ địch xung quanh về vị trí của bạn, gây sát thương phản ứng Aero trong phạm vi.
-[Phát Kiếm Feather]
-Sử dụng Heavy Attack sau khi kích hoạt [Phá Gió Feather] để tung ra [Phát Kiếm Feather], gây sát thương phản ứng Aero và Hất Tung mục tiêu.
-[Rơi Feather]
-Sử dụng Basic Attack sau khi Hất Tung mục tiêu bằng [Phát Kiếm Feather] để kích hoạt [Rơi Feather], gây sát thương phạm vi bằng cách đập xuống đất.</t>
+[Phát Kiếm Lông Vũ]
+Sử dụng Đòn Heavy Attack sau khi kích hoạt [Phá Gió Lông Vũ] để tung ra [Phát Kiếm Lông Vũ], gây sát thương phản ứng Aero và Hất Tung mục tiêu.
+[Rơi Lông Vũ]
+Sử dụng Đòn Basic Attack sau khi Hất Tung mục tiêu bằng [Phát Kiếm Lông Vũ] để kích hoạt [Rơi Lông Vũ], gây sát thương phạm vi bằng cách đập xuống đất.</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Resonance Liberation: Effect of the North Wind&lt;/color&gt;
+          <t>&lt;color=yellow&gt;Resonance Liberation: Hiệu Ứng Gió Bắc&lt;/color&gt;
 Vung kiếm tạo ra lốc xoáy, gây sát thương phản ứng Aero trong phạm vi, và cuối cùng là Hất Tung kẻ địch.</t>
         </is>
       </c>
@@ -2581,8 +2581,8 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Character Đội-up Tutorial (Example):&lt;/color&gt;
-Tích lũy sát thương nguyên tố thông qua Resonance Skill của Yangyang, kích hoạt Intro Skill, Yangyang sẽ gây sát thương cao.</t>
+          <t>&lt;color=yellow&gt;Hướng Dẫn Hợp Tác Nhân Vật (Ví Dụ): &lt;/color&gt;
+Tích lũy sát thương nguyên tố thông qua Resonance Skill của Yangyang, kích hoạt Kỹ Năng Khởi Động, Yangyang sẽ gây sát thương cao.</t>
         </is>
       </c>
     </row>
@@ -2724,18 +2724,18 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>[
-Pioneer Podcast]
-Một podcast do Pioneer Association vận hành. Nó đóng vai trò như một hướng dẫn nâng cao trải nghiệm khám phá thế giới của bạn, đồng thời mang đến những phần thưởng hậu hĩnh.
-Mỗi lần kích hoạt Pioneer Podcast, kênh Công Cộng sẽ tự động mở khóa.
+Podcast Tiên Phong]
+Một podcast do Hiệp Hội Tiên Phong vận hành. Nó đóng vai trò như một hướng dẫn nâng cao trải nghiệm khám phá thế giới của bạn, đồng thời mang đến những phần thưởng hậu hĩnh.
+Mỗi lần kích hoạt Podcast Tiên Phong, kênh Công Cộng sẽ tự động mở khóa.
 Bạn có thể mua kênh Nội Bộ hoặc kênh Nghệ Nhân để nhận thêm phần thưởng.
-[Nhiệm Vụ Pioneer Podcast]
-Bạn có thể nhận EXP Podcast bằng cách hoàn thành Nhiệm Vụ Podcast để tăng cấp Podcast, từ đó mở khóa thêm kênh và phần thưởng.
-Nhiệm Vụ Podcast bao gồm Bản Tin Sáng, Điểm Tin Tuần và Đặc San Mùa. EXP Podcast từ Đặc San Mùa không bị tính vào giới hạn EXP hàng tuần.
+[Nhiệm Vụ Podcast Tiên Phong]
+Bạn có thể nhận Điểm Kinh Nghiệm Podcast bằng cách hoàn thành Nhiệm Vụ Podcast để tăng cấp Podcast, từ đó mở khóa thêm kênh và phần thưởng.
+Nhiệm Vụ Podcast bao gồm Bản Tin Sáng, Điểm Tin Tuần và Đặc San Mùa. Điểm Kinh Nghiệm Podcast từ Đặc San Mùa không bị tính vào giới hạn Điểm Kinh Nghiệm hàng tuần.
 Bản Tin Sáng được cập nhật mỗi ngày vào lúc 04:00 theo giờ máy chủ, và Điểm Tin Tuần được cập nhật vào thứ Hai hàng tuần lúc 04:00 theo giờ máy chủ.
 Khi cấp độ Podcast của giai đoạn hiện tại đạt giới hạn, nó sẽ không tăng thêm nữa.
 [Lưu Ý]
 Nếu bạn vô tình kích hoạt lại kênh (như kênh Nội Bộ, kênh Nghệ Nhân hoặc nâng cấp từ kênh Nội Bộ lên kênh Nghệ Nhân), phần thưởng sẽ không được phát lại và số Lunite tương đương sẽ được hoàn trả trực tiếp.
-Khi Pioneer Podcast hiện tại kết thúc, mọi phần thưởng cấp độ chưa nhận sẽ được gửi qua thư.</t>
+Khi Podcast Tiên Phong hiện tại kết thúc, mọi phần thưởng cấp độ chưa nhận sẽ được gửi qua thư.</t>
         </is>
       </c>
     </row>
@@ -2875,15 +2875,15 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>[Điều Kiện Tham Gia]
-Đạt Cấp Liên Minh 35 và đến Tower Chuông trong Nhiệm Vụ Chính "Ngọn Lửa Trong Tim".
-[Event Rules]
-1. Trong thời gian thử thách, hãy khám phá và chiến đấu tại các quận thành phố. Hạ gục kẻ địch Elite tại năm khu vực thử thách để nhận Astrites và nhiều phần thưởng khác.
-2. Nếu bị đánh bại trong khu vực thử thách, Cấp Glory của bạn sẽ quay về Cấp Challenges. Hạ gục kẻ địch hoặc kích hoạt Cờ Chiến sẽ giúp tăng Cấp Glory.
-3. Sử dụng thành công các kỹ thuật như Phản Đòn và Dodge Đòn Tấn Công sẽ tăng dần Battle Engagement Points, từ đó tạm thời nâng Cấp Glory. Sử dụng khéo léo các kỹ thuật này sẽ giúp bạn chiến đấu hiệu quả hơn.
-4. Cờ Chiến được phân bố khắp khu vực. Tìm và kích hoạt chúng để nhận thưởng tăng cả Cấp Challenges và Cấp Glory. Một số lá cờ còn mang lại hiệu ứng bổ trợ khác.
-5. Finish tất cả thử thách "Cờ Chiến: Cấp Trung" và "Cờ Chiến: Cấp Cao" để kết thúc Sự Kiện "Cờ Chiến Bất Diệt". Khi sự kiện kết thúc, các khu vực thử thách vẫn sẽ cung cấp hiệu ứng đặc biệt, và kẻ địch thông thường sẽ xuất hiện trở lại.
-※Hạ gục kẻ địch Elite sẽ mở khóa các Cờ Chiến còn lại và tiết lộ tất cả Rương Báu Ẩn trong khu vực.
-※Đây là tính năng chơi vĩnh viễn. Nếu chưa hoàn thành Sự Kiện "Cờ Chiến Bất Diệt" sau khi Phiên Bản 2.4 kết thúc, bạn vẫn có thể tiếp tục tham gia qua mục Sự Kiện Permanent.</t>
+Đạt Cấp Liên Minh 35 và đến Tháp Chuông trong Nhiệm Vụ Chính "Ngọn Lửa Trong Tim".
+[Quy Tắc Sự Kiện]
+1. Trong thời gian thử thách, hãy khám phá và chiến đấu tại các quận thành phố. Hạ gục kẻ địch Tinh Anh tại năm khu vực thử thách để nhận Astrites và nhiều phần thưởng khác.
+2. Nếu bị đánh bại trong khu vực thử thách, Cấp Vinh Quang của bạn sẽ quay về Cấp Thử Thách. Hạ gục kẻ địch hoặc kích hoạt Cờ Chiến sẽ giúp tăng Cấp Vinh Quang.
+3. Sử dụng thành công các kỹ thuật như Phản Đòn và Né Tránh Đòn Tấn Công sẽ tăng dần Điểm Tham Chiến, từ đó tạm thời nâng Cấp Vinh Quang. Sử dụng khéo léo các kỹ thuật này sẽ giúp bạn chiến đấu hiệu quả hơn.
+4. Cờ Chiến được phân bố khắp khu vực. Tìm và kích hoạt chúng để nhận thưởng tăng cả Cấp Thử Thách và Cấp Vinh Quang. Một số lá cờ còn mang lại hiệu ứng bổ trợ khác.
+5. Hoàn thành tất cả thử thách "Cờ Chiến: Cấp Trung" và "Cờ Chiến: Cấp Cao" để kết thúc Sự Kiện "Cờ Chiến Bất Diệt". Khi sự kiện kết thúc, các khu vực thử thách vẫn sẽ cung cấp hiệu ứng đặc biệt, và kẻ địch thông thường sẽ xuất hiện trở lại.
+※Hạ gục kẻ địch Tinh Anh sẽ mở khóa các Cờ Chiến còn lại và tiết lộ tất cả Rương Báu Ẩn trong khu vực.
+※Đây là tính năng chơi vĩnh viễn. Nếu chưa hoàn thành Sự Kiện "Cờ Chiến Bất Diệt" sau khi Phiên Bản 2.4 kết thúc, bạn vẫn có thể tiếp tục tham gia qua mục Sự Kiện Vĩnh Viễn.</t>
         </is>
       </c>
     </row>
@@ -2958,15 +2958,15 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>[Điều Kiện Tham Gia]
-Đạt Cấp Liên Minh 35 và đến Tower Chuông trong Nhiệm Vụ Chính "Ngọn Lửa Trong Tim".
-[Event Rules]
-1. Trong thời gian thử thách, hãy khám phá và chiến đấu tại các quận thành phố. Hạ gục kẻ địch Elite tại năm khu vực thử thách để nhận Astrites và nhiều phần thưởng khác.
-2. Nếu bị đánh bại trong khu vực thử thách, Cấp Glory của bạn sẽ quay về Cấp Challenges. Hạ gục kẻ địch hoặc kích hoạt Cờ Chiến sẽ giúp tăng Cấp Glory.
-3. Sử dụng thành công các kỹ thuật như Phản Đòn và Dodge Đòn Tấn Công sẽ tăng dần Battle Engagement Points, từ đó tạm thời nâng Cấp Glory. Sử dụng khéo léo các kỹ thuật này sẽ giúp bạn chiến đấu hiệu quả hơn.
-4. Cờ Chiến được phân bố khắp khu vực. Tìm và kích hoạt chúng để nhận thưởng tăng cả Cấp Challenges và Cấp Glory. Một số lá cờ còn mang lại hiệu ứng bổ trợ khác.
-5. Finish tất cả thử thách "Cờ Chiến: Cấp Trung" và "Cờ Chiến: Cấp Cao" để kết thúc Sự Kiện "Cờ Chiến Bất Diệt". Khi sự kiện kết thúc, các khu vực thử thách vẫn sẽ cung cấp hiệu ứng đặc biệt, và kẻ địch thông thường sẽ xuất hiện trở lại.
-※Hạ gục kẻ địch Elite sẽ mở khóa các Cờ Chiến còn lại và tiết lộ tất cả Rương Báu Ẩn trong khu vực.
-※Đây là tính năng chơi vĩnh viễn. Nếu chưa hoàn thành Sự Kiện "Cờ Chiến Bất Diệt" sau khi Phiên Bản 2.4 kết thúc, bạn vẫn có thể tiếp tục tham gia qua mục Sự Kiện Permanent.</t>
+Đạt Cấp Liên Minh 35 và đến Tháp Chuông trong Nhiệm Vụ Chính "Ngọn Lửa Trong Tim".
+[Quy Tắc Sự Kiện]
+1. Trong thời gian thử thách, hãy khám phá và chiến đấu tại các quận thành phố. Hạ gục kẻ địch Tinh Anh tại năm khu vực thử thách để nhận Astrites và nhiều phần thưởng khác.
+2. Nếu bị đánh bại trong khu vực thử thách, Cấp Vinh Quang của bạn sẽ quay về Cấp Thử Thách. Hạ gục kẻ địch hoặc kích hoạt Cờ Chiến sẽ giúp tăng Cấp Vinh Quang.
+3. Sử dụng thành công các kỹ thuật như Phản Đòn và Né Tránh Đòn Tấn Công sẽ tăng dần Điểm Tham Chiến, từ đó tạm thời nâng Cấp Vinh Quang. Sử dụng khéo léo các kỹ thuật này sẽ giúp bạn chiến đấu hiệu quả hơn.
+4. Cờ Chiến được phân bố khắp khu vực. Tìm và kích hoạt chúng để nhận thưởng tăng cả Cấp Thử Thách và Cấp Vinh Quang. Một số lá cờ còn mang lại hiệu ứng bổ trợ khác.
+5. Hoàn thành tất cả thử thách "Cờ Chiến: Cấp Trung" và "Cờ Chiến: Cấp Cao" để kết thúc Sự Kiện "Cờ Chiến Bất Diệt". Khi sự kiện kết thúc, các khu vực thử thách vẫn sẽ cung cấp hiệu ứng đặc biệt, và kẻ địch thông thường sẽ xuất hiện trở lại.
+※Hạ gục kẻ địch Tinh Anh sẽ mở khóa các Cờ Chiến còn lại và tiết lộ tất cả Rương Báu Ẩn trong khu vực.
+※Đây là tính năng chơi vĩnh viễn. Nếu chưa hoàn thành Sự Kiện "Cờ Chiến Bất Diệt" sau khi Phiên Bản 2.4 kết thúc, bạn vẫn có thể tiếp tục tham gia qua mục Sự Kiện Vĩnh Viễn.</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Sau khi hoàn thành tất cả thử thách "Banner of Conquest: Medium" và "Banner of Conquest: Major", cậu có thể vô hiệu hóa chế độ "Banners Never Fall" thông qua Nhiệm Vụ Tutorial "Path of the Victorious".
+          <t>Sau khi hoàn thành tất cả thử thách "Banner of Conquest: Medium" và "Banner of Conquest: Major", cậu có thể vô hiệu hóa chế độ "Banners Never Fall" thông qua Nhiệm Vụ Hướng Dẫn "Path of the Victorious".
 Khi chế độ này bị vô hiệu hóa, kẻ địch thông thường sẽ xuất hiện trở lại trong khu vực, và hệ thống Glory Level sẽ bị tắt. Tuy nhiên, cậu vẫn có thể nhận được buff trong các vùng thử thách.
 Các Rương Chiến Lợi phẩm chưa nhận trong vùng thử thách sẽ vẫn còn để thu thập.</t>
         </is>
@@ -3104,10 +3104,10 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1. Trong sự kiện, bạn có thể xây dựng bộ bài riêng và chọn Tactics Resonator để thách đấu các cao thủ Duelist danh tiếng như Lords of Prestige và Conqueror of Prestige. Bạn có thể Dịch Chuyển Nhanh đến vị trí của họ qua Map.
-2. Bạn kiếm được Points Glory qua các trận đấu. Points Glory có thể dùng để mở khóa thêm Echoes, tùy chỉnh và tăng cường bộ bài.
+          <t>1. Trong sự kiện, bạn có thể xây dựng bộ bài riêng và chọn Chiến Thuật Resonator để thách đấu các cao thủ Duelist danh tiếng như Lords of Prestige và Conqueror of Prestige. Bạn có thể Dịch Chuyển Nhanh đến vị trí của họ qua Bản Đồ.
+2. Bạn kiếm được Điểm Vinh Quang qua các trận đấu. Điểm Vinh Quang có thể dùng để mở khóa thêm Echoes, tùy chỉnh và tăng cường bộ bài.
 3. Các trận đấu cũng mang lại Duel Resonance, dùng để nâng cấp Cấp Độ Duelist. Tăng cấp sẽ mở khóa kỹ năng và nâng cấp mới, cùng nhiều phần thưởng khác.
-4. Sau khi sự kiện kết thúc, bạn sẽ mở khóa Challenges Vô Tận, nơi bạn cạnh tranh với các Duelist khắp Septimont và nhận thưởng.
+4. Sau khi sự kiện kết thúc, bạn sẽ mở khóa Thử Thách Vô Tận, nơi bạn cạnh tranh với các Duelist khắp Septimont và nhận thưởng.
 5. Sau khi sự kiện kết thúc, bạn sẽ đối mặt với những thử thách từ các Duelist bí ẩn. Hãy đón nhận thử thách và nhận phần thưởng xứng đáng.</t>
         </is>
       </c>
@@ -3185,19 +3185,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>["Tower Trial"]
-Trong Tower Trial, kỹ năng của bạn sẽ được thử lửa. Hoàn thành các mục tiêu thử thách cụ thể để nhận được Huy Hiệu. Khi đủ Huy Hiệu, bạn sẽ nhận được những phần thưởng hậu hĩnh.
-[Zone và Tower]
-&lt;color=#c19f51&gt;The Tower of Adversity features four Zones: Stable Zone, Experiment Zone, Hazard Zone, and Overdrive Zone.&lt;/color&gt; Mỗi Zone có từ một đến ba Tower, mỗi Tower lại có nhiều Tầng, mỗi Tầng là một thử thách độc đáo. Vượt qua các thử thách để mở khóa Tower và Zone mới. Hoàn thành Zone Ổn định sẽ mở khóa Zone Thí nghiệm, và hoàn thành Zone Thí nghiệm sẽ đồng thời mở khóa Hazard Zone và Zone Quá tải.
+          <t>["Tháp Thử Thách"]
+Trong Tháp Thử Thách, kỹ năng của bạn sẽ được thử lửa. Hoàn thành các mục tiêu thử thách cụ thể để nhận được Huy Hiệu. Khi đủ Huy Hiệu, bạn sẽ nhận được những phần thưởng hậu hĩnh.
+[Khu vực và Tháp]
+&lt;color=#c19f51&gt;Tháp Thử Thách bao gồm bốn Khu vực: Khu vực Ổn định, Khu vực Thí nghiệm, Khu vực Nguy hiểm và Khu vực Quá tải.&lt;/color&gt; Mỗi Khu vực có từ một đến ba Tháp, mỗi Tháp lại có nhiều Tầng, mỗi Tầng là một thử thách độc đáo. Vượt qua các thử thách để mở khóa Tháp và Khu vực mới. Hoàn thành Khu vực Ổn định sẽ mở khóa Khu vực Thí nghiệm, và hoàn thành Khu vực Thí nghiệm sẽ đồng thời mở khóa Khu vực Nguy hiểm và Khu vực Quá tải.
 [Sinh lực]
-Trong Tower Trial, mỗi lần hoàn thành thử thách sẽ làm giảm một lượng Sinh lực nhất định của Resonators tham gia. Khi Sinh lực của một Resonators cạn kiệt, họ không thể tham gia thử thách mới nữa. &lt;color=#c19f51&gt;Vigor does not restore over time, but you can use the [Đặt lại] option on a Floor to recover the Vigor.&lt;/color&gt;
-[Hiệu ứng Zone]
-Trong Tower Trial, các hiệu ứng môi trường đặc biệt sẽ ảnh hưởng đến chiến thuật chiến đấu của bạn.
-[Giai đoạn Trial]
-Rewards Huy Hiệu ở Zone Ổn định, Zone Thí nghiệm và Zone Quá tải chỉ có thể nhận một lần. &lt;color=#c19f51&gt;However, the challenges in the Hazard Zone are periodically reset, along with your progression, bringing in new enemies, challenge goals, Area Effects, and rewards. Take on the challenges again to earn Crests and claim fresh rewards.&lt;/color&gt;
+Trong Tháp Thử Thách, mỗi lần hoàn thành thử thách sẽ làm giảm một lượng Sinh lực nhất định của Resonator tham gia. Khi Sinh lực của một Resonator cạn kiệt, họ không thể tham gia thử thách mới nữa. &lt;color=#c19f51&gt;Sinh lực không tự phục hồi theo thời gian, nhưng bạn có thể sử dụng tùy chọn [Đặt lại] ở một Tầng để khôi phục Sinh lực.&lt;/color&gt;
+[Hiệu ứng Khu vực]
+Trong Tháp Thử Thách, các hiệu ứng môi trường đặc biệt sẽ ảnh hưởng đến chiến thuật chiến đấu của bạn.
+[Giai đoạn Thử nghiệm]
+Phần thưởng Huy Hiệu ở Khu vực Ổn định, Khu vực Thí nghiệm và Khu vực Quá tải chỉ có thể nhận một lần. &lt;color=#c19f51&gt;Tuy nhiên, các thử thách ở Khu vực Nguy hiểm sẽ được đặt lại định kỳ, cùng với tiến trình của bạn, mang đến kẻ địch mới, mục tiêu thử thách mới, Hiệu ứng Khu vực mới và phần thưởng mới. Hãy đối mặt với thử thách lần nữa để kiếm Huy Hiệu và nhận phần thưởng mới.&lt;/color&gt;
 [Đồng bộ Kỷ lục]
-Kỷ lục thử thách của bạn ở &lt;color=#c19f51&gt;Floor 1-2 of Resonant Tower and Echoing Tower&lt;/color&gt; từ Giai đoạn Trial trước sẽ được giữ lại nếu bạn đã kiếm được &lt;color=#c19f51&gt;24&lt;/color&gt; Huy Hiệu trong Giai đoạn Trial trước với &lt;color=#c19f51&gt;full Crests&lt;/color&gt; ở các Tầng này;
-Kỷ lục thử thách của bạn ở &lt;color=#c19f51&gt;Floor 1-3 of Resonant Tower and Echoing Tower&lt;/color&gt; từ Giai đoạn Trial trước sẽ được giữ lại nếu bạn đã kiếm được &lt;color=#c19f51&gt;30&lt;/color&gt; Huy Hiệu trong Giai đoạn Trial trước với &lt;color=#c19f51&gt;full Crests&lt;/color&gt; ở các Tầng này.</t>
+Kỷ lục thử thách của bạn ở &lt;color=#c19f51&gt;Tầng 1-2 của Tháp Cộng Hưởng và Tháp Vọng Âm&lt;/color&gt; từ Giai đoạn Thử nghiệm trước sẽ được giữ lại nếu bạn đã kiếm được &lt;color=#c19f51&gt;24&lt;/color&gt; Huy Hiệu trong Giai đoạn Thử nghiệm trước với &lt;color=#c19f51&gt;đầy đủ Huy Hiệu&lt;/color&gt; ở các Tầng này;
+Kỷ lục thử thách của bạn ở &lt;color=#c19f51&gt;Tầng 1-3 của Tháp Cộng Hưởng và Tháp Vọng Âm&lt;/color&gt; từ Giai đoạn Thử nghiệm trước sẽ được giữ lại nếu bạn đã kiếm được &lt;color=#c19f51&gt;30&lt;/color&gt; Huy Hiệu trong Giai đoạn Thử nghiệm trước với &lt;color=#c19f51&gt;đầy đủ Huy Hiệu&lt;/color&gt; ở các Tầng này.</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Tham gia các trận đấu để kiếm Duel Resonance. Dùng Duel Resonance để tăng Cấp Độ Duel Sĩ, mở khóa kỹ năng và nâng cấp mới cho trận đấu, cùng nhiều phần thưởng khác.</t>
+          <t>Tham gia các trận đấu để kiếm Duel Resonance. Dùng Duel Resonance để tăng Cấp Độ Đấu Sĩ, mở khóa kỹ năng và nâng cấp mới cho trận đấu, cùng nhiều phần thưởng khác.</t>
         </is>
       </c>
     </row>
@@ -3402,11 +3402,11 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>Về Sự Kiện
-Với người dân Septimont, Sanguis Plateaus chính là hiện thân của vinh quang. Hàng thế hệ Võ Sĩ Đấu đã đặt chân lên mảnh đất đỏ thẫm này với ngọn lửa đam mê không bao giờ tắt. Dưới ánh mắt của những tượng đài Anh Hùng Của Các Anh Hùng, họ hạ gục kẻ thù bằng lưỡi kiếm sắc bén và trái tim rực cháy, máu nhuộm đỏ rừng cây. Vô số huyền thoại đã được viết nên ở đây, nhưng ít ai biết đến những bóng tối ẩn giấu sau vẻ hào nhoáng ấy.
+Với người dân Septimont, Cao Nguyên Sanguis chính là hiện thân của vinh quang. Hàng thế hệ Võ Sĩ Đấu đã đặt chân lên mảnh đất đỏ thẫm này với ngọn lửa đam mê không bao giờ tắt. Dưới ánh mắt của những tượng đài Anh Hùng Của Các Anh Hùng, họ hạ gục kẻ thù bằng lưỡi kiếm sắc bén và trái tim rực cháy, máu nhuộm đỏ rừng cây. Vô số huyền thoại đã được viết nên ở đây, nhưng ít ai biết đến những bóng tối ẩn giấu sau vẻ hào nhoáng ấy.
 Theo yêu cầu của một bà lão, ngươi truy tìm linh hồn của một anh hùng đã ngã xuống, lần theo những ký ức của một quá khứ bị lãng quên...
 Điều Kiện Tham Gia
-Hoàn thành Chương II Act VIII "Dưới Bàn Tay Thiêu Đốt Của Mặt Trời" và Nhiệm Vụ Phụ "Cán Cân Quá Khứ" để mở khóa.
-Event Rules
+Hoàn thành Chương II Hồi VIII "Dưới Bàn Tay Thiêu Đốt Của Mặt Trời" và Nhiệm Vụ Phụ "Cán Cân Quá Khứ" để mở khóa.
+Quy Tắc Sự Kiện
 Theo dấu vết để khám phá các khu vực và thu thập những Mảnh Thời Gian rải rác.
 Thu thập đủ Mảnh Thời Gian để nhận Astrites và nhiều phần thưởng khác.
 Sẽ có thêm Mảnh Thời Gian để thu thập ở các khu vực khác trong tương lai.
@@ -3489,13 +3489,13 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>Sự kiện web “Trở Lại Solaris” đã bắt đầu! Tham gia để nhận tới 530 Astrites cùng nhiều phần thưởng khác.
-Invite những người bạn cũ quay lại và cùng hoàn thành nhiệm vụ để nhận Astrites, Shell Credits và nhiều phần thưởng khác! Các Rover quay lại liên kết tài khoản sẽ nhận thêm quà tặng đặc biệt!
+Mời những người bạn cũ quay lại và cùng hoàn thành nhiệm vụ để nhận Astrites, Shell Credits và nhiều phần thưởng khác! Các Vận Mệnh Giả quay lại liên kết tài khoản sẽ nhận thêm quà tặng đặc biệt!
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 8
 [Quy tắc]
-1. Share mã mời của bạn với tối đa 3 người chơi quay lại trong máy chủ của bạn, hoàn thành nhiệm vụ trong game để nhận Ngọn Lửa Tâm Linh và đổi lấy tối đa Astrite x480 và Shell Credit x300.000.
+1. Chia sẻ mã mời của bạn với tối đa 3 người chơi quay lại trong máy chủ của bạn, hoàn thành nhiệm vụ trong game để nhận Ngọn Lửa Tâm Linh và đổi lấy tối đa Astrite x480 và Shell Credit x300.000.
 2. Người chơi quay lại có thể liên kết tài khoản với người chơi mà họ chọn bằng mã mời tương ứng. Việc này chỉ có thể thực hiện một lần và không thể thay đổi sau đó. Sau khi liên kết, người chơi quay lại đủ điều kiện nhận phần thưởng gồm Astrite x50, Bình Nuôi Tế Tiến Tiến x5 và Shell Credit x50.000.
-※ Mail phần thưởng trong game có thể nhận trong vòng 30 ngày kể từ khi phần thưởng được cấp.
+※ Thư phần thưởng trong game có thể nhận trong vòng 30 ngày kể từ khi phần thưởng được cấp.
 ※ Sau khi hoàn thành nhiệm vụ sự kiện, có thể có chút trễ trước khi nhận phần thưởng. Nếu gặp trường hợp này, hãy đợi ít nhất 2 phút trước khi làm mới trang hoặc khởi động lại game.
 ※ Một người chơi quay lại không thể vừa là người mời vừa là người được mời của một người chơi quay lại khác.
 [Điều kiện người chơi quay lại]
@@ -3570,7 +3570,7 @@
         <is>
           <t>1. Bạn có thể xem chi tiết về các Tacet Discord đang tấn công trong giai đoạn hiện tại, bao gồm loại và mức độ đe dọa của chúng.
 2. Chọn một hình ảnh để xem thêm thông tin về từng loại TD.
-3. TD được phân loại thành ba mức độ đe dọa: Tiêu Chuẩn, Elite và Nguy Hiểm, mỗi loại sẽ gây ra lượng sát thương khác nhau lên Energy Matrix khi tiếp cận.</t>
+3. TD được phân loại thành ba mức độ đe dọa: Tiêu Chuẩn, Tinh Anh và Nguy Hiểm, mỗi loại sẽ gây ra lượng sát thương khác nhau lên Ma Trận Năng Lượng khi tiếp cận.</t>
         </is>
       </c>
     </row>
@@ -3640,12 +3640,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Explore vùng đất mới để nhận Astrites.
+          <t>Khám phá vùng đất mới để nhận Astrites.
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 14 và hoàn thành cuộc săn đầu tiên trong Nhiệm Vụ Chính "Bằng Bàn Tay Cháy Bỏng Của Mặt Trời".
 [Quy tắc sự kiện]
-Increase Tiến Độ Khám Phá để nhận thưởng tại các mốc nhất định.
-Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được giữ lại trong 30 ngày và sẽ được gửi lại qua Mail khi bạn đăng nhập trong thời gian này.</t>
+Tăng Tiến Độ Khám Phá để nhận thưởng tại các mốc nhất định.
+Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được giữ lại trong 30 ngày và sẽ được gửi lại qua Thư khi bạn đăng nhập trong thời gian này.</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>Về sự kiện
-Theo lời mời của Iuno, bạn bước lên đỉnh Tetragon Temple để cùng cô ngắm nhìn bầu trời sao lấp lánh.
+Theo lời mời của Iuno, bạn bước lên đỉnh Đền Tetragon để cùng cô ngắm nhìn bầu trời sao lấp lánh.
 Giữa ánh sao trôi dạt nơi số phận giao hòa với các chòm sao, cô hé lộ những lời tiên tri và phước lành ẩn giấu trong các pha trăng của Septimont…
 “Cậu đến từ Huanglong phải không? Hehe, đừng lo. Tớ có thể xem trăng kiểu Huanglong cho cậu đấy.”
 Điều kiện tham gia
@@ -3795,9 +3795,9 @@
 Quy tắc
 Đăng nhập mỗi ngày trong sự kiện để nhận 1 Viên Đá Trăng Waveborn, tối đa 10 viên.
 Sử dụng Viên Đá Trăng Waveborn để giải mã Pha Trăng và nhận phần thưởng cùng hiệu ứng giới hạn thời gian.
-Mỗi hiệu ứng kéo dài 3 giờ. Decipher Pha Trăng mới trong thời gian hiệu ứng đang hoạt động sẽ thay thế hiệu ứng hiện tại.
+Mỗi hiệu ứng kéo dài 3 giờ. Giải mã Pha Trăng mới trong thời gian hiệu ứng đang hoạt động sẽ thay thế hiệu ứng hiện tại.
 Hiệu ứng chỉ có tác dụng trong thế giới mở và một số thử thách Sonoro Sphere.
-Decipher 7 Pha Trăng để nhận Avatar độc quyền “Trăng Khuyết Trăng Tròn”.</t>
+Giải mã 7 Pha Trăng để nhận Avatar độc quyền “Trăng Khuyết Trăng Tròn”.</t>
         </is>
       </c>
     </row>
@@ -3940,15 +3940,15 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>Giới Thiệu!
-Film trường Wutherium chính thức ra mắt phiên bản đặc biệt: *Resonators Combat*!
-Ghi lại những khoảnh khắc hào hùng của Resonators trong trận chiến, rồi gửi ảnh cho Fulmine và C-MOSS để nhận về vô vàn phần thưởng!
+Phim trường Wutherium chính thức ra mắt phiên bản đặc biệt: *Resonator Chiến Đấu*!
+Ghi lại những khoảnh khắc hào hùng của Resonator trong trận chiến, rồi gửi ảnh cho Fulmine và C-MOSS để nhận về vô vàn phần thưởng!
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 14 và hoàn thành Chương II Prologue "Vượt Biển Thẳm" trong Nhiệm Vụ Chính.
 [Đóng Khung Khoảnh Khắc]
 Trong sự kiện, bạn sẽ nhận được các thử thách Đóng Khung Khoảnh Khắc hàng ngày với hai chế độ: Thường và Khó. Hoàn thành chế độ Thường để mở khóa chế độ Khó của thử thách đó và chế độ Thường của thử thách tiếp theo.
-Mỗi thử thách Đóng Khung Khoảnh Khắc sẽ tập trung vào một Resonators cụ thể. Nhiệm vụ của bạn là chụp lại những khoảnh khắc nổi bật của họ trong trận chiến bằng cách hoàn thành các mục tiêu đã định. Hoàn thành nhiệm vụ sẽ mang về phần thưởng.
+Mỗi thử thách Đóng Khung Khoảnh Khắc sẽ tập trung vào một Resonator cụ thể. Nhiệm vụ của bạn là chụp lại những khoảnh khắc nổi bật của họ trong trận chiến bằng cách hoàn thành các mục tiêu đã định. Hoàn thành nhiệm vụ sẽ mang về phần thưởng.
 [Chế Độ Chậm]
-Trong thử thách Đóng Khung Khoảnh Khắc, khi Resonators được chỉ định thực hiện hành động cần thiết cho mục tiêu, Chế Độ Chậm sẽ tự động kích hoạt. Thời gian sẽ trôi chậm lại đáng kể, cho phép bạn quan sát và ghi lại những chuyển động chính xác của Resonators.
+Trong thử thách Đóng Khung Khoảnh Khắc, khi Resonator được chỉ định thực hiện hành động cần thiết cho mục tiêu, Chế Độ Chậm sẽ tự động kích hoạt. Thời gian sẽ trôi chậm lại đáng kể, cho phép bạn quan sát và ghi lại những chuyển động chính xác của Resonator.
 Trong Chế Độ Tự Do, Chế Độ Chậm sẽ không còn kích hoạt tự động. Thay vào đó, bạn có thể chủ động kích hoạt nó bằng công cụ Chế Độ Chậm bất cứ lúc nào.
 Sự kiện này không khả dụng trong Chế Độ Đồng Đội.
 Nếu có phần thưởng chưa nhận sau khi sự kiện kết thúc, chúng sẽ tự động gửi vào hộp thư của bạn khi bạn đăng nhập lại trong vòng 30 ngày.</t>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Introduction
-Waypoint là loại đánh dấu vị trí tạm thời, có chức năng tương tự Đèn Hiệu Resonance. Với tính di động cao, đây là công cụ thiết yếu khi di chuyển nơi hoang dã.
+          <t>Giới thiệu
+Điểm Dẫn Đường là loại đánh dấu vị trí tạm thời, có chức năng tương tự Đèn Hiệu Cộng Hưởng. Với tính di động cao, đây là công cụ thiết yếu khi di chuyển nơi hoang dã.
 Hướng dẫn
-1. Tiêu hao một Waypoint Mô-đun để đặt Waypoint. Waypoint Mô-đun có thể tổng hợp tại Máy Synthesis. Hãy nâng cấp Cấp Độ Pioneer Association để mở khóa công thức chế tạo Waypoint Mô-đun.
-2. Sau khi đặt, bạn có thể dịch chuyển nhanh đến tọa độ của Waypoint. Lưu ý rằng không thể đặt Waypoint tại một số vị trí nhất định.
-3. Bạn chỉ có thể đặt tối đa 10 Waypoint cùng lúc. Nếu vượt quá giới hạn, điểm đầu tiên sẽ tự động bị xóa. Bạn cũng có thể thu hồi chúng thủ công.</t>
+1. Tiêu hao một Mô-đun Điểm Dẫn Đường để đặt Điểm Dẫn Đường. Mô-đun Điểm Dẫn Đường có thể tổng hợp tại Máy Tổng Hợp. Hãy nâng cấp Cấp Độ Hiệp Hội Tiên Phong để mở khóa công thức chế tạo Mô-đun Điểm Dẫn Đường.
+2. Sau khi đặt, bạn có thể dịch chuyển nhanh đến tọa độ của Điểm Dẫn Đường. Lưu ý rằng không thể đặt Điểm Dẫn Đường tại một số vị trí nhất định.
+3. Bạn chỉ có thể đặt tối đa 10 Điểm Dẫn Đường cùng lúc. Nếu vượt quá giới hạn, điểm đầu tiên sẽ tự động bị xóa. Bạn cũng có thể thu hồi chúng thủ công.</t>
         </is>
       </c>
     </row>
@@ -4109,20 +4109,20 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>[
-Echoes Upgradees]
-Nâng cấp Echoes sẽ tăng chỉ số chính của Echoes đó. Sự cải thiện này không ngẫu nhiên.
-Nâng cấp Echoes cũng mở khóa thêm ô chỉ số phụ sau mỗi 5 cấp.
-Giới hạn cấp của Echoes phụ thuộc vào độ hiếm của nó.
+Nâng Cấp Echo]
+Nâng cấp Echo sẽ tăng chỉ số chính của Echo đó. Sự cải thiện này không ngẫu nhiên.
+Nâng cấp Echo cũng mở khóa thêm ô chỉ số phụ sau mỗi 5 cấp.
+Giới hạn cấp của Echo phụ thuộc vào độ hiếm của nó.
 [
-Tuning Echoes]
-Bằng cách điều chỉnh Echoes, bạn có thể mở khóa các chỉ số phụ ngẫu nhiên mới và khai phá tiềm năng của nó. Các chỉ số phụ được mở khóa sẽ cố định và không thể điều chỉnh lại.
-(Echoes có độ hiếm thấp nhất có thể không thể điều chỉnh do nhiễu dữ liệu.)
+Điều Chỉnh Echo]
+Bằng cách điều chỉnh Echo, bạn có thể mở khóa các chỉ số phụ ngẫu nhiên mới và khai phá tiềm năng của nó. Các chỉ số phụ được mở khóa sẽ cố định và không thể điều chỉnh lại.
+(Echo có độ hiếm thấp nhất có thể không thể điều chỉnh do nhiễu dữ liệu.)
 [
-Chỉnh Sửa Data]
+Chỉnh Sửa Dữ Liệu]
 Chỉnh sửa dữ liệu cho chỉ số chính và chỉ số phụ tuân theo quy tắc và yêu cầu vật phẩm khác nhau.
-Sử dụng Modifier để thay đổi chỉ số chính đầu tiên của Echoes đã chọn thành chỉ số được chỉ định. Điều này chỉ có thể thực hiện trên Echoes 5 sao chưa nâng cấp.
-Mỗi lần chỉnh sửa chỉ số chính sẽ tiêu tốn 1 Modifier.
-Sử dụng Bộ Chuyển Đổi để điều chỉnh các chỉ số phụ của Echoes đã chọn thành các chỉ số ngẫu nhiên, ngoại trừ các chỉ số phụ đã khóa. Điều này chỉ có thể thực hiện trên Echoes 5 sao đã điều chỉnh đầy đủ.
+Sử dụng Bộ Điều Chỉnh để thay đổi chỉ số chính đầu tiên của Echo đã chọn thành chỉ số được chỉ định. Điều này chỉ có thể thực hiện trên Echo 5 sao chưa nâng cấp.
+Mỗi lần chỉnh sửa chỉ số chính sẽ tiêu tốn 1 Bộ Điều Chỉnh.
+Sử dụng Bộ Chuyển Đổi để điều chỉnh các chỉ số phụ của Echo đã chọn thành các chỉ số ngẫu nhiên, ngoại trừ các chỉ số phụ đã khóa. Điều này chỉ có thể thực hiện trên Echo 5 sao đã điều chỉnh đầy đủ.
 Số lượng chỉ số phụ bị khóa sẽ quyết định số lượng Bộ Chuyển Đổi tiêu tốn trong mỗi lần chỉnh sửa:
 - Nếu khóa 2 chỉ số phụ trở xuống, tiêu tốn 1 Bộ Chuyển Đổi.
 - Nếu khóa 3 chỉ số phụ, tiêu tốn 2 Bộ Chuyển Đổi.
@@ -4221,29 +4221,29 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>[Cập Nhật Sự Kiện: Ảo Ảnh Tụ Hội]
-Resonators mới đã xuất hiện: Camellya, Lumi, Youhu, Shorekeeper, Encore, Verina, Calcharo, Lingyang và Mortefi.
-Tăng cấp độc quyền sẽ có trong Tiến Hóa Ý Niệm. Kích hoạt các thưởng tương ứng để nâng cấp tất cả Resonators trong Ảo Cảnh Giới.
-Explore những cảnh quan hoàn toàn mới và đối đầu với kẻ thù chưa từng thấy! Bước vào giấc mộng luôn biến đổi và khám phá những bí mật ẩn giấu!
+Resonator mới đã xuất hiện: Camellya, Lumi, Youhu, Shorekeeper, Encore, Verina, Calcharo, Lingyang và Mortefi.
+Tăng cấp độc quyền sẽ có trong Tiến Hóa Ý Niệm. Kích hoạt các thưởng tương ứng để nâng cấp tất cả Resonator trong Ảo Cảnh Giới.
+Khám phá những cảnh quan hoàn toàn mới và đối đầu với kẻ thù chưa từng thấy! Bước vào giấc mộng luôn biến đổi và khám phá những bí mật ẩn giấu!
 [Khám Phá]
-Tham gia những trận chiến hoành tráng trong Ảo Cảnh Giới và lựa chọn Resonators từ danh sách đa dạng bao gồm Rover: Spectro, Yangyang, Chixia, Baizhi, Taoqi, Jiyan, Yinlin, Jianxin, Sanhua, Jinhsi, Changli, Xiangli Yao, Zhezhi, Yuanwu, Danjin, Camellya, Lumi, Youhu, Shorekeeper, Encore, Verina, Calcharo, Lingyang và Mortefi.
-Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators có thể được giữ lại trong sự kiện, nhưng Skills Echoes và Stats sẽ không có hiệu lực.
-Sử dụng các tăng cường mạnh mẽ như Ảo Ảnh Echoes, Metaphor, Tăng Cường Character và Mảnh Phách để đánh bại những tổ hợp kẻ thù đầy thử thách.
-Thu thập Metaphor để mở khóa những kỹ năng độc đáo của Ảo Ảnh Echoes cho Resonators.
-Với độ khó cao hơn, mỗi lần chơi sẽ mang đến những thử thách và phần thưởng mới. Khi tiến xa hơn qua các cấp độ, độ khó cao hơn và phần thưởng tốt hơn sẽ xuất hiện trong Illusive Cửa hàng.
+Tham gia những trận chiến hoành tráng trong Ảo Cảnh Giới và lựa chọn Resonator từ danh sách đa dạng bao gồm Rover: Spectro, Yangyang, Chixia, Baizhi, Taoqi, Jiyan, Yinlin, Jianxin, Sanhua, Jinhsi, Changli, Xiangli Yao, Zhezhi, Yuanwu, Danjin, Camellya, Lumi, Youhu, Shorekeeper, Encore, Verina, Calcharo, Lingyang và Mortefi.
+Cấp Độ, Resonance Chain và Vũ Khí của Resonator có thể được giữ lại trong sự kiện, nhưng Kỹ Năng Echo và Chỉ Số sẽ không có hiệu lực.
+Sử dụng các tăng cường mạnh mẽ như Ảo Ảnh Echo, Ẩn Dụ, Tăng Cường Nhân Vật và Mảnh Phách để đánh bại những tổ hợp kẻ thù đầy thử thách.
+Thu thập Ẩn Dụ để mở khóa những kỹ năng độc đáo của Ảo Ảnh Echo cho Resonator.
+Với độ khó cao hơn, mỗi lần chơi sẽ mang đến những thử thách và phần thưởng mới. Khi tiến xa hơn qua các cấp độ, độ khó cao hơn và phần thưởng tốt hơn sẽ xuất hiện trong Cửa Hàng Ảo Ảnh.
 Hạng Giao Hưởng được kích hoạt trong trận chiến.
 Mọi hành động chiến đấu sẽ dần nâng cao Hạng Giao Hưởng của bạn, trong khi bị tấn công sẽ làm giảm đáng kể.
 Trong trận chiến, nếu không đạt được Hạng Giao Hưởng trong khoảng thời gian quy định, Hạng Giao Hưởng sẽ giảm dần theo thời gian.
 Hạng Giao Hưởng được chia thành 6 cấp: D, C, B, A, S và SS. Nếu đạt Hạng A trở lên, bạn sẽ nhận được những hiệu ứng đặc biệt.
-Hạng A: Sát Thương Dodge Counter tăng 100%.
-Hạng S: Sau khi thực hiện Dodge Counter, Thời Gian Cooldown của tất cả kỹ năng giảm 30%.
+Hạng A: Sát Thương Dodge Counter Tránh tăng 100%.
+Hạng S: Sau khi thực hiện Dodge Counter Tránh, Thời gian hồi Chiêu của tất cả kỹ năng giảm 30%.
 Hạng SS: Crit. Rate và Crit. DMG tăng 100%, và Hạng Giao Hưởng sẽ không giảm xuống dưới SS trong một khoảng thời gian ngắn.
 [Tiến Hóa Ý Niệm]
-Bằng cách vượt qua Ảo Cảnh Giới, bạn có thể kiếm được Memory Points quý giá. Những điểm này có thể được sử dụng trong Tiến Hóa Ý Niệm để mở khóa những tăng cường mạnh mẽ, biến Resonators trở thành một thế lực đáng gờm trong Ảo Cảnh Giới.
-[Anomaly Investigation]
+Bằng cách vượt qua Ảo Cảnh Giới, bạn có thể kiếm được Điểm Ký Ức quý giá. Những điểm này có thể được sử dụng trong Tiến Hóa Ý Niệm để mở khóa những tăng cường mạnh mẽ, biến Resonator trở thành một thế lực đáng gờm trong Ảo Cảnh Giới.
+[Điều Tra Dị Thường]
 Hoàn thành khám phá theo điều kiện chỉ định để mở khóa thành tựu và phần thưởng độc quyền.
-[Illusive Cửa hàng]
-Hoàn thành khám phá Ảo Cảnh Giới để kiếm được Illusive Specimen và đổi lấy phần thưởng độc quyền trong Illusive Cửa hàng.
-Illusive Specimen sẽ hết hạn vào cuối mỗi giai đoạn sự kiện, vì vậy đừng quên sử dụng chúng kịp thời.
+[Cửa Hàng Ảo Ảnh]
+Hoàn thành khám phá Ảo Cảnh Giới để kiếm được Mẫu Vật Ảo Ảnh và đổi lấy phần thưởng độc quyền trong Cửa Hàng Ảo Ảnh.
+Mẫu Vật Ảo Ảnh sẽ hết hạn vào cuối mỗi giai đoạn sự kiện, vì vậy đừng quên sử dụng chúng kịp thời.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Vùng Ký Ức sau khi đánh bại khối mộng ở nơi sâu nhất của cõi giới. Sử dụng Lượt Thưởng để thu thập phần thưởng của nó.
 Lượt Thưởng Tinh Thể Tàn Dư sẽ được làm mới vào thứ Hai hàng tuần lúc 04:00 sáng theo giờ máy chủ.
@@ -4327,22 +4327,22 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>[Data Bank Level]
-Dữ liệu Echoes bổ sung có thể giúp Terminal cải thiện khả năng tính toán.
-Rover có thể mở khóa Echoes mới để nhận EXP Data Bank, nâng cấp cấp độ Data Bank và nhận phần thưởng tương ứng.
-Unlock chất lượng cao hơn của Echoes hiện có cũng sẽ nhận được EXP Data Bank.
-Cấp độ Data Bank tối đa là 30.
-[Tỷ Lệ Drop Cơ Bản]
-Khi đánh bại một Discord, có khả năng giữ lại và chuyển đổi tần số còn sót lại của nó thành Echoes. Nâng cấp Data Bank của Terminal để tăng cơ hội nhận Echoes (Tỷ Lệ Drop Cơ Bản).
-[Tỷ Lệ Drop Tăng Cường]
-Đối với một số loại Discord nhất định, Terminal có thể tiêu tốn thêm năng lực tính toán để tăng cường hấp thụ Echoes và tăng cơ hội nhận Echoes. Số lần hấp thụ tăng cường có giới hạn, sau đó cần thời gian để nạp lại.
+          <t>[Cấp Độ Kho Dữ Liệu]
+Dữ liệu Echo bổ sung có thể giúp Thiết bị đầu cuối cải thiện khả năng tính toán.
+Vận Mệnh Giả có thể mở khóa Echo mới để nhận EXP Kho Dữ Liệu, nâng cấp cấp độ Kho Dữ Liệu và nhận phần thưởng tương ứng.
+Mở khóa chất lượng cao hơn của Echo hiện có cũng sẽ nhận được EXP Kho Dữ Liệu.
+Cấp độ Kho Dữ Liệu tối đa là 30.
+[Tỷ Lệ Rơi Cơ Bản]
+Khi đánh bại một Tacet Discord, có khả năng giữ lại và chuyển đổi tần số còn sót lại của nó thành Echo. Nâng cấp Kho Dữ Liệu của Thiết bị đầu cuối để tăng cơ hội nhận Echo (Tỷ Lệ Rơi Cơ Bản).
+[Tỷ Lệ Rơi Tăng Cường]
+Đối với một số loại Tacet Discord nhất định, Thiết bị đầu cuối có thể tiêu tốn thêm năng lực tính toán để tăng cường hấp thụ Echo và tăng cơ hội nhận Echo. Số lần hấp thụ tăng cường có giới hạn, sau đó cần thời gian để nạp lại.
 Số lần hấp thụ tăng cường của các loại khác nhau được tính riêng.
-*Cooldown chiêu đặt lại vào 04:00 sáng thứ Hai hàng tuần theo giờ máy chủ.
-[Rarity Drop Cao Nhất]
-Nâng cấp Data Bank của Terminal để tăng cơ hội nhận Echoes có Rarity cao hơn.
+*Thời gian hồi chiêu đặt lại vào 04:00 sáng thứ Hai hàng tuần theo giờ máy chủ.
+[Độ Hiếm Rơi Cao Nhất]
+Nâng cấp Kho Dữ Liệu của Thiết bị đầu cuối để tăng cơ hội nhận Echo có Độ Hiếm cao hơn.
 [Giới Hạn COST]
-Tổng COST của Echoes trang bị không được vượt quá Giới Hạn COST hiện tại.
-Nâng cấp Data Bank của Terminal để tăng Giới Hạn COST và trang bị Echoes mạnh hơn.</t>
+Tổng COST của Echo trang bị không được vượt quá Giới Hạn COST hiện tại.
+Nâng cấp Kho Dữ Liệu của Thiết bị đầu cuối để tăng Giới Hạn COST và trang bị Echo mạnh hơn.</t>
         </is>
       </c>
     </row>
@@ -4417,16 +4417,16 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>[
-Cơ Chế Basic]
+Cơ Chế Cơ Bản]
 Trò chơi sử dụng bộ bài 16 lá. Mỗi người chơi bắt đầu với 8 lá trên tay. Người chơi tung đồng xu để quyết định lượt đi trong mỗi vòng.
 Lượt của người chơi: rút 1 lá từ tay đối thủ. Nếu có hai lá giống nhau trên tay, có thể đánh ra thành đôi.
 Trò chơi kết thúc khi đạt một trong các điều kiện thắng.
 [Điều Kiện Thắng]
-1. Mỗi người chơi bắt đầu với 2 HP. Draw phải Lá Không Vương Miện sẽ mất 1 HP. Nếu HP giảm về 0, người chơi thua.
+1. Mỗi người chơi bắt đầu với 2 HP. Rút phải Lá Không Vương Miện sẽ mất 1 HP. Nếu HP giảm về 0, người chơi thua.
 2. Nếu một người chơi đánh hết bài trên tay trong khi đối thủ vẫn còn giữ Lá Không Vương Miện, người chơi đó thắng.
-[Details Lá Bài]
+[Chi Tiết Lá Bài]
 1. Lá Hoang Dã: Đầu mỗi lượt, Lá Hoang Dã ngẫu nhiên biến thành một lá số khác trên tay người chơi. Không thể biến thành Lá Không Vương Miện, lá đã đánh ra hoặc lặp lại biến hình ở các vòng trước. Lá Hoang Dã có thể kết đôi như lá thường.
-2. Lá Không Vương Miện: Chỉ có một lá duy nhất trong bộ bài. Draw phải lá này sẽ mất 1 HP (trong tổng 2 HP). Người chơi đầu tiên mất 2 HP sẽ thua cuộc.</t>
+2. Lá Không Vương Miện: Chỉ có một lá duy nhất trong bộ bài. Rút phải lá này sẽ mất 1 HP (trong tổng 2 HP). Người chơi đầu tiên mất 2 HP sẽ thua cuộc.</t>
         </is>
       </c>
     </row>
@@ -4562,9 +4562,9 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>Nâng Cấp Liên Minh
-1. Hoàn thành &lt;color=#c49e55&gt;various quests, Sổ tay daily activity rewards&lt;/color&gt; để thu thập Union EXP.
-2. Sử dụng Waveplate để thách đấu &lt;color=#c49e55&gt;various dungeons, Tacet Fields, bosses&lt;/color&gt; và thu thập Union EXP.
-3. Khi khám phá thế giới mở, &lt;color=#c49e55&gt;open Supply Chests&lt;/color&gt; để nhận Union EXP.</t>
+1. Hoàn thành &lt;color=#c49e55&gt;nhiệm vụ đa dạng, nhận thưởng hoạt động hàng ngày từ Sổ Tay Hướng Dẫn&lt;/color&gt; để thu thập Kinh Nghiệm Liên Minh.
+2. Sử dụng Waveplate để thách đấu &lt;color=#c49e55&gt;các dungeon, Tổ Tacet, trùm&lt;/color&gt; và thu thập Kinh Nghiệm Liên Minh.
+3. Khi khám phá thế giới mở, &lt;color=#c49e55&gt;mở Rương Vật Tư&lt;/color&gt; để nhận Kinh Nghiệm Liên Minh.</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>Về sự kiện
-Một lễ hội bất tận diễn ra bên trong một Quả Cầu Sonoro vô danh. Dù lễ hội có vẻ vĩnh cửu, nhưng một ngày nào đó, Sonoro cũng sẽ phai nhạt. Để mang đến cho nó một màn kết rực rỡ, Lollo Logistics tổ chức một bữa tiệc đặc biệt, một lời mời gọi cuối cùng để mọi người cùng tụ họp, tỏa sáng và chia sẻ một lễ kỷ niệm vui vẻ cuối cùng.</t>
+Một lễ hội bất tận diễn ra bên trong một Sonoro Sphere vô danh. Dù lễ hội có vẻ vĩnh cửu, nhưng một ngày nào đó, Sonoro cũng sẽ phai nhạt. Để mang đến cho nó một màn kết rực rỡ, Lollo Logistics tổ chức một bữa tiệc đặc biệt, một lời mời gọi cuối cùng để mọi người cùng tụ họp, tỏa sáng và chia sẻ một lễ kỷ niệm vui vẻ cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -4703,8 +4703,8 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1. Cards Wild Card: Vào đầu mỗi lượt, Wild Card sẽ ngẫu nhiên biến thành một thẻ số khác trong tay người chơi. Nó không thể biến thành Crownless Card, thẻ đã được đánh ra, hoặc lặp lại biến hình ở các vòng trước. Wild Card có thể kết hợp thành đôi như các thẻ thông thường.
-2. Crownless Card: Bộ bài chỉ có duy nhất một Crownless Card. Rút phải thẻ này sẽ khiến người chơi mất 1 HP (trong tổng số 2 HP). Người chơi đầu tiên mất 2 HP sẽ thua cuộc.</t>
+          <t>1. Thẻ Wild Card: Vào đầu mỗi lượt, Wild Card sẽ ngẫu nhiên biến thành một thẻ số khác trong tay người chơi. Nó không thể biến thành Thẻ Crownless, thẻ đã được đánh ra, hoặc lặp lại biến hình ở các vòng trước. Wild Card có thể kết hợp thành đôi như các thẻ thông thường.
+2. Thẻ Crownless: Bộ bài chỉ có duy nhất một Thẻ Crownless. Rút phải thẻ này sẽ khiến người chơi mất 1 HP (trong tổng số 2 HP). Người chơi đầu tiên mất 2 HP sẽ thua cuộc.</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Increase cấp &lt;color=yellow&gt;Forte&lt;/color&gt; để nhận EXP nâng cấp Terminal.</t>
+          <t>Tăng cấp &lt;color=yellow&gt;Forte&lt;/color&gt; để nhận EXP nâng cấp Thiết bị đầu cuối.</t>
         </is>
       </c>
     </row>
@@ -4838,11 +4838,11 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>[Tuning Meme]
-Trước khi khám phá Echo Ảo, bạn có thể chọn Tuning Meme để điều chỉnh độ khó của chuyến thám hiểm và tỷ lệ phần thưởng (Tuning Meme chỉ khả dụng ở Độ Khó IV, V và VI).
-Tuning Meme ảnh hưởng đến trải nghiệm chiến đấu của Resonators và khả năng của kẻ địch trong chuyến thám hiểm Echo Ảo sắp tới. Tỷ lệ phần thưởng sẽ được áp dụng cho các Illusive Specimen và Memory Points nhận được sau khi hoàn thành chuyến thám hiểm.
+          <t>[Điều Chỉnh Meme]
+Trước khi khám phá Tổ Tacet Ảo, bạn có thể chọn Điều Chỉnh Meme để điều chỉnh độ khó của chuyến thám hiểm và tỷ lệ phần thưởng (Điều Chỉnh Meme chỉ khả dụng ở Độ Khó IV, V và VI).
+Điều Chỉnh Meme ảnh hưởng đến trải nghiệm chiến đấu của Resonator và khả năng của kẻ địch trong chuyến thám hiểm Tổ Tacet Ảo sắp tới. Tỷ lệ phần thưởng sẽ được áp dụng cho các Mẫu Vật Ảo và Điểm Ký Ức nhận được sau khi hoàn thành chuyến thám hiểm.
 Meme Ảo Giác: Giảm độ khó tổng thể và tỷ lệ phần thưởng của chuyến thám hiểm sắp tới.
-Meme Nightmare: Increase độ khó tổng thể và tỷ lệ phần thưởng của chuyến thám hiểm sắp tới.</t>
+Meme Ác Mộng: Tăng độ khó tổng thể và tỷ lệ phần thưởng của chuyến thám hiểm sắp tới.</t>
         </is>
       </c>
     </row>
@@ -4909,9 +4909,9 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Taoqi's Special Ability: Defensive Counterattack&lt;/color&gt;
-Khi Taoqi sử dụng [Heavy Attack], nếu hành động bị gián đoạn, cô có thể tiêu hao 1 điểm Thương Năng để tung ra [Counterattack Black Tortoise] bằng [Basic Attack], kích hoạt [Black Tortoise U Minh] làm chậm phạm vi và hồi HP cho cả đội.
-[Black Tortoise U Minh] cũng có thể được kích hoạt thông qua [Chuỗi Basic Attack], [Intro Skill], [Đòn Lao Xuống] và [Resonance Liberation].</t>
+          <t>&lt;color=yellow&gt;Kỹ năng đặc biệt của Taoqi: Phản công phòng thủ&lt;/color&gt;
+Khi Taoqi sử dụng [Đòn Heavy Attack], nếu hành động bị gián đoạn, cô có thể tiêu hao 1 điểm Thương Năng để tung ra [Phản công Huyền Vũ] bằng [Đòn Basic Attack], kích hoạt [Huyền Vũ U Minh] làm chậm phạm vi và hồi HP cho cả đội.
+[Huyền Vũ U Minh] cũng có thể được kích hoạt thông qua [Chuỗi Đòn Basic Attack], [Kỹ Năng Khởi Động], [Đòn Lao Xuống] và [Resonance Liberation].</t>
         </is>
       </c>
     </row>
@@ -4977,8 +4977,8 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>&lt;color=yellow&gt;Đội-up Guide:&lt;/color&gt;
-Trigger hiệu ứng hồi máu thông qua phản công phòng thủ của Taoqi, đồng thời làm chậm kẻ địch để tạo không gian tấn công cho cả đội.</t>
+          <t>&lt;color=yellow&gt;Hướng dẫn phối hợp: &lt;/color&gt;
+Kích hoạt hiệu ứng hồi máu thông qua phản công phòng thủ của Taoqi, đồng thời làm chậm kẻ địch để tạo không gian tấn công cho cả đội.</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
           <t>[Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 14.
 [Quy Tắc Sự Kiện]
-Trong sự kiện, bạn có thể tiêu thụ Waveplate để nhận phần thưởng gấp đôi sau khi hoàn thành Challenges Mô Phỏng.
+Trong sự kiện, bạn có thể tiêu thụ Waveplate để nhận phần thưởng gấp đôi sau khi hoàn thành Thử Thách Mô Phỏng.
 Hãy xem trang Huấn Luyện Chuyên Sâu để biết số lần còn lại có thể nhận phần thưởng gấp đôi.</t>
         </is>
       </c>
@@ -5123,9 +5123,9 @@
         <is>
           <t>[Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 14.
-[Event Rules]
-Trong sự kiện, bạn có thể tiêu thụ Waveplate để nhận phần thưởng gấp đôi sau khi hoàn thành Challenges Mô Phỏng và Challenges Rèn Luyện.
-Số lần nhận phần thưởng gấp đôi được chia sẻ giữa Challenges Mô Phỏng và Challenges Rèn Luyện.
+[Quy Tắc Sự Kiện]
+Trong sự kiện, bạn có thể tiêu thụ Waveplate để nhận phần thưởng gấp đôi sau khi hoàn thành Thử Thách Mô Phỏng và Thử Thách Rèn Luyện.
+Số lần nhận phần thưởng gấp đôi được chia sẻ giữa Thử Thách Mô Phỏng và Thử Thách Rèn Luyện.
 Hãy xem trang Bountiful Crescendo để biết số lần còn lại có thể nhận phần thưởng gấp đôi.</t>
         </is>
       </c>
@@ -5197,7 +5197,7 @@
         <is>
           <t>["Điều Kiện Tham Gia"]
 Đạt Cấp Liên Minh 19.
-Event Rules
+Quy Tắc Sự Kiện
 Trong sự kiện, bạn có thể tiêu thụ Waveplates để nhận phần thưởng gấp đôi sau khi hoàn thành Tacet Suppression.
 Hãy xem trang Chord Cleansing để biết số lần còn lại có thể nhận thưởng gấp đôi.</t>
         </is>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Sau khi Dodge thành công, nhấn {0} để kích hoạt &lt;color=#ffd12f&gt;Dodge Counter&lt;/color&gt;.</t>
+          <t>Sau khi né thành công, nhấn {0} để kích hoạt &lt;color=#ffd12f&gt;Dodge Counter Tránh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Sau khi Dodge phản công thành công, nhấn {0} để kích hoạt &lt;color=#ffd12f&gt;Special Chain Attack&lt;/color&gt;.</t>
+          <t>Sau khi né phản công thành công, nhấn {0} để kích hoạt &lt;color=#ffd12f&gt;Đòn Liên Kết Đặc Biệt&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Echoes&lt;/color&gt; là nguồn sức mạnh quan trọng của Resonators. Các ngươi có thể sử dụng &lt;color=#ffd12f&gt;Echo Skill&lt;/color&gt; của Dư Âm được trang bị ở vị trí đầu tiên.</t>
+          <t>&lt;color=#ffd12f&gt;Dư Âm&lt;/color&gt; là nguồn sức mạnh quan trọng của Resonator. Các ngươi có thể sử dụng &lt;color=#ffd12f&gt;Kỹ Năng Dư Âm&lt;/color&gt; của Dư Âm được trang bị ở vị trí đầu tiên.</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Nâng cấp Ngân hàng Dữ liệu để tăng &lt;color=#ffd12f&gt;Max STA&lt;/color&gt;. Explore thế giới và hấp thụ những Echoes khác nhau!</t>
+          <t>Nâng cấp Ngân hàng Dữ liệu để tăng &lt;color=#ffd12f&gt;STA tối đa&lt;/color&gt;. Khám phá thế giới và hấp thụ những Echo khác nhau!</t>
         </is>
       </c>
     </row>
@@ -5525,8 +5525,8 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, hãy chuyển Resonator để kích hoạt &lt;color=#ffd12f&gt;Outro Skill&lt;/color&gt; của Resonator hiện tại, đồng thời tiêu hao toàn bộ Concerto Energy để kích hoạt &lt;color=#ffd12f&gt;Intro Skill&lt;/color&gt; của Resonator mới.
-Mỗi Resonator đều có &lt;color=#ffd12f&gt;Outro Skill&lt;/color&gt; và &lt;color=#ffd12f&gt;Intro Skill&lt;/color&gt; riêng biệt.</t>
+          <t>Khi Concerto Energy đầy, hãy chuyển Resonator để kích hoạt &lt;color=#ffd12f&gt;Kỹ Năng Xuất Chiến&lt;/color&gt; của Resonator hiện tại, đồng thời tiêu hao toàn bộ Concerto Energy để kích hoạt &lt;color=#ffd12f&gt;Kỹ Năng Nhập Chiến&lt;/color&gt; của Resonator mới.
+Mỗi Resonator đều có &lt;color=#ffd12f&gt;Kỹ Năng Xuất Chiến&lt;/color&gt; và &lt;color=#ffd12f&gt;Kỹ Năng Nhập Chiến&lt;/color&gt; riêng biệt.</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Một số &lt;color=#ffd12f&gt;Fissured Ledge&lt;/color&gt; bị xói mòn bởi Hiện Tượng Waveworn không thể phá hủy bằng phương pháp thông thường. Cậu có thể dùng Levitator để lấy &lt;color=#ffd12f&gt;Tacetite Fulminate&lt;/color&gt; gần đó và &lt;color=#ffd12f&gt;throw&lt;/color&gt; để kích hoạt &lt;color=#ffd12f&gt;explosion&lt;/color&gt; phá hủy Fissured Ledge.</t>
+          <t>Một số &lt;color=#ffd12f&gt;Vách Đá Nứt&lt;/color&gt; bị xói mòn bởi Hiện Tượng Waveworn không thể phá hủy bằng phương pháp thông thường. Cậu có thể dùng Levitator để lấy &lt;color=#ffd12f&gt;Tacetite Fulminate&lt;/color&gt; gần đó và &lt;color=#ffd12f&gt;ném&lt;/color&gt; để kích hoạt &lt;color=#ffd12f&gt;vụ nổ&lt;/color&gt; phá hủy Vách Đá Nứt.</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Effect Erosion Gió</t>
+          <t>Hiệu Ứng Aero Erosion</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Hiệu ứng Glacio Chafe</t>
+          <t>Hiệu Ứng Xước Băng Giá</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Effect Bùng Nổ Fusion</t>
+          <t>Hiệu Ứng Bùng Nổ Hợp Nhất</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Hiệu ứng Spectro Frazzle</t>
+          <t>Hiệu Ứng Rối Loạn Spectro</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Hiệu ứng Havoc Bane</t>
+          <t>Hiệu Ứng Hiểm Họa Havoc</t>
         </is>
       </c>
     </row>
@@ -5982,8 +5982,8 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Một số đòn tấn công &lt;color=Wind&gt;Aero&lt;/color&gt; sẽ gây hiệu ứng &lt;color=#ffd12f&gt;"Aero Erosion Effect"&lt;/color&gt; có thể chồng chất lên mục tiêu.
-Trong thời gian hiệu ứng &lt;color=#ffd12f&gt;"Aero Erosion Effect"&lt;/color&gt; còn tác dụng, nó sẽ gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; theo chu kỳ lên mục tiêu.</t>
+          <t>Một số đòn tấn công &lt;color=Wind&gt;Aero&lt;/color&gt; sẽ gây hiệu ứng &lt;color=#ffd12f&gt;"Aero Erosion"&lt;/color&gt; có thể chồng chất lên mục tiêu.
+Trong thời gian hiệu ứng &lt;color=#ffd12f&gt;"Aero Erosion"&lt;/color&gt; còn tác dụng, nó sẽ gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; theo chu kỳ lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -6049,8 +6049,8 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Sát thương của &lt;color=#ffd12f&gt;"Aero Erosion Effect"&lt;/color&gt; tăng theo số lượt tích lũy.
-Dodge các đòn tấn công để tránh tích lũy &lt;color=#ffd12f&gt;"Aero Erosion Effect"&lt;/color&gt;.</t>
+          <t>Sát thương của &lt;color=#ffd12f&gt;"Hiệu Ứng Aero Erosion"&lt;/color&gt; tăng theo số lượt tích lũy.
+Né tránh các đòn tấn công để tránh tích lũy &lt;color=#ffd12f&gt;"Hiệu Ứng Aero Erosion"&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6118,8 +6118,8 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>Một số đòn tấn công &lt;color=Thunder&gt;Electro&lt;/color&gt; sẽ gây hiệu ứng &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt; có thể chồng chất lên mục tiêu.
-Trong thời gian hiệu ứng &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt; còn tác dụng, nó sẽ gây &lt;color=Thunder&gt;Electro DMG&lt;/color&gt; theo chu kỳ lên mục tiêu. Mỗi lần gây sát thương, mục tiêu sẽ mất đi một nửa số chồng chất hiệu ứng.
-&lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt; có thể chồng chất tối đa 10 lần theo mặc định. Số lượng chồng chất càng cao, sát thương gây ra càng lớn.</t>
+Trong thời gian hiệu ứng &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt; còn tác dụng, nó sẽ gây &lt;color=Thunder&gt;Sát Thương Electro&lt;/color&gt; theo chu kỳ lên mục tiêu. Mỗi lần gây DMG, mục tiêu sẽ mất đi một nửa số chồng chất hiệu ứng.
+&lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt; có thể chồng chất tối đa 10 lần theo mặc định. Số lượng chồng chất càng cao, DMG gây ra càng lớn.</t>
         </is>
       </c>
     </row>
@@ -6188,9 +6188,9 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>Khi đạt tối đa tầng &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt;, bất kỳ tầng mới nào bị ảnh hưởng sẽ chuyển thành &lt;color=#ffd12f&gt;Electro Rage&lt;/color&gt; có thể tích lũy.
-&lt;color=#ffd12f&gt;Electro Rage&lt;/color&gt; làm tăng sát thương gây ra bởi &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt; kích hoạt tiếp theo. &lt;color=#ffd12f&gt;Electro Rage&lt;/color&gt; sẽ bị loại bỏ sau khi kích hoạt.
-&lt;color=#ffd12f&gt;Electro Rage&lt;/color&gt; có thể tích lũy tối đa 10 tầng theo mặc định. Càng nhiều tầng, &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt; gây ra càng nhiều sát thương.
-Hãy Dodge đòn cẩn thận để tránh tích lũy hiệu ứng &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt;.</t>
+&lt;color=#ffd12f&gt;Electro Rage&lt;/color&gt; làm tăng DMG gây ra bởi &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt; kích hoạt tiếp theo. &lt;color=#ffd12f&gt;Electro Rage&lt;/color&gt; sẽ bị loại bỏ sau khi kích hoạt.
+&lt;color=#ffd12f&gt;Electro Rage&lt;/color&gt; có thể tích lũy tối đa 10 tầng theo mặc định. Càng nhiều tầng, &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt; gây ra càng nhiều DMG.
+Hãy né đòn cẩn thận để tránh tích lũy hiệu ứng &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6259,9 +6259,9 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>Một số đòn tấn công &lt;color=Ice&gt;Glacio&lt;/color&gt; sẽ gây hiệu ứng &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; có thể chồng chất lên mục tiêu.
-Khi bị &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt;, mục tiêu sẽ chịu &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.
-&lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; có thể chồng chất tối đa 10 lần theo mặc định. Số lượng chồng chất càng cao, sát thương gây ra càng lớn.
-Mỗi lớp hiệu ứng &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; sẽ làm giảm Movement Speed của mục tiêu.</t>
+Khi bị &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt;, mục tiêu sẽ chịu &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.
+&lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; có thể chồng chất tối đa 10 lần theo mặc định. Số lượng chồng chất càng cao, DMG gây ra càng lớn.
+Mỗi lớp hiệu ứng &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; sẽ làm giảm Tốc Độ Di Chuyển của mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -6327,8 +6327,8 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; đạt tối đa, mục tiêu sẽ bị &lt;color=#ffd12f&gt;frozen&lt;/color&gt;, và tất cả các tầng &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; sẽ bị loại bỏ. Cố gắng vùng vẫy để thoát khỏi trạng thái &lt;color=#ffd12f&gt;frozen&lt;/color&gt; nhanh hơn.
-Hãy Dodge đòn cẩn thận để tránh tích lũy hiệu ứng &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt;.</t>
+          <t>Khi &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; đạt tối đa, mục tiêu sẽ bị &lt;color=#ffd12f&gt;đóng băng&lt;/color&gt;, và tất cả các tầng &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; sẽ bị loại bỏ. Cố gắng vùng vẫy để thoát khỏi trạng thái &lt;color=#ffd12f&gt;đóng băng&lt;/color&gt; nhanh hơn.
+Hãy né đòn cẩn thận để tránh tích lũy hiệu ứng &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6460,9 +6460,9 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#ffd12f&gt;Fusion Burst&lt;/color&gt; đạt tối đa, tất cả các tầng sẽ bị loại bỏ để kích hoạt một &lt;color=#ffd12f&gt;explosion&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; xung quanh mục tiêu.
-&lt;color=#ffd12f&gt;Fusion Burst&lt;/color&gt; có thể tích lũy tối đa 10 tầng theo mặc định. Càng nhiều tầng, sát thương gây ra càng lớn.
-Hãy Dodge đòn cẩn thận để tránh tích lũy hiệu ứng &lt;color=#ffd12f&gt;Fusion Burst&lt;/color&gt;.</t>
+          <t>Khi &lt;color=#ffd12f&gt;Fusion Burst&lt;/color&gt; đạt tối đa, tất cả các tầng sẽ bị loại bỏ để kích hoạt một &lt;color=#ffd12f&gt;vụ nổ&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; xung quanh mục tiêu.
+&lt;color=#ffd12f&gt;Fusion Burst&lt;/color&gt; có thể tích lũy tối đa 10 tầng theo mặc định. Càng nhiều tầng, DMG gây ra càng lớn.
+Hãy né đòn cẩn thận để tránh tích lũy hiệu ứng &lt;color=#ffd12f&gt;Fusion Burst&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6528,8 +6528,8 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Một số đòn tấn công &lt;color=Light&gt;Spectro&lt;/color&gt; sẽ gây hiệu ứng &lt;color=#ffd12f&gt;"Spectro Frazzle Effect"&lt;/color&gt; có thể chồng chất lên mục tiêu.
-Trong thời gian hiệu ứng &lt;color=#ffd12f&gt;"Spectro Frazzle Effect"&lt;/color&gt; còn tác dụng, số lượng chồng chất sẽ giảm dần theo thời gian, mỗi lần giảm sẽ gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt; lên mục tiêu.</t>
+          <t>Một số đòn tấn công &lt;color=Light&gt;Spectro&lt;/color&gt; sẽ gây hiệu ứng &lt;color=#ffd12f&gt;"Spectro Frazzle"&lt;/color&gt; có thể chồng chất lên mục tiêu.
+Trong thời gian hiệu ứng &lt;color=#ffd12f&gt;"Spectro Frazzle"&lt;/color&gt; còn tác dụng, số lượng chồng chất sẽ giảm dần theo thời gian, mỗi lần giảm sẽ gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt; lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -6595,8 +6595,8 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Việc tích lũy &lt;color=#ffd12f&gt;"Spectro Frazzle Effect"&lt;/color&gt; sẽ làm tăng đáng kể sát thương gây ra.
-Hãy Dodge các đòn tấn công để tránh tích lũy &lt;color=#ffd12f&gt;"Spectro Frazzle Effect"&lt;/color&gt; và giảm thiểu sát thương nhận vào.</t>
+          <t>Việc tích lũy &lt;color=#ffd12f&gt;"Hiệu Ứng Rối Loạn Spectro"&lt;/color&gt; sẽ làm tăng đáng kể DMG gây ra.
+Hãy né tránh các đòn tấn công để tránh tích lũy &lt;color=#ffd12f&gt;"Hiệu Ứng Rối Loạn Spectro"&lt;/color&gt; và giảm thiểu DMG nhận vào.</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>&lt;color=#ffd12f&gt;Havoc Bane&lt;/color&gt; có thể tích lũy tối đa 3 tầng, mỗi tầng giảm 2% Phòng Ngự của mục tiêu.
-Hãy Dodge đòn cẩn thận để tránh bị ảnh hưởng bởi hiệu ứng &lt;color=#ffd12f&gt;Havoc Bane&lt;/color&gt;.</t>
+Hãy né đòn cẩn thận để tránh bị ảnh hưởng bởi hiệu ứng &lt;color=#ffd12f&gt;Havoc Bane&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6795,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Khôi Phục Bích Họa</t>
+          <t>Khôi phục Bích Họa</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Sau khi mở khóa Công cụ, bạn có thể dùng Bộ Nâng để khôi phục bức tranh tường chưa hoàn thiện bên trái về hoa văn ban đầu.</t>
+          <t>Sau khi mở khóa Tiện Ích, bạn có thể dùng Bộ Nâng để khôi phục bức tranh tường chưa hoàn thiện bên trái về hoa văn ban đầu.</t>
         </is>
       </c>
     </row>
@@ -6926,8 +6926,8 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Biến thành Mourning Aix để bắt đầu cuộc truy đuổi trên không.
-Khi vòng ngắm xuất hiện, hãy dùng Basic Attack để tấn công kẻ địch.</t>
+          <t>Biến hình thành Mourning Aix để bắt đầu cuộc truy đuổi trên không.
+Khi vòng ngắm xuất hiện, hãy dùng Đòn Cơ Bản để tấn công kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Cậu có thể tích lũy năng lượng bằng cách tấn công kẻ địch bằng Basic Attack. Khi năng lượng đầy, chiêu thức sẽ sẵn sàng.</t>
+          <t>Cậu có thể tích lũy năng lượng bằng cách tấn công kẻ địch bằng Đòn Cơ Bản. Khi năng lượng đầy, chiêu thức sẽ sẵn sàng.</t>
         </is>
       </c>
     </row>
@@ -7123,8 +7123,8 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Skills Phản Đòn Echo là khả năng đặc biệt của một số Echo, có thể phá vỡ đòn tấn công của kẻ địch khi chúng tung ra &lt;color=HighlightB&gt;Special Attack&lt;/color&gt; và &lt;color=HighlightB&gt;Immoblize&lt;/color&gt; chúng trong thời gian ngắn.
-Trước khi kẻ địch sử dụng Đòn Special, bạn sẽ thấy &lt;color=HighlightB&gt;Red Warning Prompt&lt;/color&gt;. Hãy dùng Skills Phản Đòn Echo để chặn đứng chúng.</t>
+          <t>Kỹ Năng Phản Đòn Tiếng Vọng là khả năng đặc biệt của một số Tiếng Vọng, có thể phá vỡ đòn tấn công của kẻ địch khi chúng tung ra &lt;color=HighlightB&gt;Đòn Đặc Biệt&lt;/color&gt; và &lt;color=HighlightB&gt;Hóa Giáp&lt;/color&gt; chúng trong thời gian ngắn.
+Trước khi kẻ địch sử dụng Đòn Đặc Biệt, bạn sẽ thấy &lt;color=HighlightB&gt;Cảnh Báo Đỏ&lt;/color&gt;. Hãy dùng Kỹ Năng Phản Đòn Tiếng Vọng để chặn đứng chúng.</t>
         </is>
       </c>
     </row>
@@ -7190,8 +7190,8 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Sử dụng &lt;color=highlight&gt;Resonance Skill&lt;/color&gt; sẽ giảm Cooldown chiêu của Resonance Liberation và hồi phục Resonance Energy.
-Sử dụng &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; sẽ giảm Cooldown chiêu Resonance Skill của tất cả thành viên trong đội, tăng Crit. Rate Resonance Skill cho họ trong 3 giây và gia tăng Crit. DMG Resonance Skill. Hiệu ứng này có thể chồng chất.</t>
+          <t>Sử dụng &lt;color=highlight&gt;Resonance Skill&lt;/color&gt; sẽ giảm Thời gian hồi chiêu của Resonance Liberation và hồi phục Resonance Energy.
+Sử dụng &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; sẽ giảm Thời gian hồi chiêu Resonance Skill của tất cả thành viên trong đội, tăng Crit. Rate Resonance Skill cho họ trong 3 giây và gia tăng Crit. DMG Resonance Skill. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -7257,8 +7257,8 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Khi Resonator đang hoạt động &lt;color=highlight&gt;in trên không&lt;/color&gt;, Crit. Rate và Crit. DMG của họ sẽ tăng lên mỗi giây. Mỗi khi Đòn Attack trên không trúng mục tiêu, sẽ kích hoạt một đòn tấn công bổ sung gây Sát Thương Resonance Liberation.
-Đòn tấn công bổ sung làm tăng &lt;color=highlight&gt;Resonance Liberation DMG&lt;/color&gt; của Resonator. Hiệu ứng này có thể chồng chất.</t>
+          <t>Khi Resonator đang hoạt động &lt;color=highlight&gt;ở trên không&lt;/color&gt;, Crit. Rate và Crit. DMG của họ sẽ tăng lên mỗi giây. Mỗi khi Đòn Tấn Công trên không trúng mục tiêu, sẽ kích hoạt một đòn tấn công bổ sung gây Sát Thương Resonance Liberation.
+Đòn tấn công bổ sung làm tăng &lt;color=highlight&gt;Sát Thương Resonance Liberation&lt;/color&gt; của Resonator. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -7325,9 +7325,9 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Khi &lt;color=highlight&gt;Coordinated Attack&lt;/color&gt; trúng mục tiêu, tăng Sát Thương cho Resonators không tham chiến. Hiệu ứng này có thể chồng chất.
-Khi &lt;color=highlight&gt;Coordinated Attack&lt;/color&gt; trúng mục tiêu, tất cả thành viên trong đội nhận thêm Resonance Energy và Concerto Energy.
-Khi &lt;color=highlight&gt;Intro Skill&lt;/color&gt; trúng mục tiêu, tăng Crit. Rate và Crit. DMG cho tất cả thành viên trong đội trong 8 giây.</t>
+          <t>Khi &lt;color=highlight&gt;Đòn Phối Hợp&lt;/color&gt; trúng mục tiêu, tăng Sát Thương cho Resonator không tham chiến. Hiệu ứng này có thể chồng chất.
+Khi &lt;color=highlight&gt;Đòn Phối Hợp&lt;/color&gt; trúng mục tiêu, tất cả thành viên trong đội nhận thêm Resonance Energy và Năng Lượng Giao Hưởng.
+Khi &lt;color=highlight&gt;Kỹ Năng Khởi Động&lt;/color&gt; trúng mục tiêu, tăng Crit. Rate và Crit. DMG cho tất cả thành viên trong đội trong 8 giây.</t>
         </is>
       </c>
     </row>
@@ -7394,8 +7394,8 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Giảm Cooldown chiêu &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt;.
-Tiêu diệt kẻ địch sẽ hồi phục thêm Resonance Energy và Concerto Energy.
+          <t>Giảm Thời gian hồi chiêu &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt;.
+Tiêu diệt kẻ địch sẽ hồi phục thêm Resonance Energy và Năng Lượng Giao Hưởng.
 Tiêu diệt kẻ địch cũng tăng Crit. Rate và Crit. DMG của &lt;color=highlight&gt;Resonance Liberation&lt;/color&gt; cho tất cả thành viên trong đội. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
@@ -7462,8 +7462,8 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Giảm Cooldown chiêu &lt;color=highlight&gt;Echo Skill&lt;/color&gt;. Khi bắt đầu và kết thúc &lt;color=highlight&gt;Echo Skill&lt;/color&gt;, tung một Đường Kiếm Lưỡi Liềm bên cạnh Echo đang kích hoạt, gây sát thương Kỹ Năng Echo lên kẻ địch.
-Tiêu diệt kẻ địch sẽ tăng Sát Thương Attack và Sát Thương Kỹ Năng Echo cho tất cả thành viên trong đội.</t>
+          <t>Giảm Thời gian hồi chiêu &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt;. Khi bắt đầu và kết thúc &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt;, tung một Đường Kiếm Lưỡi Liềm bên cạnh Echo đang kích hoạt, gây DMG Kỹ Năng Echo lên kẻ địch.
+Tiêu diệt kẻ địch sẽ tăng Sát Thương Tấn Công và Sát Thương Kỹ Năng Echo cho tất cả thành viên trong đội.</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Giảm Cooldown chiêu &lt;color=highlight&gt;Echo Skill&lt;/color&gt;. &lt;color=highlight&gt;Echo Skill&lt;/color&gt; gây hiệu ứng Trì Trệ lên kẻ địch và đánh dấu chúng. Mỗi kẻ địch bị đánh dấu sẽ chịu thêm sát thương.</t>
+          <t>Giảm Thời gian hồi chiêu &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt;. &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt; gây hiệu ứng Trì Trệ lên kẻ địch và đánh dấu chúng. Mỗi kẻ địch bị đánh dấu sẽ chịu thêm DMG.</t>
         </is>
       </c>
     </row>
@@ -7594,8 +7594,8 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Increase Crit. Rate và Crit. DMG của Resonance Skill trong một khoảng thời gian sau khi sử dụng &lt;color=highlight&gt;Echo Skill&lt;/color&gt;. Hiệu ứng này có thể chồng chất.
-Đánh bại kẻ địch bằng &lt;color=highlight&gt;Resonance Skill&lt;/color&gt; sẽ giảm Cooldown chiêu Kỹ Năng Echo và Resonance Skill của Resonator, đồng thời phục hồi một lượng Concerto Energy nhất định.</t>
+          <t>Tăng Crit. Rate và Crit. DMG của Resonance Skill trong một khoảng thời gian sau khi sử dụng &lt;color=highlight&gt;Kỹ Năng Echo&lt;/color&gt;. Hiệu ứng này có thể chồng chất.
+Đánh bại kẻ địch bằng &lt;color=highlight&gt;Resonance Skill&lt;/color&gt; sẽ giảm Thời gian hồi chiêu Kỹ Năng Echo và Resonance Skill của Resonator, đồng thời phục hồi một lượng Concerto Energy nhất định.</t>
         </is>
       </c>
     </row>
@@ -7673,12 +7673,12 @@
 Lễ Hội Theo Vầng Trăng là một lễ hội truyền thống của Huanglong, gắn liền với nhiều câu chuyện nguồn gốc khác nhau, trong đó nổi tiếng nhất là truyền thuyết về Chú Cáo và Vầng Trăng. Vào đêm đặc biệt này, gia đình và bạn bè quây quần bên nhau ngắm trăng, gửi gắm những điều ước và hy vọng về một tương lai tươi sáng hơn.
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 17. Để có trải nghiệm tốt nhất, hãy hoàn thành nhiệm vụ \"Thời Khắc Vĩnh Hằng Tan Băng\" trước khi tham gia sự kiện.
-Event Rules
-1. Giúp Tương Lệ Yao chuẩn bị cho Moonlit Fair để tăng Độ Nổi Tiếng của lễ hội.
-2. Increase Độ Nổi Tiếng bằng cách thực hiện các Điều Ước và xây dựng gian hàng.
-3. Invite Companion hỗ trợ chuẩn bị bằng cách hoàn thành các Side Quests tương ứng, qua đó nhận được Đánh Giá Wish cao hơn và Quỹ Hoạt Động dồi dào hơn.
+Quy Tắc Sự Kiện
+1. Giúp Tương Lệ Dao chuẩn bị cho Hội Chợ Ánh Trăng để tăng Độ Nổi Tiếng của lễ hội.
+2. Tăng Độ Nổi Tiếng bằng cách thực hiện các Điều Ước và xây dựng gian hàng.
+3. Mời Đồng Hành hỗ trợ chuẩn bị bằng cách hoàn thành các Nhiệm Vụ Phụ tương ứng, qua đó nhận được Đánh Giá Ước Nguyện cao hơn và Quỹ Hoạt Động dồi dào hơn.
 4. Hoàn thành các mục tiêu lễ hội để nhận và đổi thưởng.
-5. Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được giữ lại trong 30 ngày và sẽ được gửi lại qua Mail khi bạn đăng nhập trong khoảng thời gian này (Lưu ý: Rewards chưa đổi sẽ không được gửi lại.)</t>
+5. Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được giữ lại trong 30 ngày và sẽ được gửi lại qua Thư khi bạn đăng nhập trong khoảng thời gian này (Lưu ý: Phần thưởng chưa đổi sẽ không được gửi lại.)</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>1. Trong Moon-Chasing Festival, bạn có thể tăng Độ Nổi Tiếng qua các hoạt động tại &lt;color=#8c7e51&gt;Lodge Wishes&lt;/color&gt; và &lt;color=#8c7e51&gt;Fair Stalls&lt;/color&gt; để làm cho Moonlit Fair thêm sôi động.
+          <t>1. Trong Lễ Hội Đuổi Trăng, bạn có thể tăng Độ Nổi Tiếng qua các hoạt động tại &lt;color=#8c7e51&gt;Điều Ước Lều Trại&lt;/color&gt; và &lt;color=#8c7e51&gt;Gian Hàng Hội Chợ&lt;/color&gt; để làm cho Hội Chợ Ánh Trăng thêm sôi động.
 2. Độ Nổi Tiếng dao động từ Cấp 1 đến Cấp 6.</t>
         </is>
       </c>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>1. Xây dựng hoặc nâng cấp quầy hàng để tăng Độ Nổi Tiếng, nhận buff và mở khóa Companions.
+          <t>1. Xây dựng hoặc nâng cấp quầy hàng để tăng Độ Nổi Tiếng, nhận buff và mở khóa Đồng Hành.
 2. Xây dựng hoặc nâng cấp quầy hàng cần Vốn, có thể kiếm được bằng cách hoàn thành Điều Ước trong Lodge Wishes.
 3. Quầy hàng có thể nâng cấp nhiều lần, cấp càng cao thì buff càng mạnh.
 4. Sau khi xây dựng quầy hàng, cậu có thể tham gia các hoạt động của quầy và có thể nhận được phần thưởng bất ngờ, cùng với phần thưởng hàng ngày cho Thus Says the Moon, Hsin's Fortuity và Riddle Twiddle.</t>
@@ -7951,8 +7951,8 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>1. Fame phản ánh kỹ năng câu cá của bạn và sự công nhận từ những ngư dân trên Riccioli Islands. Tăng Fame sẽ mang lại nhiều tiện lợi hơn khi di chuyển trên vùng biển Riccioli.
-2. Bạn có thể kiếm Fame bằng cách khám phá Riccioli Islands, hoàn thành Requests từ Nhà Buôn Planck và cập nhật Index.</t>
+          <t>1. Danh Vọng phản ánh kỹ năng câu cá của bạn và sự công nhận từ những ngư dân trên Quần Đảo Riccioli. Tăng Danh Vọng sẽ mang lại nhiều tiện lợi hơn khi di chuyển trên vùng biển Riccioli.
+2. Bạn có thể kiếm Danh Vọng bằng cách khám phá Quần Đảo Riccioli, hoàn thành Yêu Cầu từ Nhà Buôn Planck và cập nhật Mục Lục.</t>
         </is>
       </c>
     </row>
@@ -8018,8 +8018,8 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>1. Một số Nhiệm Vụ Requests cần Kỹ Năng Fishing cụ thể. Nếu chưa mở khóa kỹ năng cần thiết, cậu sẽ không thể hoàn thành những nhiệm vụ này.
-2. Tại trang Kỹ Năng Fishing, cậu có thể tiêu hao một lượng vật liệu và xu nhất định để mở khóa các Kỹ Năng Fishing.</t>
+          <t>1. Một số Nhiệm Vụ Yêu Cầu cần Kỹ Năng Câu Cá cụ thể. Nếu chưa mở khóa kỹ năng cần thiết, cậu sẽ không thể hoàn thành những nhiệm vụ này.
+2. Tại trang Kỹ Năng Câu Cá, cậu có thể tiêu hao một lượng vật liệu và xu nhất định để mở khóa các Kỹ Năng Câu Cá.</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Năng lượng Hỗn Loạn đang dâng trào trong cơ thể Rover. Giữ nút &lt;color=#ffd12f&gt;Basic Attack&lt;/color&gt; để giải phóng sức mạnh.</t>
+          <t>Năng lượng Hỗn Loạn đang dâng trào trong cơ thể Vận Mệnh Giả. Giữ nút &lt;color=#ffd12f&gt;Basic Attack&lt;/color&gt; để giải phóng sức mạnh.</t>
         </is>
       </c>
     </row>
@@ -8150,8 +8150,8 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Rover học được kỹ năng mới, mỗi đòn tấn công gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và tích &lt;color=#ffd12f&gt;Umbra&lt;/color&gt;.
-Khi "Umbra" đạt tối đa, Rover có thể giải phóng sức mạnh bằng &lt;color=#ffd12f&gt;Heavy Attack&lt;/color&gt; và bước vào trạng thái &lt;color=#ffd12f&gt;"Dark Surge"&lt;/color&gt;.</t>
+          <t>Rover học được kỹ năng mới, mỗi đòn tấn công gây &lt;color=Dark&gt;Sát Thương Havoc&lt;/color&gt; và tích &lt;color=#ffd12f&gt;Umbra&lt;/color&gt;.
+Khi "Umbra" đạt tối đa, Rover có thể giải phóng sức mạnh bằng &lt;color=#ffd12f&gt;Đòn Heavy Attack&lt;/color&gt; và bước vào trạng thái &lt;color=#ffd12f&gt;"Bùng Nổ Bóng Tối"&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8217,8 +8217,8 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Giữ {0} và nhấn giữ {1} để thực hiện &lt;color=#ffd12f&gt;Wall Dash&lt;/color&gt;. 
-Wall Dash tiêu hao &lt;color=#ffd12f&gt;STA&lt;/color&gt; và sẽ tự động kết thúc khi STA cạn kiệt.</t>
+          <t>Giữ {0} và nhấn giữ {1} để thực hiện &lt;color=#ffd12f&gt;Đột Kích Tường&lt;/color&gt;. 
+Đột Kích Tường tiêu hao &lt;color=#ffd12f&gt;STA&lt;/color&gt; và sẽ tự động kết thúc khi STA cạn kiệt.</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Nhấn {0} để dùng &lt;color=#ffd12f&gt;Basic Attack&lt;/color&gt;.</t>
+          <t>Nhấn {0} để dùng &lt;color=#ffd12f&gt;Đòn Cơ Bản&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Nhấn {0} ngay bây giờ để kích hoạt &lt;color=#ffd12f&gt;Dodge&lt;/color&gt;.</t>
+          <t>Nhấn {0} ngay bây giờ để kích hoạt &lt;color=#ffd12f&gt;Né Tránh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>{0} Sử dụng &lt;color=#ffd12f&gt;Echo skill&lt;/color&gt; này để lao về phía trước.</t>
+          <t>Dùng &lt;color=#ffd12f&gt;kỹ năng Echo&lt;/color&gt; này để lao về phía trước.</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Cậu đã thiết lập Resonance với nguồn sức mạnh tại đây. Resonators có thể từ từ hồi phục HP khi không hoạt động.</t>
+          <t>Cậu đã thiết lập Cộng Hưởng với nguồn sức mạnh tại đây. Resonator có thể từ từ hồi phục HP khi không hoạt động.</t>
         </is>
       </c>
     </row>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Cậu có thể xem &lt;color=#ffd12f&gt;Outro Skill&lt;/color&gt;. &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; {0} để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; qua menu vòng.</t>
+          <t>Cậu có thể xem &lt;color=#ffd12f&gt;Kỹ Năng Outro&lt;/color&gt;. &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; {0} để mở bảng &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; qua menu vòng.</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} {0} để kích hoạt &lt;color=#ffd12f&gt;Air Dodge&lt;/color&gt;.</t>
+          <t>Khi ở trên không, {Cus:Ipt,Touch=nhấn PC=nhấn Gamepad=nhấn} {0} để kích hoạt &lt;color=#ffd12f&gt;Né Tránh Trên Không&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8739,8 +8739,8 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để mở menu &lt;color=#ffd12f&gt;Resonators&lt;/color&gt; qua vòng điều hướng.
-Equip Echoes cụ thể để kích hoạt hiệu ứng &lt;color=#ffd12f&gt;Sonata&lt;/color&gt;</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở menu &lt;color=#ffd12f&gt;Resonator&lt;/color&gt; qua vòng điều hướng.
+Trang bị Echo cụ thể để kích hoạt hiệu ứng &lt;color=#ffd12f&gt;Sonata&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#ffd12f&gt;Giữ&lt;/color&gt; để mở Sổ tay qua vòng điều hướng. Bạn có thể xác định vị trí kẻ địch trong &lt;color=#ffd12f&gt;Sổ tay&lt;/color&gt;</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở Sổ Hướng Dẫn qua vòng điều hướng. Bạn có thể xác định vị trí kẻ địch trong &lt;color=#ffd12f&gt;Sổ Hướng Dẫn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8871,8 +8871,8 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Mỗi Tacet Field đều có một hiệu ứng đặc biệt riêng.
-Tacet Field nằm ở Central Plains sẽ định kỳ tạo ra một Quả Cầu Concerto Energy, giúp hồi phục Concerto Energy và gây &lt;color=#ffd12f&gt;AoE DMG&lt;/color&gt; sau khi bạn sử dụng &lt;color=#ffd12f&gt;Intro Skill&lt;/color&gt;.</t>
+          <t>Mỗi Tổ Tacet đều có một hiệu ứng đặc biệt riêng.
+Tổ Tacet nằm ở Central Plains sẽ định kỳ tạo ra một Quả Cầu Concerto Energy, giúp hồi phục Concerto Energy và gây &lt;color=#ffd12f&gt;Sát Thương Khu Vực&lt;/color&gt; sau khi bạn sử dụng &lt;color=#ffd12f&gt;Kỹ Năng Intro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>{0} sử dụng Resonance Skill để nhận "Umbra".</t>
+          <t>Dùng Resonance Skill để nhận "Umbra".</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>{0} dùng Resonance Skill để nhận "Umbra".</t>
+          <t>Dùng Resonance Skill để nhận "Umbra".</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Kỹ Năng Phản Đòn</t>
+          <t>Kỹ năng phản đòn</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Một &lt;color=#ffd12f&gt;Warning Prompt&lt;/color&gt; sẽ xuất hiện trước khi kẻ địch sử dụng &lt;color=#ffd12f&gt;Special Skills&lt;/color&gt;. Bạn có thể chặn những đòn tấn công này bằng &lt;color=#ffd12f&gt;specific Echo Skills&lt;/color&gt;, hoặc dùng &lt;color=#ffd12f&gt;Counterattacks&lt;/color&gt; để giành lợi thế.</t>
+          <t>Một &lt;color=#ffd12f&gt;Cảnh Báo Đỏ&lt;/color&gt; sẽ xuất hiện trước khi kẻ địch sử dụng &lt;color=#ffd12f&gt;Kỹ Năng Đặc Biệt&lt;/color&gt;. Bạn có thể chặn những đòn tấn công này bằng &lt;color=#ffd12f&gt;Kỹ Năng Echo cụ thể&lt;/color&gt;, hoặc dùng &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt; để giành lợi thế.</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Cậu đã thiết lập Resonance với nguồn sức mạnh tại đây. Resonators có thể từ từ hồi phục HP khi không hoạt động.</t>
+          <t>Cậu đã thiết lập Cộng Hưởng với nguồn sức mạnh tại đây. Resonator có thể từ từ hồi phục HP khi không hoạt động.</t>
         </is>
       </c>
     </row>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Giữ {0} để sử dụng &lt;color=#ffd12f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Giữ {0} để sử dụng &lt;color=#ffd12f&gt;Đòn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Giữ {0} để sử dụng &lt;color=#ffd12f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Giữ {0} để sử dụng &lt;color=#ffd12f&gt;Đòn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9531,9 +9531,9 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Một số kẻ địch đặc biệt trên Solaris-3 cực kỳ hung bạo và &lt;color=#ffd12f&gt;hard to defeat&lt;/color&gt;. Hãy sử dụng &lt;color=#ffd12f&gt;Counterattacks&lt;/color&gt;, &lt;color=#ffd12f&gt;Dodge Counters&lt;/color&gt; hoặc &lt;color=#ffd12f&gt;Intro Skills&lt;/color&gt; để gây sát thương đáng kể lên chúng.
+          <t>Một số kẻ địch đặc biệt trên Solaris-3 cực kỳ hung bạo và &lt;color=#ffd12f&gt;khó đánh bại&lt;/color&gt;. Hãy sử dụng &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt;, &lt;color=#ffd12f&gt;Né Phản Công&lt;/color&gt; hoặc &lt;color=#ffd12f&gt;Kỹ Năng Khởi Động&lt;/color&gt; để gây sát thương đáng kể lên chúng.
 Lưu ý rằng những kẻ địch đặc biệt này không mạnh lên theo Giai Đoạn SOL của bạn. Nếu hiện tại khó đánh bại, hãy nâng cấp nhân vật và thử lại sau.
-Những kẻ địch đặc biệt này sẽ &lt;color=#ffd12f&gt;regenerate&lt;/color&gt; sau khi bị đánh bại.</t>
+Những kẻ địch đặc biệt này sẽ &lt;color=#ffd12f&gt;tái sinh&lt;/color&gt; sau khi bị đánh bại.</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Kẻ Địch Đặc Biệt</t>
+          <t>Kẻ Thù Đặc Biệt</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       <c r="M132" t="inlineStr">
         <is>
           <t>Vảy cứng của Lumiscale Construct tạo thành lá chắn bảo vệ, giảm toàn bộ sát thương nhận vào khi kích hoạt.
-Lõi của Lumiscale Construct sẽ lộ ra &lt;color=#ffd12f&gt;after each attack&lt;/color&gt; và khi nó ở trạng thái &lt;color=#ffd12f&gt;immobilized&lt;/color&gt;. Hãy tấn công vào thời điểm này để gây sát thương hiệu quả.</t>
+Lõi của Lumiscale Construct sẽ lộ ra &lt;color=#ffd12f&gt;sau mỗi đòn tấn công&lt;/color&gt; và khi nó ở trạng thái &lt;color=#ffd12f&gt;bất động&lt;/color&gt;. Hãy tấn công vào thời điểm này để gây sát thương hiệu quả.</t>
         </is>
       </c>
     </row>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch và Dodge các đòn tấn công của chúng để tăng Cấp Độ Giao Hưởng.</t>
+          <t>Gây sát thương lên kẻ địch và né đòn của chúng để tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch và Dodge các đòn tấn công của chúng để tăng Cấp Độ Giao Hưởng.</t>
+          <t>Gây sát thương lên kẻ địch và né đòn của chúng để tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Gây sát thương lên kẻ địch và Dodge các đòn tấn công của chúng để tăng Cấp Độ Giao Hưởng.</t>
+          <t>Gây sát thương lên kẻ địch và né đòn của chúng để tăng Cấp Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -9939,13 +9939,13 @@
 Học viện đang thử nghiệm một loại công nghệ mới, được đồn đoán có khả năng mô phỏng những kẻ địch mạnh mẽ để hỗ trợ huấn luyện chiến đấu cho binh lính...
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 14.
-Event Rules
+Quy Tắc Sự Kiện
 1. Trong Tactical Simulacra, hãy đối đầu với làn sóng kẻ địch hùng mạnh bằng cách sử dụng các hiệu ứng đặc biệt trong các miền mô phỏng khác nhau.
 2. Khi hoàn thành nhiều thử thách hơn, bạn sẽ mở khóa thêm nhiều hiệu ứng đặc biệt để hỗ trợ trong các thử thách tiếp theo.
-3. Kết quả của mỗi thử thách bao gồm ba phần: Points Quái Vật, Time Points và Technical Points.
-i. Points Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
-ii. Time Points được tính dựa trên thời gian còn lại khi hoàn thành thử thách. Càng đánh bại nhiều kẻ địch, hệ số chuyển đổi điểm càng cao.
-iii. Technical Points được tính cho mỗi lần Phản Công và Dodge thành công. Mỗi thử thách có giới hạn tối đa về số Technical Points có thể đạt được.</t>
+3. Kết quả của mỗi thử thách bao gồm ba phần: Điểm Quái Vật, Điểm Thời Gian và Điểm Kỹ Thuật.
+i. Điểm Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
+ii. Điểm Thời Gian được tính dựa trên thời gian còn lại khi hoàn thành thử thách. Càng đánh bại nhiều kẻ địch, hệ số chuyển đổi điểm càng cao.
+iii. Điểm Kỹ Thuật được tính cho mỗi lần Phản Công và Né Tránh thành công. Mỗi thử thách có giới hạn tối đa về số Điểm Kỹ Thuật có thể đạt được.</t>
         </is>
       </c>
     </row>
@@ -10012,9 +10012,9 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Với một số loại Tacet Discord nhất định, Terminal của con có thể tiêu hao thêm năng lực tính toán để tăng cường hấp thụ Echo và nâng cao cơ hội nhận được Echo rơi. Nó chỉ có thể thực hiện số lần hấp thụ tăng cường giới hạn, sau đó cần thời gian nạp lại.
+          <t>Với một số loại Tacet Discord nhất định, Thiết bị đầu cuối của con có thể tiêu hao thêm năng lực tính toán để tăng cường hấp thụ Echo và nâng cao cơ hội nhận được Echo rơi. Nó chỉ có thể thực hiện số lần hấp thụ tăng cường giới hạn, sau đó cần thời gian nạp lại.
 Số lần hấp thụ tăng cường của các loại khác nhau được tính riêng.
-*Cooldown chiêu đặt lại vào 04:00 thứ Hai hàng tuần theo giờ máy chủ.</t>
+*Thời gian hồi chiêu đặt lại vào 04:00 thứ Hai hàng tuần theo giờ máy chủ.</t>
         </is>
       </c>
     </row>
@@ -10087,12 +10087,12 @@
       <c r="M138" t="inlineStr">
         <is>
           <t>Về sự kiện
-Chúng tôi đã chuẩn bị những phần thưởng tuyệt vời để tri ân các Rover trên khắp thế giới vì sự ủng hộ của các bạn.
+Chúng tôi đã chuẩn bị những phần thưởng tuyệt vời để tri ân các Vận Mệnh Giả trên khắp thế giới vì sự ủng hộ của các bạn.
 Bạn có thể nhận phần thưởng ngay khi sự kiện bắt đầu.
 Điều kiện tham gia
 Đạt Cấp Liên Minh 8.
 Quy tắc sự kiện
-Rewards của sự kiện sẽ được phân phối qua ba giai đoạn, mỗi giai đoạn sẽ mở khóa vào ngày đã định (theo giờ máy chủ 04:00).
+Phần thưởng của sự kiện sẽ được phân phối qua ba giai đoạn, mỗi giai đoạn sẽ mở khóa vào ngày đã định (theo giờ máy chủ 04:00).
 Lưu ý rằng phần thưởng của sự kiện này sẽ KHÔNG được gửi lại qua thư trong game sau khi sự kiện kết thúc. Hãy lưu ý thời gian diễn ra sự kiện và nhận phần thưởng trước khi sự kiện kết thúc.</t>
         </is>
       </c>
@@ -10161,7 +10161,7 @@
       <c r="M139" t="inlineStr">
         <is>
           <t>Hầm Photon thường xuất hiện theo bộ và phát ra những luồng năng lượng vàng kết nối với Rào Chắn Photon.
-Cả &lt;color=#ffd12f&gt;Ranged Attacks&lt;/color&gt; lẫn &lt;color=#ffd12f&gt;Melee Attacks&lt;/color&gt; đều có thể vô hiệu hóa Hầm Photon. Vô hiệu hóa tất cả Hầm Photon trong một bộ sẽ làm tắt Rào Chắn Photon.
+Cả &lt;color=#ffd12f&gt;Tấn Công Xa&lt;/color&gt; lẫn &lt;color=#ffd12f&gt;Tấn Công Cận Chiến&lt;/color&gt; đều có thể vô hiệu hóa Hầm Photon. Vô hiệu hóa tất cả Hầm Photon trong một bộ sẽ làm tắt Rào Chắn Photon.
 Khi Rào Chắn Photon bị phá vỡ, những kẻ địch đứng yên bên trong sẽ hoạt động trở lại.</t>
         </is>
       </c>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Stand trên Thiết Bị Nhảy một lúc để phóng mình theo hướng mục tiêu. 
+          <t>Đứng trên Thiết Bị Nhảy một lúc để phóng mình theo hướng mục tiêu. 
 Thiết Bị Nhảy cũng có thể sử dụng khi bạn biến hình thành Clang Bang.</t>
         </is>
       </c>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Những chiếc Chuông Gió rải rác khắp Núi Firmament, có thể thu thập bằng &lt;color=#ffd12f&gt;Basic Attack&lt;/color&gt; hoặc &lt;color=#ffd12f&gt;Ranged Attack&lt;/color&gt;. Có ai đó rất quan tâm đến chúng đấy. Hãy thu thập Chuông Gió để đổi lấy tài nguyên quý giá từ cô ấy nhé.</t>
+          <t>Những chiếc Chuông Gió rải rác khắp Núi Firmament, có thể thu thập bằng &lt;color=#ffd12f&gt;Basic Attack&lt;/color&gt; hoặc &lt;color=#ffd12f&gt;Tấn Công Từ Xa&lt;/color&gt;. Có ai đó rất quan tâm đến chúng đấy. Hãy thu thập Chuông Gió để đổi lấy tài nguyên quý giá từ cô ấy nhé.</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Dodge hoặc Dodge Counter thành công sẽ tăng mạnh cấp độ Giao Hưởng.</t>
+          <t>Né tránh hoặc Phản đòn né tránh thành công sẽ tăng mạnh cấp độ Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Chạm vào biểu tượng Resonator của &lt;color=#ffd12f&gt;party member&lt;/color&gt; để kích hoạt Intro Skill của Resonator và Outro Skill của họ.</t>
+          <t>Chạm vào biểu tượng Resonator của &lt;color=#ffd12f&gt;thành viên đội&lt;/color&gt; để kích hoạt Kỹ Năng Intro của Resonator và Kỹ Năng Outro của họ.</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Kỹ Năng Enhanced Resonance</t>
+          <t>Resonance Skill Cường Hóa</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Kỹ Năng Enhanced Resonance 1</t>
+          <t>Resonance Skill Cường Hóa 1</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Kỹ Năng Enhanced Resonance 2</t>
+          <t>Resonance Skill Cường Hóa 2</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Kỹ Năng Enhanced Resonance 3</t>
+          <t>Resonance Skill Cường Hóa 3</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Cơ Bản&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Đòn Nặng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Enhanced Resonance Skill&lt;/color&gt;</t>
+          <t>Luuk Herssen: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Skill Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Luuk Herssen: Hướng dẫn toàn diện &lt;color=#d4bf5f&gt;Enhanced Resonance Skill&lt;/color&gt;</t>
+          <t>Luuk Herssen: Hướng dẫn toàn diện &lt;color=#d4bf5f&gt;Resonance Skill Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack để tiêu hao Thể Lực và tung đòn &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;, bật lên không trung và gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Giữ Basic Attack để tiêu hao STA và tung đòn &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;, bật lên không trung và gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Sau khi thực hiện 4 đòn tấn công liên tiếp, &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sẽ khả dụng, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Sau khi thực hiện 4 đòn tấn công liên tiếp, &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; sẽ khả dụng, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Normal Attack trên không để thực hiện 3 đòn liên tiếp bằng lưỡi hái, sau đó &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sẽ sẵn sàng, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Đòn Thường trên không để thực hiện 3 đòn liên tiếp bằng lưỡi hái, sau đó &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; sẽ sẵn sàng, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack một lần, sau đó {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy hai lần để thực hiện các đòn tấn công liên tiếp bằng lưỡi hái. Sau đó, &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sẽ được kích hoạt, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack một lần, sau đó {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy hai lần để thực hiện các đòn tấn công liên tiếp bằng lưỡi hái. Sau đó, &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; sẽ được kích hoạt, gây &lt;color=Light&gt;DMG Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Giữ Normal Attack giữa không trung để tiêu hao STA và tung &lt;color=Highlight&gt;Plunging Attack&lt;/color&gt;, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Giữ Normal Attack giữa không trung để tiêu hao STA và tung &lt;color=Highlight&gt;Đòn Lao Xuống&lt;/color&gt;, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Resonance Skill để phóng nhanh đến vị trí mục tiêu, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill để phóng nhanh đến vị trí mục tiêu, gây &lt;color=Light&gt;Sát Thương Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge để lơ lửng trong chốc lát và phóng một lưỡi kiếm vào mục tiêu, gây sát thương &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} né tránh để lơ lửng trong chốc lát và phóng một lưỡi kiếm vào mục tiêu, gây DMG &lt;color=Light&gt;Spectro cố định&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12116,9 +12116,9 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Sau khi thực hiện 3 đòn &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; liên tiếp trên không, &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sẽ được kích hoạt.
-&lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; có 3 dạng. Mỗi lần sử dụng sẽ chuyển &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sang dạng tiếp theo theo thứ tự.
-Sử dụng 2 dạng đầu của &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sẽ liên kết vào &lt;color=Highlight&gt;Special Basic Attack&lt;/color&gt;. Sử dụng dạng thứ 3 của &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt; sẽ liên kết vào &lt;color=Highlight&gt;Special Mid-air Attack&lt;/color&gt;.</t>
+          <t>Sau khi thực hiện 3 đòn Basic Attack liên tiếp trên không, &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; sẽ khả dụng.
+&lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; có 3 dạng. Mỗi lần sử dụng sẽ chuyển sang dạng tiếp theo theo thứ tự.
+Sử dụng 2 dạng đầu của &lt;color=Highlight&gt;Resonance Skill Nâng Cao&lt;/color&gt; sẽ liên kết thành &lt;color=Highlight&gt;Đòn Basic Attack Đặc Biệt&lt;/color&gt;. Sử dụng dạng thứ 3 sẽ liên kết thành &lt;color=Highlight&gt;Đòn Mid-air Attack Đặc Biệt&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Luuk Herssen vung dao mổ, gây &lt;color=Light&gt;Spectro DMG&lt;/color&gt;.</t>
+          <t>Luuk Herssen vung dao mổ, gây &lt;color=Light&gt;DMG Spectro&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Resonance Skill&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12508,7 +12508,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Chained Resonance Skill 1&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng Hưởng Liên Kết 1&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Chained Resonance Skill 2&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng Hưởng Liên Kết 2&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Enhanced Heavy Attack&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Nâng Cao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Sigrika: &lt;color=#d4bf5f&gt;Resonance Skill Finisher&lt;/color&gt;</t>
+          <t>Sigrika: &lt;color=#d4bf5f&gt;Hướng dẫn Hoàn Tất Kỹ năng Cộng Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp để vào trạng thái &lt;color=Highlight&gt;Decipher&lt;/color&gt; và tung ra &lt;color=Highlight&gt;Enhanced Basic Attack&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp để vào trạng thái &lt;color=Highlight&gt;Giải Mã&lt;/color&gt; và tung ra &lt;color=Highlight&gt;Đòn Basic Attack Nâng Cao&lt;/color&gt;, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Giữ Normal Attack và tiêu hao STA để tung &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Giữ Normal Attack và tiêu hao STA để tung &lt;color=Highlight&gt;Đòn Tấn Công Mạnh&lt;/color&gt;, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Resonance Skill để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill để tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Resonance Skill ngay sau khi tung &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Chained Resonance Skill 1&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Skill ngay sau khi tung &lt;color=Highlight&gt;Giai Đoạn 4 Đòn Cơ Bản&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Resonance Skill Liên Hoàn 1&lt;/color&gt;, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Khi có ít nhất 50 điểm &lt;color=Highlight&gt;Full Stop&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill ngay sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; để kích hoạt &lt;color=Highlight&gt;Chained Resonance Skill 2&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
+          <t>Khi có ít nhất 50 điểm &lt;color=Highlight&gt;Dấu Chấm Câu&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill ngay sau khi sử dụng &lt;color=Highlight&gt;Đòn Basic Attack Giai Đoạn 4&lt;/color&gt; để kích hoạt &lt;color=Highlight&gt;Resonance Skill Liên Kết 2&lt;/color&gt;, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Nhấn {Cus:Ipt,Touch=Ấn PC=press Gamepad=press} Resonance Liberation để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và ban hiệu ứng &lt;color=Highlight&gt;Divergent&lt;/color&gt;.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Resonance Liberation để tấn công mục tiêu, gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và ban hiệu ứng &lt;color=Highlight&gt;Divergent&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Nếu đánh trúng mục tiêu trực tiếp bằng &lt;color=Highlight&gt;Enhanced BA&lt;/color&gt; trong thời gian thi triển, bạn sẽ nhận được một &lt;color=Highlight&gt;Rune: Trust&lt;/color&gt;.</t>
+          <t>Nếu đánh trúng mục tiêu trực tiếp bằng &lt;color=Highlight&gt;BA Nâng Cao&lt;/color&gt; trong thời gian thi triển, bạn sẽ nhận được một &lt;color=Highlight&gt;Rune: Trust&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Trong thời gian thi triển, nếu đánh trúng mục tiêu trực tiếp bằng &lt;color=Highlight&gt;Chained Resonance Skill 1&lt;/color&gt; hoặc &lt;color=Highlight&gt;Chained Resonance Skill 2&lt;/color&gt;, bạn sẽ nhận được một &lt;color=Highlight&gt;Rune: Answer&lt;/color&gt;.</t>
+          <t>Trong thời gian thi triển, nếu đánh trúng mục tiêu trực tiếp bằng &lt;color=Highlight&gt;Resonance Skill Chuỗi 1&lt;/color&gt; hoặc &lt;color=Highlight&gt;Resonance Skill Chuỗi 2&lt;/color&gt;, bạn sẽ nhận được một &lt;color=Highlight&gt;Rune: Answer&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Với hai &lt;color=Highlight&gt;Runes&lt;/color&gt;, giữ Normal Attack để thi triển Heavy Attack được tăng cường và nhận &lt;color=Highlight&gt;Full Stop&lt;/color&gt;.</t>
+          <t>Với hai &lt;color=Highlight&gt;Rune&lt;/color&gt;, giữ Normal Attack để thi triển Heavy Attack được tăng cường và nhận &lt;color=Highlight&gt;Full Stop&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đạt tối đa, giữ Resonance Skill để tung &lt;color=Highlight&gt;Resonance Skill Finisher&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Full Stop&lt;/color&gt; đạt tối đa, giữ Resonance Skill để tung &lt;color=Highlight&gt;Hồi Kết Resonance Skill&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Sau &lt;color=#f4d582&gt;Crimson Fragment&lt;/color&gt;, &lt;color=#f4d582&gt;Basic Attack 2&lt;/color&gt; hoặc &lt;color=#f4d582&gt;Vindication&lt;/color&gt;, dùng &lt;color=#f4d582&gt;Dodge Counter&lt;/color&gt; để thực hiện tối đa 2 đòn Crimson Erosion, gây &lt;color=#e649a6&gt;Havoc DMG&lt;/color&gt;, áp dụng &lt;color=#f4d582&gt;Incinerating Will&lt;/color&gt; lên mục tiêu trúng đòn, tăng 20% sát thương Danjin gây ra lên mục tiêu bị đánh dấu.</t>
+          <t>Sau &lt;color=#f4d582&gt;Đòn Cơ Bản 2&lt;/color&gt;, &lt;color=#f4d582&gt;Vindication&lt;/color&gt; hoặc &lt;color=#f4d582&gt;Dodge Counter Tránh&lt;/color&gt;, dùng &lt;color=#f4d582&gt;Mảnh Crimson&lt;/color&gt; để thực hiện tối đa 2 đòn Crimson Erosion, gây &lt;color=#e649a6&gt;Sát Thương Havoc&lt;/color&gt;, áp dụng &lt;color=#f4d582&gt;Ý Chí Thiêu Đốt&lt;/color&gt; lên mục tiêu trúng đòn, tăng 20% DMG Danjin gây ra lên mục tiêu bị đánh dấu.</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>1. Khi hoàn thành Simulation Challenge, bạn có thể tiêu 40 Waveplate để nhận thưởng. Vật phẩm rơi chính bao gồm nguyên liệu tăng EXP vũ khí, EXP Resonators và Shell Credit.</t>
+          <t>1. Khi hoàn thành Thử Thách Mô Phỏng, bạn có thể tiêu 40 Waveplate để nhận thưởng. Vật phẩm rơi chính bao gồm nguyên liệu tăng EXP vũ khí, EXP Resonator và Shell Credit.</t>
         </is>
       </c>
     </row>
@@ -13890,14 +13890,14 @@
           <t>Về sự kiện
 Cosmos xuất hiện gần một cánh cổng kỳ lạ, mời bạn bước vào và hỗ trợ một cuộc thử nghiệm nào đó.
 Những thế giới đằng sau cánh cổng đan xen như một tấm thảm huyền bí—
-"Rover hiền lành ơi, mong ngươi tìm thấy vận may trong thế giới sáng rõ."
+"Vận Mệnh Giả hiền lành ơi, mong ngươi tìm thấy vận may trong thế giới sáng rõ."
 Điều kiện tham gia
 Đạt Cấp Liên Minh 22.
 Quy tắc sự kiện
-1. Bảo vệ thiết bị thử nghiệm và đánh bại Discord để giành chiến thắng tuyệt đối!
-2. Cosmos sẽ cung cấp những Echoid đặc biệt để hỗ trợ Resonators.
+1. Bảo vệ thiết bị thử nghiệm và đánh bại Tacet Discord để giành chiến thắng tuyệt đối!
+2. Cosmos sẽ cung cấp những Echoid đặc biệt để hỗ trợ Resonator.
 2. Trong chế độ này, bạn chỉ được sử dụng các Echoid được chỉ định (Sonata vẫn có hiệu lực và chỉ Kỹ Năng Echo chính sẽ bị thay thế).
-3. Points = (Thời gian còn lại mỗi đợt x hệ số thời gian) + (HP còn lại của thiết bị cuối trận x hệ số độ khó)
+3. Điểm = (Thời gian còn lại mỗi đợt x hệ số thời gian) + (HP còn lại của thiết bị cuối trận x hệ số độ khó)
 4. Mức điểm tối đa sẽ tăng lên khi mở khóa các cấp độ cao hơn. Chơi lại các giai đoạn để tích lũy thêm điểm.</t>
         </is>
       </c>
@@ -13971,9 +13971,9 @@
         <is>
           <t>[Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 17 và hoàn thành "Ngôi Sao Oan Nghiệt".
-[Event Rules]
+[Quy Tắc Sự Kiện]
 1. Tham gia "Dưới Ánh Trăng" và giúp chuẩn bị cho Hội Chợ Trăng để tăng Độ Nổi Tiếng của lễ hội.
-2. Increase Độ Nổi Tiếng bằng cách hoàn thành Điều Ước và xây dựng các gian hàng.
+2. Tăng Độ Nổi Tiếng bằng cách hoàn thành Điều Ước và xây dựng các gian hàng.
 3. Đạt các mục tiêu Độ Nổi Tiếng để nhận phần thưởng tương ứng.
 4. Phần thưởng chưa nhận sẽ được gửi qua thư khi bạn đăng nhập lần đầu trong vòng 30 ngày sau khi sự kiện kết thúc.</t>
         </is>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Trong Chế Độ Hợp Tác, khi &lt;color=#ffd12f&gt;party member&lt;/color&gt; có Concerto Energy đầy, chạm vào biểu tượng của họ để kích hoạt Intro Skill của Resonator và Outro Skill của Resonator đó. Concerto Energy đầy sẽ tự động được xóa sau 10 giây.
+          <t>Trong Chế Độ Hợp Tác, khi &lt;color=#ffd12f&gt;thành viên nhóm&lt;/color&gt; có Concerto Energy đầy, chạm vào biểu tượng của họ để kích hoạt Kỹ Năng Intro của Resonator và Kỹ Năng Outro của Resonator đó. Concerto Energy đầy sẽ tự động được xóa sau 10 giây.
 Mỗi thành viên trong nhóm chỉ có thể kích hoạt hiệu ứng này một lần.</t>
         </is>
       </c>
@@ -14108,8 +14108,8 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Dấu Thời Gian có thể được sử dụng để kích hoạt các Chronopin trong tàn tích Court of Savantae, &lt;color=#ffd12f&gt;temporarily stagnating&lt;/color&gt; &lt;color=#ffd12f&gt;flow of time&lt;/color&gt; trong phạm vi hiệu quả.
-Bạn có thể sử dụng Dấu Thời Gian để &lt;color=#ffd12f&gt;enemies or mechanisms&lt;/color&gt; trong phạm vi vào trạng thái tĩnh trong 10 giây. Sử dụng lại trong thời gian đóng băng để &lt;color=#ffd12f&gt;end&lt;/color&gt; hiệu ứng sớm.</t>
+          <t>Dấu Thời Gian có thể được sử dụng để kích hoạt các Chronopin trong tàn tích Court of Savantae, &lt;color=#ffd12f&gt;làm ngưng trệ tạm thời&lt;/color&gt; &lt;color=#ffd12f&gt;dòng chảy thời gian&lt;/color&gt; trong phạm vi hiệu quả.
+Bạn có thể dùng Dấu Thời Gian để &lt;color=#ffd12f&gt;đóng băng kẻ địch hoặc cơ chế&lt;/color&gt; trong phạm vi vào trạng thái tĩnh trong 10 giây. Sử dụng lại trong thời gian đóng băng để &lt;color=#ffd12f&gt;kết thúc&lt;/color&gt; hiệu ứng sớm.</t>
         </is>
       </c>
     </row>
@@ -14206,14 +14206,14 @@
 3. Nâng cấp Persona Pinball và thu thập các Tactical ROM mạnh mẽ để củng cố đội hình khi tiến xa hơn. Kẻ thù càng mạnh, phần thưởng càng hấp dẫn.
 4. Nếu đăng nhập trong vòng 30 ngày sau khi sự kiện kết thúc, mọi phần thưởng chưa nhận sẽ tự động gửi vào hộp thư trong game.
 Hướng dẫn
-1. Sát thương Bật: Va chạm với kẻ địch để gây Sát thương Bật dựa trên Tấn Công của Pinball.
-2. Năng lượng Skill: Mỗi Pinball có thể chứa tối đa 600 điểm Năng lượng Skill. Sử dụng Skill tiêu tốn chính xác 600 điểm.
+1. DMG Bật: Va chạm với kẻ địch để gây DMG Bật dựa trên ATK của Pinball.
+2. Năng lượng Kỹ năng: Mỗi Pinball có thể chứa tối đa 600 điểm Năng lượng Kỹ năng. Sử dụng Kỹ năng tiêu tốn chính xác 600 điểm.
 3. Năng lượng Tốc Rush: Đội hình chia sẻ tối đa 400 điểm Năng lượng Tốc Rush. Mỗi lần phóng từ Flipper sẽ hồi 200 điểm.
-4. Combo &amp; Đòn Quyền Năng: Gây Sát thương Bật sẽ tăng số hit Combo. Khi đạt 5, 10 hoặc 25 hit, lần phóng tiếp theo sẽ trở thành Đòn Quyền Năng Cấp 1, 2 hoặc 3, gây Sát thương Quyền Năng dựa trên Tấn Công của Pinball Đội trưởng.
+4. Combo &amp; Đòn Quyền Năng: Gây DMG Bật sẽ tăng số hit Combo. Khi đạt 5, 10 hoặc 25 hit, lần phóng tiếp theo sẽ trở thành Đòn Quyền Năng Cấp 1, 2 hoặc 3, gây DMG Quyền Năng dựa trên ATK của Pinball Đội trưởng.
 5. Kích Nổ: Đội hình có thể chứa tối đa 500 điểm Kích Nổ. Khi thanh Kích Nổ đầy, kích hoạt các hiệu ứng sau trong thời gian giới hạn:
-(1) Va chạm với kẻ địch gây Sát thương Quyền Năng dựa trên Tấn Công của Pinball Đội trưởng và tăng số hit Combo lên 1.
-(2) Cơ chế Bật Hướng xuất hiện. Chạm vào chúng sẽ khiến Pinball Tốc Rush theo hướng định sẵn, gây Sát thương Rush dựa trên Tấn Công của Pinball Đội trưởng.
-(3) Đội hình hồi Năng lượng Skill nhanh hơn mỗi giây.
+(1) Va chạm với kẻ địch gây DMG Quyền Năng dựa trên ATK của Pinball Đội trưởng và tăng số hit Combo lên 1.
+(2) Cơ chế Bật Hướng xuất hiện. Chạm vào chúng sẽ khiến Pinball Tốc Rush theo hướng định sẵn, gây DMG Rush dựa trên ATK của Pinball Đội trưởng.
+(3) Đội hình hồi Năng lượng Kỹ năng nhanh hơn mỗi giây.
 (4) Tốc độ Di chuyển của đội hình tăng 20%.</t>
         </is>
       </c>
@@ -14287,11 +14287,11 @@
         <is>
           <t>[Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 14.
-[Event Rules]
-1. Thu thập càng nhiều Tactic Points càng tốt trong Infinite Battle Simulation.
-2. Mỗi khu vực trong mô phỏng có ba Points Khảo Sát, kẻ địch sẽ mạnh hơn ở mỗi điểm. Đánh bại kẻ địch tại Points Khảo Sát thứ ba sẽ mang lại lượng lớn Tactic Points.
-3. Mở Rương Cung Ứng sau khi đánh bại kẻ địch để nhận Tactic Points và Biến Số Công Suất Low.
-4. Khi thu thập đủ Biến Số Công Suất Low, bạn có thể mở khóa các hiệu ứng mạnh mẽ mới—Biến Số Công Suất High, giúp tăng sức chiến đấu đáng kể trong Infinite Battle Simulation.</t>
+[Quy Tắc Sự Kiện]
+1. Thu thập càng nhiều Điểm Chiến Thuật càng tốt trong Mô Phỏng Chiến Đấu Vô Tận.
+2. Mỗi khu vực trong mô phỏng có ba Điểm Khảo Sát, kẻ địch sẽ mạnh hơn ở mỗi điểm. Đánh bại kẻ địch tại Điểm Khảo Sát thứ ba sẽ mang lại lượng lớn Điểm Chiến Thuật.
+3. Mở Rương Cung Ứng sau khi đánh bại kẻ địch để nhận Điểm Chiến Thuật và Biến Số Công Suất Thấp.
+4. Khi thu thập đủ Biến Số Công Suất Thấp, bạn có thể mở khóa các hiệu ứng mạnh mẽ mới—Biến Số Công Suất Cao, giúp tăng sức chiến đấu đáng kể trong Mô Phỏng Chiến Đấu Vô Tận.</t>
         </is>
       </c>
     </row>
@@ -14356,7 +14356,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Khi kẻ địch sử dụng &lt;color=#ffd12f&gt;Overclocking Skill&lt;/color&gt;, một dấu &lt;color=#ffd12f&gt;warning&lt;/color&gt; sẽ xuất hiện. Trong trạng thái này, khả năng chống gián đoạn của kẻ địch sẽ được tăng cường. Hãy tập trung và tránh các đòn tấn công.</t>
+          <t>Khi kẻ địch sử dụng &lt;color=#ffd12f&gt;Kỹ Năng Quá Tải&lt;/color&gt;, một dấu &lt;color=#ffd12f&gt;cảnh báo hình chữ thập đặc biệt&lt;/color&gt; sẽ xuất hiện. Trong trạng thái này, khả năng chống gián đoạn của kẻ địch sẽ được tăng cường. Hãy tập trung và tránh các đòn tấn công.</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Một số kẻ địch đột biến đã xuất hiện trong không gian dữ liệu. Chúng sẽ &lt;color=#ffd12f&gt;explode&lt;/color&gt; khi bị đánh bại, nên tránh xa vụ nổ đó.</t>
+          <t>Một số kẻ địch đột biến đã xuất hiện trong không gian dữ liệu. Chúng sẽ &lt;color=#ffd12f&gt;nổ&lt;/color&gt; khi bị đánh bại, nên tránh xa vụ nổ đó.</t>
         </is>
       </c>
     </row>
@@ -14493,11 +14493,11 @@
         <is>
           <t>[
 Dịch Chuyển Nhanh]
-Sử dụng Dịch Chuyển Nhanh để dịch chuyển đến Trạm Resonance hoặc Đèn Hiệu Resonance đang hoạt động trong phạm vi 500 mét từ vị trí mục tiêu.
+Sử dụng Dịch Chuyển Nhanh để dịch chuyển đến Trạm Cộng Hưởng hoặc Đèn Hiệu Cộng Hưởng đang hoạt động trong phạm vi 500 mét từ vị trí mục tiêu.
 [Ghi chú]
 Dịch Chuyển Nhanh không khả dụng trong các trường hợp sau:
-1. Không có Trạm Resonance hoặc Đèn Hiệu Resonance nào đang hoạt động trong phạm vi 500 mét từ vị trí mục tiêu. Bạn có thể kích hoạt chúng và thử lại.
-2. Không có Trạm Resonance hoặc Đèn Hiệu Resonance nào trong phạm vi 500 mét từ vị trí mục tiêu. Bạn có thể đặt Waypoint gần đó và thử lại.</t>
+1. Không có Trạm Cộng Hưởng hoặc Đèn Hiệu Cộng Hưởng nào đang hoạt động trong phạm vi 500 mét từ vị trí mục tiêu. Bạn có thể kích hoạt chúng và thử lại.
+2. Không có Trạm Cộng Hưởng hoặc Đèn Hiệu Cộng Hưởng nào trong phạm vi 500 mét từ vị trí mục tiêu. Bạn có thể đặt Điểm Dẫn Đường gần đó và thử lại.</t>
         </is>
       </c>
     </row>
@@ -14641,13 +14641,13 @@
 Bên cánh cửa bí ẩn, có một cô bé vô tình lạc qua—Dorothy. Cô cần sự giúp đỡ của cậu để đánh bại những con quái vật ẩn nấp sau cánh cửa đó.
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 22.
-Event Rules
-1. Trong thử thách này, cậu có thể chọn "Bạn Companions của Dorothy" làm Echoes hỗ trợ chiến đấu, giúp tăng cường sức mạnh cho Resonators.
-2. Resonators bị hạ gục sẽ tự động hồi sinh sau một khoảng thời gian.
+Quy Tắc Sự Kiện
+1. Trong thử thách này, cậu có thể chọn "Bạn Đồng Hành của Dorothy" làm Echo hỗ trợ chiến đấu, giúp tăng cường sức mạnh cho Resonator.
+2. Resonator bị hạ gục sẽ tự động hồi sinh sau một khoảng thời gian.
 3. Cậu có thể hoàn thành nhiệm vụ cùng bạn bè.
-4. Trong chế độ này, chỉ được sử dụng Echoes đã chỉ định (Sonata vẫn có hiệu lực và chỉ Skill Echoes chính bị thay thế).
-5. Cách Tính Points: Points Hoàn Thành + (Thời Gian Còn Lại x Hệ Số Thời Gian).
-Total Points sẽ là tổng điểm cao nhất đạt được ở các màn thông thường. (Không tính điểm cho các màn thử thách).</t>
+4. Trong chế độ này, chỉ được sử dụng Echo đã chỉ định (Sonata vẫn có hiệu lực và chỉ Skill Echo chính bị thay thế).
+5. Cách Tính Điểm: Điểm Hoàn Thành + (Thời Gian Còn Lại x Hệ Số Thời Gian).
+Tổng Điểm sẽ là tổng điểm cao nhất đạt được ở các màn thông thường. (Không tính điểm cho các màn thử thách).</t>
         </is>
       </c>
     </row>
@@ -14724,9 +14724,9 @@
 Những ánh sáng nhấp nháy dịu dàng thì thầm khúc ca tri ân, tôn vinh những món quà quý giá mà cậu từng trao tặng.
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14.
-Details
-Đây là sự kiện tăng cấp, nơi cậu sẽ nhận được những phần thưởng tuyệt vời khi đạt các mốc trong 4 hoạt động tăng cấp theo chủ đề: tăng cấp Resonator - "Journey Sao", tăng cấp vũ khí - "Cosmical Forge", tăng cấp Echoes - "Echo Đồng Điệu", và tăng cấp kỹ năng - "Unison Resonance".
-Tất cả phần thưởng chưa nhận sẽ được gửi qua Mail vào lần đăng nhập tiếp theo trong vòng 30 ngày sau khi sự kiện kết thúc.</t>
+Chi tiết
+Đây là sự kiện tăng cấp, nơi cậu sẽ nhận được những phần thưởng tuyệt vời khi đạt các mốc trong 4 hoạt động tăng cấp theo chủ đề: tăng cấp Resonator - "Hành Trình Sao", tăng cấp vũ khí - "Lò Rèn Vũ Trụ", tăng cấp Echo - "Tiếng Vọng Đồng Điệu", và tăng cấp kỹ năng - "Cộng Hưởng Đồng Nhất".
+Tất cả phần thưởng chưa nhận sẽ được gửi qua Thư vào lần đăng nhập tiếp theo trong vòng 30 ngày sau khi sự kiện kết thúc.</t>
         </is>
       </c>
     </row>
@@ -14813,9 +14813,9 @@
 3. Có 4 giai đoạn với số lượng đợt kẻ địch giới hạn và 1 giai đoạn với số lượng đợt kẻ địch vô hạn.
 i. Ở các giai đoạn có số lượng đợt kẻ địch giới hạn, bạn chỉ có thể tiến vào nửa sau của trận chiến khi hết giờ hoặc sau khi tiêu diệt hết kẻ địch.
 ii. Ở giai đoạn có số lượng đợt kẻ địch vô hạn, bạn chỉ có thể tiến vào nửa sau khi hết giờ.
-4. Points kiếm được ở các giai đoạn có số lượng đợt kẻ địch giới hạn bao gồm cả Time Points và Points Quái Vật, trong khi điểm ở giai đoạn có số lượng đợt kẻ địch vô hạn chỉ bao gồm Points Quái Vật.
-i. Points Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
-ii. Time Points được tính dựa trên thời gian còn lại khi hoàn thành thử thách.</t>
+4. Điểm kiếm được ở các giai đoạn có số lượng đợt kẻ địch giới hạn bao gồm cả Điểm Thời Gian và Điểm Quái Vật, trong khi điểm ở giai đoạn có số lượng đợt kẻ địch vô hạn chỉ bao gồm Điểm Quái Vật.
+i. Điểm Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
+ii. Điểm Thời Gian được tính dựa trên thời gian còn lại khi hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack: Charged I&lt;/color&gt;</t>
+          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack: Nạp I&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack: Charged II&lt;/color&gt;</t>
+          <t>Hình dạng Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Heavy Attack: Nạp II&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Heavy Attack: Charged I&lt;/color&gt; (Dạng Cơ Giới)</t>
+          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Đòn Nặng: Tích Năng I&lt;/color&gt; (Dạng Cơ Giới)</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Heavy Attack: Charged II&lt;/color&gt; (Dạng Cơ Giới)</t>
+          <t>Hướng dẫn: &lt;color=#d4bf5f&gt;Đòn Nặng: Tích Năng II&lt;/color&gt; (Dạng Cơ Giới)</t>
         </is>
       </c>
     </row>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Aemeath: &lt;color=#d4bf5f&gt;Resonance Liberation&lt;/color&gt;</t>
+          <t>Aemeath: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Resonance Liberation Finisher&lt;/color&gt;</t>
+          <t>Aemeath: Hướng dẫn &lt;color=#d4bf5f&gt;Kết Thúc Giải Cứu Cộng Hưởng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Giữ Normal Attack để tiêu hao STA và tích lực, sau đó thả ra để tung &lt;color=Highlight&gt;Heavy Attack: Charged I&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Giữ Normal Attack để tiêu hao STA và tích lực, sau đó thả ra để tung &lt;color=Highlight&gt;Đòn Tấn Công Mạnh: Tích Lực I&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Giữ Normal Attack để tiêu hao STA và tích lực. Giữ lâu hơn để tung ra &lt;color=Highlight&gt;Heavy Attack: Charged 2&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; cao hơn.</t>
+          <t>Giữ Normal Attack để tiêu hao STA và tích lực. Giữ lâu hơn để tung ra &lt;color=Highlight&gt;Đòn Heavy Attack: Tích Lực 2&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Hệ Fusion&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15920,7 +15920,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 2, 3, or 4&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong khoảng thời gian nhất định để tung &lt;color=Highlight&gt;Sync Strike&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Giai Đoạn Đòn Basic Attack 2, 3 hoặc 4&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong khoảng thời gian nhất định để tung &lt;color=Highlight&gt;Đòn Đồng Bộ&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15985,7 +15985,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt; và &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; đạt 50%, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thi triển Resonance Skill &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Song Tấu Thần Thánh&lt;/color&gt; và &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt; đạt 50%, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thi triển Resonance Skill &lt;color=Highlight&gt;Hòa Tấu Thần Thánh&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Giữ Normal Attack để tiêu hao STA và tích lực, sau đó thả ra để tung &lt;color=Highlight&gt;Heavy Attack: Charged I&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Giữ Normal Attack để tiêu hao STA và tích lực, sau đó thả ra để tung &lt;color=Highlight&gt;Đòn Tấn Công Mạnh: Tích Lực I&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Giữ Normal Attack để tiêu hao STA và tích lực. Giữ lâu hơn để tung ra &lt;color=Highlight&gt;Heavy Attack: Charged II&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; cao hơn.</t>
+          <t>Giữ Normal Attack để tiêu hao STA và tích lực. Giữ lâu hơn để tung ra &lt;color=Highlight&gt;Đòn Heavy Attack: Tích Lực II&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Hệ Fusion&lt;/color&gt; cao hơn.</t>
         </is>
       </c>
     </row>
@@ -16245,7 +16245,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16375,7 +16375,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 2, 3, or 4&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong khoảng thời gian nhất định để tung &lt;color=Highlight&gt;Sync Strike&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Giai Đoạn Đòn Basic Attack 2, 3 hoặc 4&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong khoảng thời gian nhất định để tung &lt;color=Highlight&gt;Đòn Đồng Bộ&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt; và &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; đạt 50%, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thi triển Resonance Skill &lt;color=Highlight&gt;Seraphic Duet&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Song Tấu Thần Thánh&lt;/color&gt; và &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt; đạt 50%, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để thi triển Resonance Skill &lt;color=Highlight&gt;Hòa Tấu Thần Thánh&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 2, 3, or 4&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong khoảng thời gian nhất định để tung &lt;color=Highlight&gt;Sync Strike&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.</t>
+          <t>Sau khi sử dụng &lt;color=Highlight&gt;Giai Đoạn Đòn Basic Attack 2, 3 hoặc 4&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong khoảng thời gian nhất định để tung &lt;color=Highlight&gt;Đòn Đồng Bộ&lt;/color&gt;, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16570,7 +16570,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và chuyển sang dạng Cơ Khí, mở khóa &lt;color=Highlight&gt;Resonance Liberation Finisher&lt;/color&gt;.</t>
+          <t>Gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và chuyển sang dạng Cơ Khí, mở khóa &lt;color=Highlight&gt;Đòn Kết Thúc Resonance Liberation&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Sau khi mở khóa &lt;color=Highlight&gt;Resonance Liberation Finisher&lt;/color&gt;, khi cả &lt;color=Highlight&gt;Synchronization Rate&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Rate&lt;/color&gt; đều đạt tối đa cùng lúc, &lt;color=Highlight&gt;Resonance Liberation Finisher&lt;/color&gt; sẽ khả dụng, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; cực lớn và chuyển sang dạng Aemeath.</t>
+          <t>Sau khi mở khóa &lt;color=Highlight&gt;Kết Thúc Giải Cộng Hưởng&lt;/color&gt;, khi cả &lt;color=Highlight&gt;Tỷ Lệ Đồng Bộ&lt;/color&gt; và &lt;color=Highlight&gt;Tỷ Lệ Cộng Hưởng&lt;/color&gt; đều đạt tối đa cùng lúc, &lt;color=Highlight&gt;Kết Thúc Giải Cộng Hưởng&lt;/color&gt; sẽ khả dụng, gây &lt;color=Fire&gt;Sát Thương Hệ Fusion&lt;/color&gt; cực lớn và chuyển sang dạng Aemeath.</t>
         </is>
       </c>
     </row>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Basic Attack - Present Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack - Bản Ngã Hiện Tại&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Heavy Attack - Present Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack - Bản Ngã Hiện Tại&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Resonance Skill - Present Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn - Resonance Skill - Bản Ngã Hiện Tại&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -16960,7 +16960,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Heavy Attack - Frost Splinter: Present Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack - Mảnh Băng: Bản Ngã Hiện Tại&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Basic Attack - Foreclaimed Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack - Bản Ngã Đã Định&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17090,7 +17090,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Heavy Attack - Foreclaimed Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack - Bản Ngã Đã Định&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Resonance Skill - Foreclaimed Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn - Resonance Skill - Bản Ngã Đã Định&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Iai Stance&lt;/color&gt; và &lt;color=#d4bf5f&gt;Basic Attack - Iai&lt;/color&gt; (Combo)</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Tư Thế Iai&lt;/color&gt; và &lt;color=#d4bf5f&gt;Basic Attack - Iai&lt;/color&gt; (Combo)</t>
         </is>
       </c>
     </row>
@@ -17285,7 +17285,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Iai Stance&lt;/color&gt; và &lt;color=#d4bf5f&gt;Basic Attack - Iai&lt;/color&gt; (Combo) Phần 2</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Tư Thế Iai&lt;/color&gt; và &lt;color=#d4bf5f&gt;Basic Attack - Iai&lt;/color&gt; (Combo) Phần 2</t>
         </is>
       </c>
     </row>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Hiyuki: &lt;color=#d4bf5f&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;</t>
+          <t>Hiyuki: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack - Băng Giá Cay Đắng: Bản Ngã Đã Định&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Trong trạng thái &lt;color=Highlight&gt;Present Self&lt;/color&gt;, thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Ở Stage 3, cô sẽ nhận được 100 điểm &lt;color=Highlight&gt;Dedication&lt;/color&gt;.</t>
+          <t>Trong trạng thái &lt;color=Highlight&gt;Bản Ngã Hiện Tại&lt;/color&gt;, thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Ở Giai Đoạn 3, cô sẽ nhận được 100 điểm &lt;color=Highlight&gt;Sự Cống Hiến&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Có thể tiếp nối bằng &lt;color=Highlight&gt;Basic Attack - Present Self&lt;/color&gt; Cấp 3.</t>
+          <t>Tiêu hao STA để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Có thể tiếp nối bằng &lt;color=Highlight&gt;Đòn Basic Attack - Hiện Thân&lt;/color&gt; Cấp 3.</t>
         </is>
       </c>
     </row>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để tiêu hao Thể Lực và thực hiện Đòn Lao Xuống, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;.</t>
+          <t>Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Đòn Normal Attack để tiêu hao STA và thực hiện Đòn Lao Xuống, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17610,7 +17610,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Tăng cường &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt; tiếp theo: Restore thêm 100 điểm &lt;color=Highlight&gt;Dedication&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Có thể tiếp nối bằng &lt;color=Highlight&gt;Basic Attack - Present Self Stage 3&lt;/color&gt;.</t>
+          <t>Tăng cường &lt;color=Highlight&gt;Đòn Cơ Bản - Hiện Thân Giai Đoạn 3&lt;/color&gt; tiếp theo: Hồi phục thêm 100 điểm &lt;color=Highlight&gt;Sự Cống Hiến&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Có thể tiếp nối bằng &lt;color=Highlight&gt;Đòn Cơ Bản - Hiện Thân Giai Đoạn 3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Đạt 300 điểm &lt;color=Highlight&gt;Dedication&lt;/color&gt; sẽ mở khóa &lt;color=Highlight&gt;Heavy Attack - Frost Splinter: Present Self&lt;/color&gt;, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và mở khóa &lt;color=Highlight&gt;Foreclaiming: Inward Vision&lt;/color&gt;.</t>
+          <t>Đạt 300 điểm &lt;color=Highlight&gt;Cống Hiến&lt;/color&gt; sẽ mở khóa &lt;color=Highlight&gt;Đòn Heavy Attack - Mảnh Băng Giá: Bản Ngã Hiện Tại&lt;/color&gt;, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và mở khóa &lt;color=Highlight&gt;Tiền Tuyên: Nhãn Quan Nội Tâm&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;. Hiyuki chuyển sang trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt; và nhận 3 điểm &lt;color=Highlight&gt;Frostharden Iai&lt;/color&gt;.</t>
+          <t>Gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;. Hiyuki chuyển sang trạng thái &lt;color=Highlight&gt;Bản Thể Đã Định&lt;/color&gt; và nhận 3 điểm &lt;color=Highlight&gt;Lưỡi Kiếm Băng Giá&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, có thể thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Frostheart&lt;/color&gt; khi trúng mục tiêu.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Tự Xưng Đã Mất&lt;/color&gt;, có thể thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Linh Hồn Băng Giá&lt;/color&gt; khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để vào trạng thái &lt;color=Highlight&gt;Giữ Breath&lt;/color&gt;. Khi thả &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc khi Thể Lực cạn kiệt, Hiyuki sẽ lao về phía trước, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt; và chặn các đòn tấn công đến.</t>
+          <t>Khi ở trạng thái &lt;color=Highlight&gt;Tự Xưng Đã Mất&lt;/color&gt;, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để vào trạng thái &lt;color=Highlight&gt;Nín Thở&lt;/color&gt;. Khi thả &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc khi STA cạn kiệt, Hiyuki sẽ lao về phía trước, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt; và chặn các đòn tấn công đến.</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện tối đa 3 đòn tấn công liên tiếp trên không, gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, với giai đoạn cuối là &lt;color=Highlight&gt;Mid-air Plunging Attack&lt;/color&gt;. Đánh trúng mục tiêu sẽ hồi phục &lt;color=Highlight&gt;Frostheart&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện tối đa 3 đòn tấn công liên tiếp trên không, gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;, với giai đoạn cuối là &lt;color=Highlight&gt;Tấn Công Lao Xuống Trên Không&lt;/color&gt;. Đánh trúng mục tiêu sẽ hồi phục &lt;color=Highlight&gt;Frostheart&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18200,8 +18200,8 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Khi Hiyuki có 3 tầng &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Foreclaimed Self&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Heavy Attack - Bitterfrost: Foreclaimed Self&lt;/color&gt;.
-Tiêu hao STA và 3 tầng &lt;color=Highlight&gt;Whiteout Bitterfrost&lt;/color&gt; để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, đồng thời nhận 1 điểm &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt;.</t>
+          <t>Khi Hiyuki có 3 tầng &lt;color=Highlight&gt;Băng Giá Cắt Da&lt;/color&gt;, &lt;color=Highlight&gt;Heavy Attack - Bản Ngã Đã Định&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Heavy Attack - Băng Giá: Bản Ngã Đã Định&lt;/color&gt;.
+Tiêu hao STA và 3 tầng &lt;color=Highlight&gt;Băng Giá Cắt Da&lt;/color&gt; để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, đồng thời nhận 1 điểm &lt;color=Highlight&gt;Kiếm Rèn Băng Giá&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18267,8 +18267,8 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để vào trạng thái nạp, trong đó Hiyuki liên tục tiêu hao &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt;. Thả ra để gây &lt;color=Ice&gt;Glacio DMG&lt;/color&gt;, lượng sát thương tỉ lệ thuận với số &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; đã tiêu hao. Kỹ năng này cũng có thể được sử dụng bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;. Khi sử dụng theo cách này, kỹ năng sẽ không tiêu hao &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; nếu chưa đầy và tiêu hao toàn bộ &lt;color=Highlight&gt;Snowforged Blade&lt;/color&gt; nếu đã đầy.
-Sau khi sử dụng kỹ năng này, Hiyuki để lại &lt;color=Highlight&gt;Foreclaimed Self&lt;/color&gt;.</t>
+          <t>Giữ &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt; để vào trạng thái nạp, trong đó Hiyuki liên tục tiêu hao &lt;color=Highlight&gt;Kiếm Rèn Băng Giá&lt;/color&gt;. Thả ra để gây &lt;color=Ice&gt;Sát Thương Glacio&lt;/color&gt;, tỉ lệ thuận với lượng &lt;color=Highlight&gt;Kiếm Rèn Băng Giá&lt;/color&gt; đã tiêu hao. Kỹ năng này cũng có thể được kích hoạt bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} &lt;color=Highlight&gt;Resonance Liberation&lt;/color&gt;. Khi kích hoạt theo cách này, kỹ năng sẽ không tiêu hao &lt;color=Highlight&gt;Kiếm Rèn Băng Giá&lt;/color&gt; nếu chưa đầy và tiêu hao toàn bộ khi đã đầy.
+Sau khi sử dụng kỹ năng, Hiyuki để lại &lt;color=Highlight&gt;Bản Ngã Đã Định Trước&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Stage 1 Kỹ Năng Enhanced Resonance</t>
+          <t>Giai Đoạn 1 Resonance Skill Cường Hóa</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Stage 2 Kỹ Năng Enhanced Resonance</t>
+          <t>Giai Đoạn 2 Resonance Skill Cường Hóa</t>
         </is>
       </c>
     </row>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Basic Attack - Stagecraft Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack - Hình Thức Stagecraft&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Heavy Attack - Stagecraft Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack - Hình Thức Stagecraft&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18593,7 +18593,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Resonance Skill - Stagecraft Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng hưởng - Hình thái Diễn xuất&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Enhanced Resonance Skill- Stagecraft Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Nâng Cao - Hình Thức Stagecraft&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Resonance Liberation - Stagecraft Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation - Hình Thức Stagecraft&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Basic Attack - Breakdown Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Basic Attack - Hình Thức Breakdown&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18853,7 +18853,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Heavy Attack - Breakdown Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack - Hình Thức Breakdown&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18918,7 +18918,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Mid-air Heavy Attack - Breakdown Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Heavy Attack Giữa Không - Hình Thức Breakdown&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -18983,7 +18983,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Resonance Skill - Breakdown Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Kỹ năng Cộng hưởng - Hình thái Phân rã&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Enhanced Resonance Skill - Breakdown Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Nâng Cao - Hình Thức Breakdown&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Resonance Liberation - Breakdown Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Liberation - Hình Thức Breakdown&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Denia: &lt;color=#d4bf5f&gt;Enhanced Resonance Skill - Breakdown Form&lt;/color&gt;</t>
+          <t>Denia: &lt;color=#d4bf5f&gt;Hướng dẫn Resonance Skill Nâng Cao - Hình Thức Breakdown&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19243,7 +19243,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi &lt;color=Highlight&gt;Hạt Hư Không&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19308,7 +19308,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Hạt Hư Không&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
+          <t>Tiêu hao STA để thực hiện Đòn Lao Xuống từ trên không, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Hạt Hư Không&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19438,7 +19438,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Thu hút mục tiêu xung quanh, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
+          <t>Thu hút mục tiêu xung quanh, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19503,7 +19503,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Thu hút mục tiêu xung quanh, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
+          <t>Thu hút mục tiêu xung quanh, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và hồi phục &lt;color=Highlight&gt;Void Particle&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19568,7 +19568,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và chuyển sang &lt;color=Highlight&gt;Breakdown Form&lt;/color&gt;.</t>
+          <t>Gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và chuyển sang &lt;color=Highlight&gt;Dạng Phân Rã&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19634,8 +19634,8 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và tích năng lượng cho &lt;color=Highlight&gt;Resonance Liberation - Breakdown Form&lt;/color&gt;.
-Tiêu hao &lt;color=Highlight&gt;Void Particle&lt;/color&gt; để tăng sát thương kỹ năng.</t>
+          <t>Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và tích năng lượng cho &lt;color=Highlight&gt;Resonance Liberation - Hình Thái Phá Hủy&lt;/color&gt;.
+Tiêu hao &lt;color=Highlight&gt;Hạt Hư Không&lt;/color&gt; để tăng DMG kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -19701,8 +19701,8 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tiêu hao STA để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và nạp &lt;color=Highlight&gt;Resonance Liberation - Breakdown Form&lt;/color&gt;.
-Tiêu hao &lt;color=Highlight&gt;Void Particle&lt;/color&gt; để tăng sát thương kỹ năng.</t>
+          <t>Tiêu hao STA để gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và nạp &lt;color=Highlight&gt;Resonance Liberation - Hình Thái Phân Rã&lt;/color&gt;.
+Tiêu hao &lt;color=Highlight&gt;Hạt Hư Không&lt;/color&gt; để tăng DMG kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -19768,8 +19768,8 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; giữa không trung để thực hiện Đòn Lao Xuống từ trên không, tiêu hao STA, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và nạp &lt;color=Highlight&gt;Resonance Liberation - Breakdown Form&lt;/color&gt;.
-Tiêu hao &lt;color=Highlight&gt;Void Particle&lt;/color&gt; để tăng sát thương kỹ năng.</t>
+          <t>Giữ &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; giữa không trung để thực hiện Đòn Lao Xuống từ trên không, tiêu hao STA, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và nạp &lt;color=Highlight&gt;Resonance Liberation - Hình Thái Phá Hủy&lt;/color&gt;.
+Tiêu hao &lt;color=Highlight&gt;Hạt Vô Định&lt;/color&gt; để tăng DMG kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -19834,7 +19834,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Thu hút mục tiêu xung quanh, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và nạp &lt;color=Highlight&gt;Resonance Liberation - Breakdown Form&lt;/color&gt;.</t>
+          <t>Thu hút mục tiêu xung quanh, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và nạp &lt;color=Highlight&gt;Resonance Liberation - Breakdown Form&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Khi &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt; đầy, tiêu hao toàn bộ &lt;color=Highlight&gt;Conformal Charge&lt;/color&gt; và &lt;color=Highlight&gt;Void Particle&lt;/color&gt; để sử dụng kỹ năng này, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; và chuyển sang &lt;color=Highlight&gt;Stagecraft Form&lt;/color&gt;.</t>
+          <t>Khi &lt;color=Highlight&gt;Điện Tích Đồng Dạng&lt;/color&gt; đầy, tiêu hao toàn bộ &lt;color=Highlight&gt;Điện Tích Đồng Dạng&lt;/color&gt; và &lt;color=Highlight&gt;Hạt Vô Định&lt;/color&gt; để sử dụng kỹ năng này, gây &lt;color=Fire&gt;Sát Thương Fusion&lt;/color&gt; và chuyển sang &lt;color=Highlight&gt;Hình Thái Diễn Xuất&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20031,7 +20031,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để vào tư thế sẵn sàng Dodge đòn và tích Chí. Nếu Dodge thành công đòn tấn công của kẻ địch, bỏ qua sát thương từ đòn đó, phản công gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt; và tích thêm Chí. Thả nút Resonance Skill để ngắt tư thế và tung đòn tấn công gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, đồng thời tích Chí.</t>
+          <t>Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để vào tư thế sẵn sàng né đòn và tích Chí. Nếu né tránh thành công đòn tấn công của kẻ địch, bỏ qua DMG từ đòn đó, phản công gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt; và tích thêm Chí. Thả nút Resonance Skill để ngắt tư thế và tung đòn tấn công gây &lt;color=Wind&gt;Sát Thương Aero&lt;/color&gt;, đồng thời tích Chí.</t>
         </is>
       </c>
     </row>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Khi đang ở trên không, chạm &lt;color=#ffd12f&gt;Dodge&lt;/color&gt; để kích hoạt &lt;color=#ffd12f&gt;Mid-Air Dodge&lt;/color&gt;.</t>
+          <t>Khi đang ở trên không, chạm &lt;color=#ffd12f&gt;Né Tránh&lt;/color&gt; để kích hoạt &lt;color=#ffd12f&gt;Né Tránh Giữa Không&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20161,7 +20161,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Stand gần Đèn Cảm Ứng và chạm vào nút "Kích hoạt" để kích hoạt.</t>
+          <t>Đứng gần Đèn Cảm Ứng và chạm vào nút "Kích hoạt" để kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -20227,8 +20227,8 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#ffd12f&gt;stick&lt;/color&gt; và nhấn &lt;color=#ffd12f&gt;Dodge&lt;/color&gt; gần tường để thực hiện &lt;color=#ffd12f&gt;Wall Dash&lt;/color&gt;.
-Đập Wall tiêu hao &lt;color=#ffd12f&gt;STA&lt;/color&gt; và sẽ tự động kết thúc khi STA cạn kiệt.</t>
+          <t>Dùng &lt;color=#ffd12f&gt;gậy&lt;/color&gt; và nhấn &lt;color=#ffd12f&gt;Nút Né Tránh&lt;/color&gt; gần tường để thực hiện &lt;color=#ffd12f&gt;Đập Tường&lt;/color&gt;.
+Đập Tường tiêu hao &lt;color=#ffd12f&gt;STA&lt;/color&gt; và sẽ tự động kết thúc khi STA cạn kiệt.</t>
         </is>
       </c>
     </row>
@@ -20305,19 +20305,19 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>["Equip Echoes"]
-Equip Echoes để nhận thuộc tính, Skills Echoes và các thưởng hiệu đặc biệt.
+          <t>["Trang Bị Echo"]
+Trang bị Echo để nhận thuộc tính, Kỹ Năng Echo và các thưởng hiệu đặc biệt.
 Kéo và thả để trang bị nhanh hơn.
 [CHI PHÍ]
-Số lượng Echoes bạn có thể trang bị bị giới hạn bởi tổng CHI PHÍ. CHI PHÍ của các Echoes đã trang bị không được vượt quá giới hạn CHI PHÍ hiện tại.
-Thu thập Echoes loại mới để nâng cấp cấp độ Data Bank và tăng giới hạn CHI PHÍ.
-[Skills Echoes]
-Echoes được lắp vào vị trí chính (vị trí đầu tiên) có thể kích hoạt Skills Echoes tương ứng. Switch nút "Tóm Tắt" để xem mô tả chi tiết và ngắn gọn về Skills Echoes.
-Khi Skills Echoes đang được sử dụng, Echoes chính tương ứng tạm thời không thể thay thế hoặc gỡ bỏ.
-[Sonata Effect]
-Mỗi Echoes đều mang theo "Sonata" riêng. Khi số lượng Echoes cùng loại Sonata đạt 2 hoặc 5, Sonata Effect tương ứng sẽ được kích hoạt.
-Nhiều Echoes cùng loại Sonata và cùng tên trang bị chỉ được tính một lần cho Sonata Effect.
-Echoes cùng tên có thể mang Sonata khác nhau do sự khác biệt về dữ liệu.</t>
+Số lượng Echo bạn có thể trang bị bị giới hạn bởi tổng CHI PHÍ. CHI PHÍ của các Echo đã trang bị không được vượt quá giới hạn CHI PHÍ hiện tại.
+Thu thập Echo loại mới để nâng cấp cấp độ Kho Dữ Liệu và tăng giới hạn CHI PHÍ.
+[Kỹ Năng Echo]
+Echo được lắp vào vị trí chính (vị trí đầu tiên) có thể kích hoạt Kỹ Năng Echo tương ứng. Chuyển nút "Tóm Tắt" để xem mô tả chi tiết và ngắn gọn về Kỹ Năng Echo.
+Khi Kỹ Năng Echo đang được sử dụng, Echo chính tương ứng tạm thời không thể thay thế hoặc gỡ bỏ.
+[Hiệu Ứng Sonata]
+Mỗi Echo đều mang theo "Sonata" riêng. Khi số lượng Echo cùng loại Sonata đạt 2 hoặc 5, Hiệu Ứng Sonata tương ứng sẽ được kích hoạt.
+Nhiều Echo cùng loại Sonata và cùng tên trang bị chỉ được tính một lần cho Hiệu Ứng Sonata.
+Echo cùng tên có thể mang Sonata khác nhau do sự khác biệt về dữ liệu.</t>
         </is>
       </c>
     </row>
@@ -20386,11 +20386,11 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Trong chuỗi thử thách này, bạn được mặc định nhận "Roaming Variable".
--Kỹ năng Grapple không bước vào Cooldown chiêu trong một khoảng thời gian ngắn sau khi kích hoạt.
-&lt;color=Highlight&gt;1. Each Infinite Battle Simulation realm has three Charting Nodes available for challenge.
-2. Each Charting Node requires a certain amount of Tactic Points to unlock.
-3. Mở Supply Chests to obtain Tactic Points in the Infinite Battle Simulation.&lt;/color&gt;</t>
+          <t>Trong chuỗi thử thách này, bạn được mặc định nhận "Biến Số Lang Thang".
+-Kỹ năng Grapple không bước vào Thời gian hồi chiêu trong một khoảng thời gian ngắn sau khi kích hoạt.
+&lt;color=Highlight&gt;1. Mỗi lãnh địa Infinite Battle Simulation có ba Charting Node để thử thách.
+2. Mỗi Charting Node yêu cầu một lượng Tactic Points nhất định để mở khóa.
+3. Mở Supply Chest để nhận Tactic Points trong Infinite Battle Simulation.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20460,12 +20460,12 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Trong loạt thử thách này, bạn được mặc định nhận "Speeding Variable".
+          <t>Trong loạt thử thách này, bạn được mặc định nhận "Biến Số Tăng Tốc".
 -Tốc độ di chuyển của Resonator được tăng lên mặc định.
--Lao nhanh sẽ hất tung kẻ địch lên không và gây sát thương. Hiệu ứng này kéo dài 10 giây và sẽ bị loại bỏ khi chuyển sang Resonator khác, với thời gian Cooldown là 10 giây.
-&lt;color=Highlight&gt;1. Each Infinite Battle Simulation realm has three Charting Nodes available for challenge.
-2. Each Charting Node requires a certain amount of Tactic Points to unlock.
-3. Mở Supply Chests to obtain Tactic Points in the Infinite Battle Simulation.&lt;/color&gt;</t>
+-Lao nhanh sẽ hất tung kẻ địch lên không và gây DMG. Hiệu ứng này kéo dài 10 giây và sẽ bị loại bỏ khi chuyển sang Resonator khác, với thời gian Hồi Chiêu là 10 giây.
+&lt;color=Highlight&gt;1. Mỗi khu vực Mô Phỏng Chiến Đấu Vô Hạn có ba Nút Lập Bản Đồ để thử thách.
+2. Mỗi Nút Lập Bản Đồ yêu cầu một lượng Điểm Chiến Thuật nhất định để mở khóa.
+3. Mở Rương Vật Tư để nhận Điểm Chiến Thuật trong Mô Phỏng Chiến Đấu Vô Hạn.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -20536,10 +20536,10 @@
       <c r="M295" t="inlineStr">
         <is>
           <t>Về Sự Kiện
-Chi nhánh Ragunna của Pioneer Association đang chuẩn bị ra mắt dòng sản phẩm mới. Để đạt chỉ tiêu doanh số do cấp trên đề ra, Alannah đang tìm kiếm một cố vấn đáng tin cậy để hỗ trợ...
+Chi nhánh Ragunna của Hiệp Hội Tiên Phong đang chuẩn bị ra mắt dòng sản phẩm mới. Để đạt chỉ tiêu doanh số do cấp trên đề ra, Alannah đang tìm kiếm một cố vấn đáng tin cậy để hỗ trợ...
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 14.
-Event Rules
+Quy Tắc Sự Kiện
 Alannah sẽ tung ra một nhiệm vụ điều tra mới mỗi ngày. Hoàn thành các khảo sát để nhận phần thưởng tương ứng và có cái nhìn thoáng qua về thế giới Rinascita!</t>
         </is>
       </c>
@@ -20636,24 +20636,24 @@
 May mắn thay, một con mèo trắng xuất hiện, dẫn lối đưa ngươi trở về, giúp tìm lại những đồng đội bị lạc trong cõi mộng. Cùng nhau, các ngươi chiến đấu chống lại những bóng tối hỗn mang đen tối nhất.
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 17.
-[Dreamscape Odyssey]
-Tham gia cùng chú mèo trắng kỳ lạ giải cứu Resonators đồng hành khỏi cõi Mộng Ảo của họ. Cùng nhau, các ngươi sẽ lặn sâu vào Somnoire để khám phá sự thật đằng sau những cơn ác mộng. Mỗi trong số 6 cõi Mộng Ảo sẽ mang đến phần thưởng độc đáo khi hoàn thành.
+[Hành Trình Mộng Ảo]
+Tham gia cùng chú mèo trắng kỳ lạ giải cứu các Resonator đồng hành khỏi cõi Mộng Ảo của họ. Cùng nhau, các ngươi sẽ lặn sâu vào Somnoire để khám phá sự thật đằng sau những cơn ác mộng. Mỗi trong số 6 cõi Mộng Ảo sẽ mang đến phần thưởng độc đáo khi hoàn thành.
 [Kẻ Đuổi Theo Vết Rạn]
 Những cơn ác mộng đã xé toạc bức màn thực tại, gieo rắc hỗn loạn khắp thế giới. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint từ chú mèo trắng kỳ lạ.
-Hoàn thành "Dreamscape Odyssey: Ngọn Núi và Sáu Đồng Tín" để mở khóa "Kẻ Đuổi Theo Vết Rạn".
+Hoàn thành "Hành Trình Mộng Ảo: Ngọn Núi và Sáu Đồng Tín" để mở khóa "Kẻ Đuổi Theo Vết Rạn".
 Mỗi trong số 6 giai đoạn thử thách sẽ mang đến phần thưởng độc đáo khi hoàn thành.
-[Nightmare Revisits]
-Bóng tối u ám nhìn ngươi bằng đôi mắt rực lửa, như thể muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin cậy, kết nối tâm trí và tinh thần, sống lại trận chiến huy hoàng chống lại ác mộng luôn rình rập. Đối đầu với Black Cat một lần nữa cùng Resonators mà ngươi lựa chọn. Lần này, thử thách chiến đấu sẽ có những biến thể mới thú vị. Hãy sử dụng sức mạnh của Dream Link để giành lợi thế!
-Hoàn thành "Khi Night Gõ Cửa" để mở khóa "Nightmare Revisits".
+[Ác Mộng Quay Trở Lại]
+Bóng tối u ám nhìn ngươi bằng đôi mắt rực lửa, như thể muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin cậy, kết nối tâm trí và tinh thần, sống lại trận chiến huy hoàng chống lại ác mộng luôn rình rập. Đối đầu với Black Cat một lần nữa cùng các Resonator mà ngươi lựa chọn. Lần này, thử thách chiến đấu sẽ có những biến thể mới thú vị. Hãy sử dụng sức mạnh của Dream Link để giành lợi thế!
+Hoàn thành "Khi Đêm Gõ Cửa" để mở khóa "Ác Mộng Quay Trở Lại".
 Mỗi trong số 6 giai đoạn thử thách sẽ mang đến phần thưởng độc đáo khi hoàn thành.
-[Dream Shard]
-Hoàn thành Kẻ Đuổi Theo Vết Rạn, Nightmare Revisits và nhiệm vụ "Khi Night Gõ Cửa" để nhận Dream Shard.
-Thu thập đủ số lượng Dream Shard cần thiết để mở khóa phần thưởng theo từng mốc.
-Dream Shard có thể thu thập bất cứ lúc nào bằng cách tham gia sự kiện.
-[Limited-Time Reward]
-Hoàn thành các mục tiêu Limited-Time Reward để nhận phần thưởng độc quyền, bao gồm Vũ Khí 4-Star Nổi Bật "Somnoire Anchor" và Dự Phóng Vũ Khí Nổi Bật "Projection: Somnoire Anchor".
+[Mảnh Giấc Mơ]
+Hoàn thành Kẻ Đuổi Theo Vết Rạn, Ác Mộng Quay Trở Lại và nhiệm vụ "Khi Đêm Gõ Cửa" để nhận Mảnh Giấc Mơ.
+Thu thập đủ số lượng Mảnh Giấc Mơ cần thiết để mở khóa phần thưởng theo từng mốc.
+Mảnh Giấc Mơ có thể thu thập bất cứ lúc nào bằng cách tham gia sự kiện.
+[Phần Thưởng Giới Hạn]
+Hoàn thành các mục tiêu Phần Thưởng Giới Hạn để nhận phần thưởng độc quyền, bao gồm Vũ Khí 4 Sao Nổi Bật "Somnoire Anchor" và Dự Phóng Vũ Khí Nổi Bật "Projection: Somnoire Anchor".
 [Lưu ý]
-Các mục tiêu Limited-Time Reward sẽ hết hạn khi sự kiện kết thúc, nhưng ngươi vẫn có thể tiếp tục thử thách các giai đoạn sau đó để nhận phần thưởng tiêu chuẩn.</t>
+Các mục tiêu Phần Thưởng Giới Hạn sẽ hết hạn khi sự kiện kết thúc, nhưng ngươi vẫn có thể tiếp tục thử thách các giai đoạn sau đó để nhận phần thưởng tiêu chuẩn.</t>
         </is>
       </c>
     </row>
@@ -20749,24 +20749,24 @@
 May mắn thay, một con mèo trắng xuất hiện, dẫn lối đưa ngươi trở về, giúp tìm lại những đồng đội bị lạc trong cõi mộng. Cùng nhau, các ngươi chiến đấu chống lại những bóng tối hỗn mang đen tối nhất.
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 17.
-[Dreamscape Odyssey]
-Tham gia cùng chú mèo trắng kỳ lạ giải cứu Resonators đồng hành khỏi cõi Mộng Ảo của họ. Cùng nhau, các ngươi sẽ lặn sâu vào Somnoire để khám phá sự thật đằng sau những cơn ác mộng. Mỗi trong số 6 cõi Mộng Ảo sẽ mang đến phần thưởng độc đáo khi hoàn thành.
+[Hành Trình Mộng Ảo]
+Tham gia cùng chú mèo trắng kỳ lạ giải cứu các Resonator đồng hành khỏi cõi Mộng Ảo của họ. Cùng nhau, các ngươi sẽ lặn sâu vào Somnoire để khám phá sự thật đằng sau những cơn ác mộng. Mỗi trong số 6 cõi Mộng Ảo sẽ mang đến phần thưởng độc đáo khi hoàn thành.
 [Kẻ Đuổi Theo Vết Rạn]
 Những cơn ác mộng đã xé toạc bức màn thực tại, gieo rắc hỗn loạn khắp thế giới. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint từ chú mèo trắng kỳ lạ.
-Hoàn thành "Dreamscape Odyssey: Ngọn Núi và Sáu Đồng Tín" để mở khóa "Kẻ Đuổi Theo Vết Rạn".
+Hoàn thành "Hành Trình Mộng Ảo: Ngọn Núi và Sáu Đồng Tín" để mở khóa "Kẻ Đuổi Theo Vết Rạn".
 Mỗi trong số 6 giai đoạn thử thách sẽ mang đến phần thưởng độc đáo khi hoàn thành.
-[Nightmare Revisits]
-Bóng tối u ám nhìn ngươi bằng đôi mắt rực lửa, như thể muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin cậy, kết nối tâm trí và tinh thần, sống lại trận chiến huy hoàng chống lại ác mộng luôn rình rập. Đối đầu với Black Cat một lần nữa cùng Resonators mà ngươi lựa chọn. Lần này, thử thách chiến đấu sẽ có những biến thể mới thú vị. Hãy sử dụng sức mạnh của Dream Link để giành lợi thế!
-Hoàn thành "Khi Night Gõ Cửa" để mở khóa "Nightmare Revisits".
+[Ác Mộng Quay Trở Lại]
+Bóng tối u ám nhìn ngươi bằng đôi mắt rực lửa, như thể muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin cậy, kết nối tâm trí và tinh thần, sống lại trận chiến huy hoàng chống lại ác mộng luôn rình rập. Đối đầu với Black Cat một lần nữa cùng các Resonator mà ngươi lựa chọn. Lần này, thử thách chiến đấu sẽ có những biến thể mới thú vị. Hãy sử dụng sức mạnh của Dream Link để giành lợi thế!
+Hoàn thành "Khi Đêm Gõ Cửa" để mở khóa "Ác Mộng Quay Trở Lại".
 Mỗi trong số 6 giai đoạn thử thách sẽ mang đến phần thưởng độc đáo khi hoàn thành.
-[Dream Shard]
-Hoàn thành Kẻ Đuổi Theo Vết Rạn, Nightmare Revisits và nhiệm vụ "Khi Night Gõ Cửa" để nhận Dream Shard.
-Thu thập đủ số lượng Dream Shard cần thiết để mở khóa phần thưởng theo từng mốc.
-Dream Shard có thể thu thập bất cứ lúc nào bằng cách tham gia sự kiện.
-[Limited-Time Reward]
-Hoàn thành các mục tiêu Limited-Time Reward để nhận phần thưởng độc quyền, bao gồm Vũ Khí 4-Star Nổi Bật "Somnoire Anchor" và Dự Phóng Vũ Khí Nổi Bật "Projection: Somnoire Anchor".
+[Mảnh Giấc Mơ]
+Hoàn thành Kẻ Đuổi Theo Vết Rạn, Ác Mộng Quay Trở Lại và nhiệm vụ "Khi Đêm Gõ Cửa" để nhận Mảnh Giấc Mơ.
+Thu thập đủ số lượng Mảnh Giấc Mơ cần thiết để mở khóa phần thưởng theo từng mốc.
+Mảnh Giấc Mơ có thể thu thập bất cứ lúc nào bằng cách tham gia sự kiện.
+[Phần Thưởng Giới Hạn]
+Hoàn thành các mục tiêu Phần Thưởng Giới Hạn để nhận phần thưởng độc quyền, bao gồm Vũ Khí 4 Sao Nổi Bật "Somnoire Anchor" và Dự Phóng Vũ Khí Nổi Bật "Projection: Somnoire Anchor".
 [Lưu ý]
-Các mục tiêu Limited-Time Reward sẽ hết hạn khi sự kiện kết thúc, nhưng ngươi vẫn có thể tiếp tục thử thách các giai đoạn sau đó để nhận phần thưởng tiêu chuẩn.</t>
+Các mục tiêu Phần Thưởng Giới Hạn sẽ hết hạn khi sự kiện kết thúc, nhưng ngươi vẫn có thể tiếp tục thử thách các giai đoạn sau đó để nhận phần thưởng tiêu chuẩn.</t>
         </is>
       </c>
     </row>
@@ -20831,7 +20831,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Nightmares đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
+          <t>Ác Mộng đã xé toạc màn thực tại, gieo rắc hỗn loạn khắp thế gian. Chỉ còn mình ngươi có thể khôi phục trật tự đang sụp đổ, với ân huệ huyền bí Illusive Sprint nhận được từ con mèo trắng kỳ lạ.</t>
         </is>
       </c>
     </row>
@@ -20923,27 +20923,27 @@
         <is>
           <t>Về Nội Dung
 Ánh mắt rực lửa của bóng tối đang dõi theo ngươi, như thể muốn kéo ngươi trở lại vực thẳm vô tận. Hãy bước vào Somnoire cùng những người đồng hành đáng tin cậy, kết nối tâm trí và tinh thần, rồi sống lại trận chiến hào hùng chống lại cơn ác mộng luôn rình rập.
-Tái hiện trận chiến đỉnh cao cùng Resonators mà ngươi lựa chọn. Sử dụng sức mạnh của Dream Link để giành lợi thế trong cuộc chiến này!
+Tái hiện trận chiến đỉnh cao cùng các Resonator mà ngươi lựa chọn. Sử dụng sức mạnh của Dream Link để giành lợi thế trong cuộc chiến này!
 Mỗi trong số 6 giai đoạn thử thách sẽ mang đến phần thưởng độc đáo khi hoàn thành.
 Đội Hình
-Chọn 1 Main Resonators và 2 Resonators Hỗ Trợ để bắt đầu thử thách.
-Ngươi chỉ điều khiển Main Resonators, trong khi Resonators Hỗ Trợ sẽ ở lại chiến trường và tự động chiến đấu bên cạnh ngươi.
-Trong mùa sự kiện này, Resonators có sẵn bao gồm: Rover-Spectro, Encore, Yinlin, Changli, Zhezhi, Camellya và Lumi.
+Chọn 1 Resonator Chính và 2 Resonator Hỗ Trợ để bắt đầu thử thách.
+Ngươi chỉ điều khiển Resonator Chính, trong khi các Resonator Hỗ Trợ sẽ ở lại chiến trường và tự động chiến đấu bên cạnh ngươi.
+Trong mùa sự kiện này, các Resonator có sẵn bao gồm: Rover-Spectro, Encore, Yinlin, Changli, Zhezhi, Camellya và Lumi.
 Dream Link
 "Dream Link" có sẵn trong thử thách Nightmare Revisits:
 Khi Năng Lượng Đồng Bộ của ngươi đạt tối đa, hãy kích hoạt Resonance Liberation của tất cả thành viên trong đội liên tiếp để kích hoạt Link Field.
 Khi Link Field được kích hoạt:
-1. Attack, Crit. Rate, Crit. DMG, Attack Speed và Movement Speed của tất cả thành viên trong đội được tăng cường đáng kể, đồng thời Cooldown chiêu của Resonance Skill được rút ngắn.
+1. ATK, Crit. Rate, Crit. DMG, Tốc Độ ATK và Tốc Độ Di Chuyển của tất cả thành viên trong đội được tăng cường đáng kể, đồng thời Cooldown chiêu của Resonance Skill được rút ngắn.
 2. Một Vùng Trì Trệ được tạo ra, khiến kẻ địch trong Link Field bị bất động.
-3. Kẻ địch gần đó sẽ bị kéo về phía Resonators khi kích hoạt.
+3. Kẻ địch gần đó sẽ bị kéo về phía các Resonator khi kích hoạt.
 4. Khi Link Field kết thúc, đội của ngươi sẽ nhận được hiệu ứng hồi phục HP liên tục.
 Sinister Calling
 Bảo vệ [Dreamscape Telephone] cho đến khi đánh bại tất cả cơn ác mộng.
-Points số được tính như sau: Thời Gian Còn Lại × Hệ Số Thời Gian + Độ Nguyên Vẹn [Dreamscape Telephone] × Hệ Số Độ Nguyên Vẹn + Points từ việc đánh bại kẻ địch.
+Điểm số được tính như sau: Thời Gian Còn Lại × Hệ Số Thời Gian + Độ Nguyên Vẹn [Dreamscape Telephone] × Hệ Số Độ Nguyên Vẹn + Điểm từ việc đánh bại kẻ địch.
 Tiêu diệt tất cả kẻ địch trong một đợt trước khi đếm ngược kết thúc để nhận thêm điểm Thời Gian.
 Terror Reborn
 Tiêu diệt tất cả những cơn ác mộng trong giấc mơ sâu.
-Points số được tính như sau: Thời Gian Còn Lại × Hệ Số Thời Gian + Points từ việc đánh bại kẻ địch.
+Điểm số được tính như sau: Thời Gian Còn Lại × Hệ Số Thời Gian + Điểm từ việc đánh bại kẻ địch.
 Tiêu diệt tất cả kẻ địch trong một đợt trước khi đếm ngược kết thúc để nhận thêm điểm Thời Gian.
 Phần Thưởng
 Các thử thách điểm số sẽ luôn mở. Đạt các mốc mục tiêu để nhận nhiều phần thưởng đa dạng.</t>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Chạm {0} để tung Resonance Liberation và kích hoạt Dream Link</t>
+          <t>Chạm {0} để tung Resonance Liberation và kích hoạt Liên Kết Giấc Mơ</t>
         </is>
       </c>
     </row>
@@ -21141,7 +21141,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Trong Tower of Adversity, khi hoàn thành một thử thách, &lt;color=#c19f51&gt;Vigor&lt;/color&gt; của Resonators tham gia sẽ giảm một lượng nhất định. Khi Vigor của một Resonators cạn kiệt, họ &lt;color=#c19f51&gt;no longer take part in new challenges&lt;/color&gt;. Vigor không tự phục hồi theo thời gian, nhưng cậu có thể sử dụng tùy chọn [Đặt lại] ở từng Tầng để hồi phục Vigor.</t>
+          <t>Trong Tháp Nghịch Cảnh, khi hoàn thành một thử thách, &lt;color=#c19f51&gt;Sinh Lực&lt;/color&gt; của các Resonator tham gia sẽ giảm một lượng nhất định. Khi Sinh Lực của một Resonator cạn kiệt, họ &lt;color=#c19f51&gt;không thể tham gia thử thách mới&lt;/color&gt;. Sinh Lực không tự phục hồi theo thời gian, nhưng cậu có thể sử dụng tùy chọn [Đặt lại] ở từng Tầng để hồi phục Sinh Lực.</t>
         </is>
       </c>
     </row>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Rewards Huy Chương ở Stable Zone, Khu Thí Nghiệm và Khu Vượt Giới chỉ có thể nhận một lần. Tuy nhiên, các thử thách ở Hazard Zone sẽ &lt;color=#c19f51&gt;periodically reset&lt;/color&gt;, cùng với tiến trình của bạn, mang đến kẻ địch mới, mục tiêu thử thách mới, Hiệu Ứng Khu Vực và phần thưởng mới. Hãy đối mặt với thử thách lần nữa để giành Huy Chương và &lt;color=#c19f51&gt;claim fresh rewards.&lt;/color&gt;</t>
+          <t>Phần thưởng Huy Chương ở Khu Vực Ổn Định, Khu Thí Nghiệm và Khu Vượt Giới chỉ có thể nhận một lần. Tuy nhiên, các thử thách ở Khu Nguy Hiểm sẽ &lt;color=#c19f51&gt;được thiết lập lại định kỳ&lt;/color&gt;, cùng với tiến trình của bạn, mang đến kẻ địch mới, mục tiêu thử thách mới, Hiệu Ứng Khu Vực và phần thưởng mới. Hãy đối mặt với thử thách lần nữa để giành Huy Chương và &lt;color=#c19f51&gt;nhận phần thưởng mới.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -21273,7 +21273,7 @@
       <c r="M304" t="inlineStr">
         <is>
           <t>Gây sát thương để tích Lượng Đồng Bộ. Khi Năng Lượng Liên Kết đầy, chuẩn bị kích hoạt Giấc Mơ Liên Kết.
-Dodge thành công và &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt; sẽ cung cấp nhiều Lượng Đồng Bộ.</t>
+Né thành công và &lt;color=#ffd12f&gt;Phản Đòn&lt;/color&gt; sẽ cung cấp nhiều Lượng Đồng Bộ.</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Đồng Bộ Ảo chỉ kéo dài 10 giây. Nếu cậu không kích hoạt Resonance Liberation của Resonator tiếp theo trong thời gian đó, toàn bộ Năng Lượng Đồng Bộ sẽ mất và quá trình đồng bộ sẽ kết thúc.</t>
+          <t>Đồng Bộ Ảo chỉ kéo dài 10 giây. Nếu cậu không kích hoạt Giải Cứu Cộng Hưởng của Resonator tiếp theo trong thời gian đó, toàn bộ Năng Lượng Đồng Bộ sẽ mất và quá trình đồng bộ sẽ kết thúc.</t>
         </is>
       </c>
     </row>
@@ -21475,9 +21475,9 @@
         <is>
           <t>Kích hoạt Resonance Liberation trong trạng thái Đồng Bộ Ảo sẽ kích hoạt trạng thái Liên Kết Mộng và mở ra Trường Liên Kết.
 Khi Trường Liên Kết hoạt động:
-1. Tấn Công, Crit. Rate và Crit. DMG của tất cả thành viên đội được tăng cường đáng kể, đồng thời Cooldown chiêu Resonance Skill cũng giảm mạnh.
+1. ATK, Crit. Rate và Crit. DMG của tất cả thành viên đội được tăng cường đáng kể, đồng thời thời gian hồi chiêu Resonance Skill cũng giảm mạnh.
 2. Một Vùng Trì Trệ được tạo ra, khiến kẻ địch trong Trường Liên Kết bị bất động.
-3. Kẻ địch gần đó sẽ bị kéo về phía Resonators của bạn khi kích hoạt.
+3. Kẻ địch gần đó sẽ bị kéo về phía Resonator của bạn khi kích hoạt.
 4. Khi Trường Liên Kết kết thúc, đội của bạn sẽ nhận được hồi máu liên tục.</t>
         </is>
       </c>
@@ -21673,7 +21673,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Resonance Skill Nâng Cao đẩy mục tiêu vào trạng thái &lt;color=Highlight&gt;Hazy Dream&lt;/color&gt;.</t>
+          <t>Resonance Skill Nâng Cao đẩy mục tiêu vào trạng thái &lt;color=Highlight&gt;Giấc Mơ Mơ Hồ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21738,7 +21738,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Resonance Skill Nâng Cao đẩy mục tiêu vào trạng thái &lt;color=Highlight&gt;Hazy Dream&lt;/color&gt;.</t>
+          <t>Resonance Skill Nâng Cao đẩy mục tiêu vào trạng thái &lt;color=Highlight&gt;Giấc Mơ Mơ Hồ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21803,7 +21803,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Resonance Skill Nâng Cao đẩy mục tiêu vào trạng thái &lt;color=Highlight&gt;Hazy Dream&lt;/color&gt;.</t>
+          <t>Resonance Skill Nâng Cao đẩy mục tiêu vào trạng thái &lt;color=Highlight&gt;Giấc Mơ Mơ Hồ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Sử Dụng Tiện Ích Tập Hợp Kẻ Địch Của Roccia</t>
+          <t>Sử dụng Tiện Ích Thu Hút Kẻ Địch của Roccia</t>
         </is>
       </c>
     </row>
@@ -22014,15 +22014,15 @@
 Học viện đang thử nghiệm một loại công nghệ mới, được đồn đoán có khả năng mô phỏng những kẻ địch mạnh mẽ để hỗ trợ huấn luyện chiến đấu cho binh lính...
 Điều Kiện Tham Gia
 Đạt Cấp Liên Minh 14.
-Event Rules
+Quy Tắc Sự Kiện
 1. Trong Tactical Simulacra II, hãy đối đầu với làn sóng kẻ địch hùng mạnh bằng cách sử dụng các hiệu ứng đặc biệt trong các miền mô phỏng khác nhau.
 2. Khi hoàn thành nhiều thử thách hơn, bạn sẽ mở khóa thêm nhiều hiệu ứng đặc biệt để hỗ trợ trong các thử thách tiếp theo.
-3. Kết quả của mỗi thử thách bao gồm ba phần: Points Quái Vật, Time Points và Technical Points.
-i. Points Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
-ii. Time Points được tính dựa trên thời gian còn lại khi hoàn thành thử thách. Càng đánh bại nhiều kẻ địch, hệ số chuyển đổi điểm càng cao.
-iii. Technical Points được tính cho mỗi lần Phản Công và Dodge thành công.
-Xếp Hạng Combat
-Duy trì tấn công kẻ địch sẽ cải thiện Xếp Hạng Combat của bạn, trong khi các động tác Dodge, Phản Công Dodge và Phản Công thành công sẽ mang lại hiệu quả tăng điểm cao hơn. Tuy nhiên, bị tấn công sẽ làm giảm đáng kể Xếp Hạng Combat của bạn.</t>
+3. Kết quả của mỗi thử thách bao gồm ba phần: Điểm Quái Vật, Điểm Thời Gian và Điểm Kỹ Thuật.
+i. Điểm Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
+ii. Điểm Thời Gian được tính dựa trên thời gian còn lại khi hoàn thành thử thách. Càng đánh bại nhiều kẻ địch, hệ số chuyển đổi điểm càng cao.
+iii. Điểm Kỹ Thuật được tính cho mỗi lần Phản Công và Né Tránh thành công.
+Xếp Hạng Chiến Đấu
+Duy trì tấn công kẻ địch sẽ cải thiện Xếp Hạng Chiến Đấu của bạn, trong khi các động tác Né Tránh, Phản Công Né Tránh và Phản Công thành công sẽ mang lại hiệu quả tăng điểm cao hơn. Tuy nhiên, bị tấn công sẽ làm giảm đáng kể Xếp Hạng Chiến Đấu của bạn.</t>
         </is>
       </c>
     </row>
@@ -22104,15 +22104,15 @@
 Dường như có ai đó vừa cập nhật chương trình mô phỏng chiến đấu bí ẩn đang gây sốt trên Huaxu Hive tại Học viện...
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 40.
-[Event Rules]
+[Quy Tắc Sự Kiện]
 1. Trong Pincer Maneuver Warriors, hãy đối đầu với làn sóng kẻ địch mạnh mẽ bằng cách điều khiển hai đội với các hiệu ứng đặc biệt trên hai chiến trường mô phỏng riêng biệt.
 2. Chiến trường mô phỏng cung cấp các hiệu ứng có lợi áp dụng cho cả hai đội hoặc chỉ dành riêng cho một đội.
 3. Có 4 giai đoạn với số lượng làn sóng kẻ địch giới hạn và 1 giai đoạn với làn sóng vô hạn.
 i. Ở các giai đoạn có số lượng kẻ địch giới hạn, bạn chỉ có thể tiến vào nửa sau trận chiến khi hết thời gian hoặc tiêu diệt hết kẻ địch.
 ii. Ở giai đoạn có làn sóng kẻ địch vô hạn, bạn chỉ có thể tiến vào nửa sau khi hết thời gian.
-4. Points kiếm được ở các giai đoạn có số lượng kẻ địch giới hạn bao gồm cả Time Points và Points Quái Vật, trong khi điểm ở giai đoạn có làn sóng vô hạn chỉ bao gồm Points Quái Vật.
-i. Points Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
-ii. Time Points được tính dựa trên thời gian còn lại khi hoàn thành thử thách.</t>
+4. Điểm kiếm được ở các giai đoạn có số lượng kẻ địch giới hạn bao gồm cả Điểm Thời Gian và Điểm Quái Vật, trong khi điểm ở giai đoạn có làn sóng vô hạn chỉ bao gồm Điểm Quái Vật.
+i. Điểm Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
+ii. Điểm Thời Gian được tính dựa trên thời gian còn lại khi hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -22199,9 +22199,9 @@
 3. Có các giai đoạn khác nhau với số lượng làn sóng kẻ địch giới hạn hoặc vô hạn.
 i. Ở các giai đoạn có số lượng làn sóng kẻ địch giới hạn, cậu chỉ có thể tiến vào nửa sau trận chiến khi hết giờ hoặc tiêu diệt hết kẻ địch.
 ii. Ở giai đoạn có số lượng làn sóng kẻ địch vô hạn, cậu chỉ có thể tiến vào nửa sau khi hết giờ.
-4. Points kiếm được ở các giai đoạn có số lượng làn sóng kẻ địch giới hạn bao gồm cả Time Points và Points Quái Vật, trong khi điểm ở giai đoạn có số lượng làn sóng vô hạn chỉ bao gồm Points Quái Vật.
-i. Points Quái Vật được tính khi tiêu diệt kẻ địch trong thử thách, với điểm thưởng cho mỗi làn sóng bị đánh bại.
-ii. Time Points được tính dựa trên thời gian còn lại khi hoàn thành thử thách.</t>
+4. Điểm kiếm được ở các giai đoạn có số lượng làn sóng kẻ địch giới hạn bao gồm cả Điểm Thời Gian và Điểm Quái Vật, trong khi điểm ở giai đoạn có số lượng làn sóng vô hạn chỉ bao gồm Điểm Quái Vật.
+i. Điểm Quái Vật được tính khi tiêu diệt kẻ địch trong thử thách, với điểm thưởng cho mỗi làn sóng bị đánh bại.
+ii. Điểm Thời Gian được tính dựa trên thời gian còn lại khi hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -22288,9 +22288,9 @@
 3. Có nhiều giai đoạn khác nhau với số lượng làn sóng kẻ địch giới hạn hoặc vô hạn.
 i. Ở các giai đoạn có số lượng làn sóng kẻ địch giới hạn, cậu chỉ có thể tiến vào nửa sau trận chiến khi hết thời gian hoặc tiêu diệt hết kẻ địch.
 ii. Ở giai đoạn có làn sóng kẻ địch vô hạn, cậu chỉ có thể tiến vào nửa sau khi hết thời gian.
-4. Points kiếm được ở các giai đoạn có số lượng làn sóng kẻ địch giới hạn bao gồm cả Time Points và Points Quái Vật, trong khi điểm ở giai đoạn có làn sóng vô hạn chỉ bao gồm Points Quái Vật.
-i. Points Quái Vật được tính khi đánh bại kẻ địch trong thử thách, với điểm thưởng cho mỗi làn sóng tiêu diệt.
-ii. Time Points được tính dựa trên thời gian còn lại khi hoàn thành thử thách.</t>
+4. Điểm kiếm được ở các giai đoạn có số lượng làn sóng kẻ địch giới hạn bao gồm cả Điểm Thời Gian và Điểm Quái Vật, trong khi điểm ở giai đoạn có làn sóng vô hạn chỉ bao gồm Điểm Quái Vật.
+i. Điểm Quái Vật được tính khi đánh bại kẻ địch trong thử thách, với điểm thưởng cho mỗi làn sóng tiêu diệt.
+ii. Điểm Thời Gian được tính dựa trên thời gian còn lại khi hoàn thành thử thách.</t>
         </is>
       </c>
     </row>
@@ -22360,8 +22360,8 @@
         <is>
           <t>Tăng cường Đội I: Khi sử dụng Resonance Skill trúng mục tiêu, đội nhận thêm 1 điểm Dấu Đà. Hiệu ứng kéo dài 4 giây.
 Hạ gục kẻ địch đặc biệt để nhận hiệu ứng tăng cường đặc biệt.
-Tăng cường Special 1: Khả năng chống gián đoạn của đội được tăng cường đáng kể trong 30 giây.
-Tăng cường Special 2: Đội nhận 100 Concerto Energy.</t>
+Tăng cường Đặc Biệt 1: Khả năng chống gián đoạn của đội được tăng cường đáng kể trong 30 giây.
+Tăng cường Đặc Biệt 2: Đội nhận 100 Concerto Energy.</t>
         </is>
       </c>
     </row>
@@ -22429,10 +22429,10 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội II: Kích hoạt Tác Động sẽ tăng 30% Tấn Công cho tất cả thành viên trong đội trong 30 giây.
+          <t>Hiệu ứng Đội II: Kích hoạt Tác Động sẽ tăng 30% ATK cho tất cả thành viên trong đội trong 30 giây.
 Hạ gục kẻ địch đặc biệt để nhận hiệu ứng tăng cường đặc biệt.
 Hiệu ứng đặc biệt 1: Khả năng chống gián đoạn của đội được tăng cường đáng kể trong 30 giây.
-Hiệu ứng đặc biệt 2: Đội nhận 100 Concerto Energy.</t>
+Hiệu ứng đặc biệt 2: Đội nhận 100 Năng Lượng Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -22500,10 +22500,10 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội I: Khi Resonator chủ động gây Crit. DMG Hệ Electro lên mục tiêu, đội nhận thêm 2 tầng Điện Ấn. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+          <t>Hiệu ứng Đội I: Khi Resonator chủ động gây Sát Thương Bạo Kích Hệ Electro lên mục tiêu, đội nhận thêm 2 tầng Điện Ấn. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
 Hạ gục kẻ địch đặc biệt để nhận hiệu ứng tăng cường đặc biệt.
 Hiệu ứng đặc biệt 1: Khả năng chống gián đoạn của đội được tăng cường đáng kể trong 30 giây.
-Hiệu ứng đặc biệt 2: Đội nhận 100 Concerto Energy.</t>
+Hiệu ứng đặc biệt 2: Đội nhận 100 Năng Lượng Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -22571,10 +22571,10 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội II: Khi Resonator chủ động gây Crit. DMG từ Đòn Phối Hợp lên mục tiêu, đội nhận thêm 1 tầng Điện Ấn. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+          <t>Hiệu ứng Đội II: Khi Resonator chủ động gây Sát Thương Bạo Kích từ Đòn Phối Hợp lên mục tiêu, đội nhận thêm 1 tầng Điện Ấn. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
 Hạ gục kẻ địch đặc biệt để nhận hiệu ứng tăng cường đặc biệt.
 Hiệu ứng đặc biệt 1: Khả năng chống gián đoạn của đội được tăng cường đáng kể trong 30 giây.
-Hiệu ứng đặc biệt 2: Đội nhận 100 Concerto Energy.</t>
+Hiệu ứng đặc biệt 2: Đội nhận 100 Năng Lượng Giao Hưởng.</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội II: Kích hoạt Tác Động sẽ tăng 30% Tấn Công cho tất cả thành viên trong đội trong 30 giây.</t>
+          <t>Hiệu ứng Đội II: Kích hoạt Tác Động sẽ tăng 30% ATK cho tất cả thành viên trong đội trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội I: Khi Resonator chủ động gây Crit. DMG Hệ Electro lên mục tiêu, đội nhận thêm 1 tầng Điện Ấn. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>Hiệu ứng Đội I: The team gains an extra stack of Thunder Mark when the active Resonator deals Critical Electro DMG to a target. This effect can be triggered once per second.</t>
         </is>
       </c>
     </row>
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội II: Khi Resonator chủ động gây Crit. DMG từ Đòn Phối Hợp lên mục tiêu, đội nhận thêm 1 tầng Điện Ấn. Hiệu ứng này có thể kích hoạt mỗi giây một lần.</t>
+          <t>Hiệu ứng Đội II: The team gains an extra stack of Thunder Mark when the active Resonator deals Critical Coordinated Attack DMG to a target. This effect can be triggered once per second.</t>
         </is>
       </c>
     </row>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Fae Ignis phát nổ khi bị đánh bại, gây sát thương lên các mục tiêu xung quanh. Hiệu ứng này sẽ không kích hoạt nếu nó bị đánh bại &lt;color=#ffd12f&gt;in trên không&lt;/color&gt;.</t>
+          <t>Fae Ignis phát nổ khi bị đánh bại, gây sát thương lên các mục tiêu xung quanh. Hiệu ứng này sẽ không kích hoạt nếu nó bị đánh bại &lt;color=#ffd12f&gt;trong không trung&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -22965,8 +22965,8 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless tấn công bằng tia laser, có thể chặn bằng &lt;color=#ffd12f&gt;Counterattacks&lt;/color&gt;.
-Phản Đòn thành công sẽ gây sát thương lớn lên Chop Chop: Headless.</t>
+          <t>Chop Chop: Headless attacks with laser beams, which can be blocked with &lt;color=#ffd12f&gt;Counterattacks&lt;/color&gt;.
+Successful Counterattacks deal great DMG to Chop Chop: Headless.</t>
         </is>
       </c>
     </row>
@@ -23032,7 +23032,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Ở chế độ phòng thủ, Sentry Construct có khả năng Giảm Sát Thương cao và phục hồi Năng Lượng Rung từ từ. &lt;color=#ffd12f&gt;Attacking it from behind&lt;/color&gt; sẽ vô hiệu hóa chế độ phòng thủ của nó.
+          <t>Ở chế độ phòng thủ, Sentry Construct có khả năng Giảm Sát Thương cao và phục hồi Năng Lượng Rung từ từ. &lt;color=#ffd12f&gt;Tấn công từ phía sau&lt;/color&gt; sẽ vô hiệu hóa chế độ phòng thủ của nó.
 Nếu bị tấn công khi đang ở trên không, nó sẽ mất nhiều Năng Lượng Rung hơn và dễ bị vô hiệu hóa hơn.</t>
         </is>
       </c>
@@ -23098,7 +23098,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Khi Chop Chop: Vô Đầu kết hợp với cối xay gió, các đòn tấn công của chúng có thể bị phản đòn bằng &lt;color=#ffd12f&gt;Questless Knight's Echo Skill&lt;/color&gt;, gây sát thương lớn.</t>
+          <t>Khi Chop Chop: Vô Đầu kết hợp với cối xay gió, các đòn tấn công của chúng có thể bị phản đòn bằng &lt;color=#ffd12f&gt;Kỹ Năng Hồi Âm Kỵ Sĩ Vô Nhiệm&lt;/color&gt;, gây DMG lớn.</t>
         </is>
       </c>
     </row>
@@ -23165,8 +23165,8 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Một &lt;color=#ffd12f&gt;beacon&lt;/color&gt; mà cậu từng tự đặt ra cho mình, chứa đựng sức mạnh và niềm tin để tiến về phía trước.
-Khả năng của &lt;color=#ffd12f&gt;Rover: Spectro&lt;/color&gt; đã được tăng cường. Resonance Liberation &lt;color=#ffd12f&gt;Echoing Orchestra&lt;/color&gt; và Resonance Skill &lt;color=#ffd12f&gt;Resonating Spin&lt;/color&gt; giờ đây sẽ gây hiệu ứng &lt;color=#ffd12f&gt;Spectro Frazzle Effect&lt;/color&gt; lên mục tiêu trong khi vẫn giữ nguyên hiệu ứng ban đầu.
+          <t>Một &lt;color=#ffd12f&gt;cột mốc&lt;/color&gt; mà cậu từng tự đặt ra cho mình, chứa đựng sức mạnh và niềm tin để tiến về phía trước.
+Khả năng của &lt;color=#ffd12f&gt;Rover: Spectro&lt;/color&gt; đã được tăng cường. Resonance Liberation &lt;color=#ffd12f&gt;Echoing Orchestra&lt;/color&gt; và Resonance Skill &lt;color=#ffd12f&gt;Resonating Spin&lt;/color&gt; giờ đây sẽ gây hiệu ứng &lt;color=#ffd12f&gt;Spectro Frazzle&lt;/color&gt; lên mục tiêu trong khi vẫn giữ nguyên hiệu ứng ban đầu.
 Xem thêm chi tiết trong giao diện Forte của Resonator.</t>
         </is>
       </c>
@@ -23234,7 +23234,7 @@
       <c r="M332" t="inlineStr">
         <is>
           <t>Những bức tranh morph đổ nát này hút tần số và năng lượng từ môi trường xung quanh để duy trì hình dạng, khiến khoáng chất, thực vật, thậm chí cả động vật gần đó mất đi sự sống động và màu sắc.
-Màu sắc bị hấp thụ biến thành những khối màu hỗn loạn trên Bảng Màu Tràn. &lt;color=#ffd12f&gt;Adjusting all the blocks into a designated color&lt;/color&gt; sẽ khôi phục lại vẻ sống động ban đầu của môi trường.</t>
+Màu sắc bị hấp thụ biến thành những khối màu hỗn loạn trên Bảng Màu Tràn. &lt;color=#ffd12f&gt;Điều chỉnh tất cả các khối màu về một màu chỉ định&lt;/color&gt; sẽ khôi phục lại vẻ sống động ban đầu của môi trường.</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Resonance Nexus&lt;/color&gt; lưu trữ thông tin về khu vực xung quanh. Kích hoạt nó để nhận dữ liệu &lt;color=#ffd12f&gt;Map&lt;/color&gt; tương ứng.</t>
+          <t>&lt;color=#ffd12f&gt;Nexus Cộng Hưởng&lt;/color&gt; lưu trữ thông tin về khu vực xung quanh. Kích hoạt nó để nhận dữ liệu &lt;color=#ffd12f&gt;Bản Đồ&lt;/color&gt; tương ứng.</t>
         </is>
       </c>
     </row>
@@ -23365,8 +23365,8 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Sau khi kích hoạt &lt;color=#ffd12f&gt;Resonance Beacon&lt;/color&gt;, bạn có thể mở Map và &lt;color=#ffd12f&gt;fast travel&lt;/color&gt; đến bất kỳ Resonance Beacon nào đã kích hoạt.
-Hãy đến Trạm Resonance hoặc Resonance Beacon để &lt;color=#ffd12f&gt;heal&lt;/color&gt; Resonators bị thương hoặc bất tỉnh.</t>
+          <t>Sau khi kích hoạt &lt;color=#ffd12f&gt;Điểm Cộng Hưởng&lt;/color&gt;, bạn có thể mở Bản Đồ và &lt;color=#ffd12f&gt;dịch chuyển tức thời&lt;/color&gt; đến bất kỳ Điểm Cộng Hưởng nào đã kích hoạt.
+Hãy đến Trạm Cộng Hưởng hoặc Điểm Cộng Hưởng để &lt;color=#ffd12f&gt;hồi phục&lt;/color&gt; Resonator bị thương hoặc bất tỉnh.</t>
         </is>
       </c>
     </row>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Khi đang Flight, dùng phím di chuyển (hoặc cần điều khiển) để tăng hoặc giảm độ cao.
+          <t>Khi đang Bay, dùng phím di chuyển (hoặc cần điều khiển) để tăng hoặc giảm độ cao.
 Khi bổ nhào, bạn sẽ tích lũy động lượng cho Echo Wings, giúp bạn bay cao hơn.
 Hãy bổ nhào để khôi phục động lượng khi nó cạn kiệt.</t>
         </is>
@@ -23502,8 +23502,8 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Nhấn nút Flight Siêu Tốc để kích hoạt &lt;color=#ffd12f&gt;Ultra Flight&lt;/color&gt;.
-Chế độ này giúp bạn hoàn toàn bất chấp trọng lực nhưng tiêu hao &lt;color=#ffd12f&gt;more STA&lt;/color&gt;.
+          <t>Nhấn nút Bay Siêu Tốc để kích hoạt &lt;color=#ffd12f&gt;Bay Siêu Tốc&lt;/color&gt;.
+Chế độ này giúp bạn hoàn toàn bất chấp trọng lực nhưng tiêu hao &lt;color=#ffd12f&gt;nhiều STA hơn&lt;/color&gt;.
 So với bay ngang, tốc độ tiêu hao STA sẽ tăng khi bay lên và giảm khi hạ xuống.</t>
         </is>
       </c>
@@ -23569,7 +23569,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Boost Unit: Flight là phần thưởng cho &lt;color=#ffd12f&gt;Exploration Progress&lt;/color&gt;. Nó tăng &lt;color=#ffd12f&gt;max STA&lt;/color&gt; khi bay.</t>
+          <t>Đơn vị Tăng cường: Bay là phần thưởng cho &lt;color=#ffd12f&gt;Tiến độ Thám hiểm&lt;/color&gt;. Nó tăng &lt;color=#ffd12f&gt;STA tối đa&lt;/color&gt; khi bay.</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23634,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Stand ngay trước chân bia, rồi dùng Grapple kéo tấm bia bị lệch về vị trí cũ để khôi phục lại di tích.</t>
+          <t>Đứng ngay trước chân bia, rồi dùng Grapple kéo tấm bia bị lệch về vị trí cũ để khôi phục lại di tích.</t>
         </is>
       </c>
     </row>
@@ -23764,7 +23764,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Dreamscape Nexus đóng vai trò điểm trung chuyển tần số và giấc mơ đến Somnoire. Hãy bảo vệ nó khỏi bị phá hủy trong thời gian quy định. Mỗi đợt kẻ địch bị đánh bại &lt;color=#ffd12f&gt;reduces the remaining defense time.&lt;/color&gt;</t>
+          <t>Trung Tâm Cảnh Mộng đóng vai trò điểm trung chuyển tần số và giấc mơ đến Somnoire. Hãy bảo vệ nó khỏi bị phá hủy trong thời gian quy định. Mỗi đợt kẻ địch bị đánh bại &lt;color=#ffd12f&gt;sẽ giảm thời gian phòng thủ còn lại.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -23829,7 +23829,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Hãy cẩn thận với Nightmare Tacet Discord trong một số đợt tấn công, chúng có thể &lt;color=#ffd12f&gt;deal greater DMG&lt;/color&gt; trên Nexus Cảnh Giới Mộng.</t>
+          <t>Hãy cẩn thận với Tacet Discord Ác Mộng trong một số đợt tấn công, chúng có thể &lt;color=#ffd12f&gt;gây DMG lớn hơn&lt;/color&gt; trên Nexus Cảnh Giới Mộng.</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Khi HP của Cuddle Wuddle giảm xuống dưới 80%, nó sẽ bước vào giai đoạn chuẩn bị đồng bộ. Trong thời gian này, bạn có thể ngăn chặn sự đồng bộ bằng cách gây sát thương tương đương 20% HP tối đa của Cuddle Wuddle hoặc đánh bại các Plushies Echoes khác.</t>
+          <t>Khi HP của Cuddle Wuddle giảm xuống dưới 80%, nó sẽ bước vào giai đoạn chuẩn bị đồng bộ. Trong thời gian này, bạn có thể ngăn chặn sự đồng bộ bằng cách gây DMG tương đương 20% HP tối đa của Cuddle Wuddle hoặc đánh bại các Plushies Echoes khác.</t>
         </is>
       </c>
     </row>
@@ -23959,7 +23959,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Khi Cuddle Wuddle đồng bộ với các thú nhồi bông khác, chúng sẽ tung ra Đòn Phối Hợp. Tuy nhiên, nếu &lt;color=#ffd12f&gt;HP drops below 30%&lt;/color&gt;, sự đồng bộ sẽ chấm dứt, và Cuddle Wuddle sẽ bị tê liệt.</t>
+          <t>Khi Cuddle Wuddle đồng bộ với các thú nhồi bông khác, chúng sẽ tung ra Đòn Phối Hợp. Tuy nhiên, nếu &lt;color=#ffd12f&gt;HP của Cuddle Wuddle giảm xuống dưới 30%&lt;/color&gt;, sự đồng bộ sẽ chấm dứt, và Cuddle Wuddle sẽ bị tê liệt.</t>
         </is>
       </c>
     </row>
@@ -24090,8 +24090,8 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Đi qua Tacet Field nhô lên từ mặt đất để bước vào Tacet Field ở một chiều không gian khác.
-Sau khi hoàn thành Tacet Field, bạn có thể tiêu thụ Waveplate để nhận các vật liệu phát triển Echoes và thu thập Echoes thuộc bộ Sonata tương ứng.</t>
+          <t>Đi qua Tổ Tacet nhô lên từ mặt đất để bước vào Tổ Tacet ở một chiều không gian khác.
+Sau khi hoàn thành Tổ Tacet, bạn có thể tiêu thụ Waveplate để nhận các vật liệu phát triển Echo và thu thập Echo thuộc bộ Sonata tương ứng.</t>
         </is>
       </c>
     </row>
@@ -24156,7 +24156,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Vũ Công Vitreum tuần tra Kho Tàng, lao vào kẻ xâm nhập và gây sát thương khi va chạm.</t>
+          <t>Vũ Công Vitreum tuần tra Kho Tàng, lao vào kẻ xâm nhập và gây DMG khi va chạm.</t>
         </is>
       </c>
     </row>
@@ -24221,7 +24221,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Scatter Prism tăng cường đáng kể Forte của Carlotta. Bắn vào chúng bằng "bộ trang sức" sẽ vô hiệu hóa vĩnh viễn các camera giám sát và Vitreum Dancer trong phạm vi rộng.</t>
+          <t>Lăng Kính Phân Tán tăng cường đáng kể Forte của Carlotta. Bắn vào chúng bằng "bộ trang sức" sẽ vô hiệu hóa vĩnh viễn các camera giám sát và Vitreum Dancer trong phạm vi rộng.</t>
         </is>
       </c>
     </row>
@@ -24286,7 +24286,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Mức Alertness cho biết hệ thống an ninh của Kho Tàng phát hiện hành động của ngươi đến mức nào. Nó sẽ tăng khi ngươi bị các Vũ Công Vitreum phát hiện, bị camera giám sát bắt gặp, hoặc tham gia chiến đấu. Ngươi có thể giảm mức này bằng cách vô hiệu hóa hệ thống an ninh hoặc đánh bại kẻ địch. Nếu Mức Alertness đạt 100, ngươi sẽ bị buộc phải rút lui và bắt đầu lại từ khu vực trước đó.</t>
+          <t>Mức Cảnh Giác cho biết hệ thống an ninh của Kho Tàng phát hiện hành động của ngươi đến mức nào. Nó sẽ tăng khi ngươi bị các Vũ Công Vitreum phát hiện, bị camera giám sát bắt gặp, hoặc tham gia chiến đấu. Ngươi có thể giảm mức này bằng cách vô hiệu hóa hệ thống an ninh hoặc đánh bại kẻ địch. Nếu Mức Cảnh Giác đạt 100, ngươi sẽ bị buộc phải rút lui và bắt đầu lại từ khu vực trước đó.</t>
         </is>
       </c>
     </row>
@@ -24351,7 +24351,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Defense Laser chặn một số lối đi và gây sát thương cho bất kỳ ai chạm vào.</t>
+          <t>Tia Laser Phòng Ngự chặn một số lối đi và gây DMG cho bất kỳ ai chạm vào.</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Kháng Bất Động</t>
+          <t>Kháng Hóa Bất Động</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Nâng Cấp: Erosion Aero</t>
+          <t>Nâng Cấp: Aero Erosion</t>
         </is>
       </c>
     </row>
@@ -24611,7 +24611,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Tăng Cường: Glacio Chafe</t>
+          <t>Nâng Cấp: Glacio Chafe</t>
         </is>
       </c>
     </row>
@@ -24676,7 +24676,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Tăng Cường: Fusion Burst</t>
+          <t>Nâng Cấp: Fusion Burst</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Tăng Cường: Spectro Frazzle</t>
+          <t>Nâng Cấp: Spectro Frazzle</t>
         </is>
       </c>
     </row>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tăng Cường: Havoc Bane</t>
+          <t>Nâng Cấp: Havoc Bane</t>
         </is>
       </c>
     </row>
@@ -24871,7 +24871,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Immune gián đoạn khi HP trên 50%.</t>
+          <t>Miễn nhiễm gián đoạn khi HP trên 50%.</t>
         </is>
       </c>
     </row>
@@ -25196,7 +25196,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Tấn Công tăng 100% mỗi 20 giây. Hiệu ứng này có thể chồng chất vô hạn.</t>
+          <t>ATK tăng 100% mỗi 20 giây. Hiệu ứng này có thể chồng chất vô hạn.</t>
         </is>
       </c>
     </row>
@@ -25326,7 +25326,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Khi bị đánh bại sẽ phát nổ, gây sát thương bằng 100% Tấn Công của chúng.</t>
+          <t>Khi bị đánh bại sẽ phát nổ, gây DMG bằng 100% ATK của chúng.</t>
         </is>
       </c>
     </row>
@@ -25391,7 +25391,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Sau 2 giây không chịu sát thương, chúng sẽ phục hồi 10% HP tối đa mỗi giây. Hiệu ứng này sẽ bị hủy nếu chịu sát thương.</t>
+          <t>Sau 2 giây không chịu DMG, chúng sẽ phục hồi 10% HP tối đa mỗi giây. Hiệu ứng này sẽ bị hủy nếu chịu DMG.</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Gây Sát Thương sẽ tăng Tấn Công thêm 20%, tối đa 4 lần tích lũy. Tất cả sẽ bị xóa nếu không gây Sát Thương trong 6 giây.</t>
+          <t>Gây Sát Thương sẽ tăng ATK thêm 20%, tối đa 4 lần tích lũy. Tất cả sẽ bị xóa nếu không gây Sát Thương trong 6 giây.</t>
         </is>
       </c>
     </row>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Khi nhận sát thương từ 25% HP tối đa trở lên trong 1 giây, đẩy lùi kẻ địch xung quanh và gây sát thương bằng 100% Tấn Công của bản thân.</t>
+          <t>Khi nhận DMG từ 25% HP tối đa trở lên trong 1 giây, đẩy lùi kẻ địch xung quanh và gây DMG bằng 100% ATK của bản thân.</t>
         </is>
       </c>
     </row>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Gây Sát Thương sẽ áp 1 lớp Erosion Aero lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần.</t>
+          <t>Gây Sát Thương sẽ áp 1 lớp Xói Mòn Aero lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Gây Sát Thương sẽ áp 1 lớp Glacio Chafe lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần.</t>
+          <t>Gây Sát Thương sẽ áp 1 lớp Xước Băng Giá lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Gây Sát Thương sẽ áp 1 lớp Bùng Nổ Nhiệt Hạch lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần.</t>
+          <t>Gây Sát Thương sẽ áp 1 lớp Bùng Fusion Burst lên mục tiêu. Hiệu ứng này có thể kích hoạt mỗi 6 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -25846,7 +25846,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Gây sát thương sẽ áp 1 tầng Hỗn Loạn Quang trên mục tiêu. Hiệu ứng này chỉ kích hoạt mỗi 6 giây 1 lần.</t>
+          <t>Gây DMG sẽ áp 1 tầng Hỗn Loạn Quang trên mục tiêu. Hiệu ứng này chỉ kích hoạt mỗi 6 giây 1 lần.</t>
         </is>
       </c>
     </row>
@@ -25911,7 +25911,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Gây sát thương sẽ áp 1 tầng Hỗn Loạn Ác lên mục tiêu. Hiệu ứng này chỉ kích hoạt mỗi 6 giây 1 lần.</t>
+          <t>Gây DMG sẽ áp 1 tầng Hỗn Loạn Ác lên mục tiêu. Hiệu ứng này chỉ kích hoạt mỗi 6 giây 1 lần.</t>
         </is>
       </c>
     </row>
@@ -25976,7 +25976,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Loại kẻ địch này có HP và Tấn Công cao hơn nhiều. Dodge phản công và Phản đòn còn có thể làm giảm Vibration Strength và HP của chúng.</t>
+          <t>Loại kẻ địch này có HP và ATK cao hơn nhiều. Né phản công và Phản đòn còn có thể làm giảm Sức Rung và HP của chúng.</t>
         </is>
       </c>
     </row>
@@ -26041,7 +26041,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Restore 20% HP cho đồng đội xung quanh khi bị đánh bại.</t>
+          <t>Hồi phục 20% HP cho đồng đội xung quanh khi bị đánh bại.</t>
         </is>
       </c>
     </row>
@@ -26106,7 +26106,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Gây Fusion DMG lên kẻ địch xung quanh mỗi giây bằng 2% HP tối đa của mục tiêu. Hiệu ứng này không chồng chất.</t>
+          <t>Gây Sát Thương Fusion lên kẻ địch xung quanh mỗi giây bằng 2% HP tối đa của mục tiêu. Hiệu ứng này không chồng chất.</t>
         </is>
       </c>
     </row>
@@ -26171,7 +26171,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Immune Electro DMG khi HP dưới 50%.</t>
+          <t>Miễn nhiễm DMG Electro khi HP dưới 50%.</t>
         </is>
       </c>
     </row>
@@ -26301,7 +26301,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Khi bị đánh bại, tăng Tấn Công cho đồng đội xung quanh lên 60% trong 15 giây.</t>
+          <t>Khi bị đánh bại, tăng ATK cho đồng đội xung quanh lên 60% trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -26366,7 +26366,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Nhận sát thương sẽ tăng 10% sát thương gây ra trong 8 giây, tối đa 10 lần cộng dồn.</t>
+          <t>Nhận DMG sẽ tăng 10% DMG gây ra trong 8 giây, tối đa 10 lần cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -26435,11 +26435,11 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Tăng cường Đội I: Khi sử dụng Resonance Liberation, Resonators nhận 10 điểm Dấu Băng Giá, toàn đội nhận thêm 20 Concerto Energy và 20 Resonance Energy.
-Khi Dấu Băng Giá đạt 40 điểm, Icefall sẽ tự động kích hoạt, gây Glacio DMG và giảm 50% Vibration Strength của mục tiêu.
+          <t>Tăng cường Đội I: Khi sử dụng Resonance Liberation, Resonator nhận 10 điểm Dấu Băng Giá, toàn đội nhận thêm 20 Concerto Energy và 20 Resonance Energy.
+Khi Dấu Băng Giá đạt 40 điểm, Icefall sẽ tự động kích hoạt, gây DMG Glacio và giảm 50% Sức Rung của mục tiêu.
 Tăng cường Kẻ Địch:
-- Hào Quang Cháy Bỏng: Một số kẻ địch gây sát thương DoT hệ Fusion lên Resonators gần đó.
-- Tiêu diệt những kẻ địch này sẽ tăng 20% Tấn Công cho toàn đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
+- Hào Quang Cháy Bỏng: Một số kẻ địch gây DMG DoT hệ Fusion lên Resonator gần đó.
+- Tiêu diệt những kẻ địch này sẽ tăng 20% ATK cho toàn đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
         </is>
       </c>
     </row>
@@ -26507,10 +26507,10 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội II: Khi sử dụng Intro Skill, hồi phục 20 Concerto Energy và 20 Resonance Energy cho tất cả thành viên trong đội, đồng thời giảm 15% Cooldown chiêu của Resonance Liberation.
+          <t>Hiệu ứng Đội II: Khi sử dụng Kỹ Năng Khởi Động, hồi phục 20 Năng Lượng Giao Hưởng và 20 Resonance Energy cho tất cả thành viên trong đội, đồng thời giảm 15% thời gian hồi chiêu của Resonance Liberation.
 Hiệu ứng Kẻ Địch:
-- Hào Quang Cháy Bỏng: Một số kẻ địch gây Sát Thương Hệ Fusion theo thời gian lên Resonators gần đó.
-- Hạ gục những kẻ địch này sẽ tăng 20% Tấn Công cho tất cả thành viên trong đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
+- Hào Quang Cháy Bỏng: Một số kẻ địch gây Sát Thương Hệ Fusion theo thời gian lên các Resonator gần đó.
+- Hạ gục những kẻ địch này sẽ tăng 20% ATK cho tất cả thành viên trong đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
         </is>
       </c>
     </row>
@@ -26580,8 +26580,8 @@
         <is>
           <t>Tăng cường Đội I: Tất cả thành viên trong đội thuộc hệ Havoc hồi 4 Concerto Energy mỗi giây.
 Tăng cường Kẻ Địch:
-- Hào Quang Cháy Bỏng: Một số kẻ địch gây sát thương DoT hệ Fusion lên Resonators gần đó.
-- Tiêu diệt những kẻ địch này sẽ tăng 20% Tấn Công cho toàn đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
+- Hào Quang Cháy Bỏng: Một số kẻ địch gây DMG DoT hệ Fusion lên Resonator gần đó.
+- Tiêu diệt những kẻ địch này sẽ tăng 20% ATK cho toàn đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
         </is>
       </c>
     </row>
@@ -26649,10 +26649,10 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội II: Mọi thành viên trong đội hồi phục thêm 2 Concerto Energy mỗi giây.
+          <t>Hiệu ứng Đội II: Mọi thành viên trong đội hồi phục thêm 2 Năng Lượng Giao Hưởng mỗi giây.
 Hiệu ứng Kẻ Địch:
-- Hào Quang Cháy Bỏng: Một số kẻ địch gây Sát Thương Hệ Fusion theo thời gian lên Resonators gần đó.
-- Hạ gục những kẻ địch này sẽ tăng 20% Tấn Công cho tất cả thành viên trong đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
+- Hào Quang Cháy Bỏng: Một số kẻ địch gây Sát Thương Hệ Fusion theo thời gian lên các Resonator gần đó.
+- Hạ gục những kẻ địch này sẽ tăng 20% ATK cho tất cả thành viên trong đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
         </is>
       </c>
     </row>
@@ -26721,11 +26721,11 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Tăng cường Đội I: Khi sử dụng Resonance Liberation, Resonators nhận 10 điểm Dấu Băng Giá, toàn đội nhận thêm 20 Concerto Energy và 20 Resonance Energy.
-Khi Dấu Băng Giá đạt 40 điểm, Icefall sẽ tự động kích hoạt, gây Glacio DMG và giảm 50% Vibration Strength của mục tiêu.
+          <t>Tăng cường Đội I: Khi sử dụng Resonance Liberation, Resonator nhận 10 điểm Dấu Băng Giá, toàn đội nhận thêm 20 Concerto Energy và 20 Resonance Energy.
+Khi Dấu Băng Giá đạt 40 điểm, Icefall sẽ tự động kích hoạt, gây DMG Glacio và giảm 50% Sức Rung của mục tiêu.
 Tăng cường Kẻ Địch:
-- Hào Quang Cháy Bỏng: Một số kẻ địch gây sát thương DoT hệ Fusion lên Resonators gần đó.
-- Tiêu diệt những kẻ địch này sẽ tăng 20% Tấn Công cho toàn đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
+- Hào Quang Cháy Bỏng: Một số kẻ địch gây DMG DoT hệ Fusion lên Resonator gần đó.
+- Tiêu diệt những kẻ địch này sẽ tăng 20% ATK cho toàn đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
         </is>
       </c>
     </row>
@@ -26793,10 +26793,10 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội II: Khi sử dụng Intro Skill, hồi phục 20 Concerto Energy và 20 Resonance Energy cho tất cả thành viên trong đội, đồng thời giảm 15% Cooldown chiêu của Resonance Liberation.
+          <t>Hiệu ứng Đội II: Khi sử dụng Kỹ Năng Khởi Động, hồi phục 20 Năng Lượng Giao Hưởng và 20 Resonance Energy cho tất cả thành viên trong đội, đồng thời giảm 15% thời gian hồi chiêu của Resonance Liberation.
 Hiệu ứng Kẻ Địch:
-- Hào Quang Cháy Bỏng: Một số kẻ địch gây Sát Thương Hệ Fusion theo thời gian lên Resonators gần đó.
-- Hạ gục những kẻ địch này sẽ tăng 20% Tấn Công cho tất cả thành viên trong đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
+- Hào Quang Cháy Bỏng: Một số kẻ địch gây Sát Thương Hệ Fusion theo thời gian lên các Resonator gần đó.
+- Hạ gục những kẻ địch này sẽ tăng 20% ATK cho tất cả thành viên trong đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
         </is>
       </c>
     </row>
@@ -26866,8 +26866,8 @@
         <is>
           <t>Tăng cường Đội I: Tất cả thành viên trong đội thuộc hệ Havoc hồi 4 Concerto Energy mỗi giây.
 Tăng cường Kẻ Địch:
-- Hào Quang Cháy Bỏng: Một số kẻ địch gây sát thương DoT hệ Fusion lên Resonators gần đó.
-- Tiêu diệt những kẻ địch này sẽ tăng 20% Tấn Công cho toàn đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
+- Hào Quang Cháy Bỏng: Một số kẻ địch gây DMG DoT hệ Fusion lên Resonator gần đó.
+- Tiêu diệt những kẻ địch này sẽ tăng 20% ATK cho toàn đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
         </is>
       </c>
     </row>
@@ -26935,10 +26935,10 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Hiệu ứng Đội II: Mọi thành viên trong đội hồi phục thêm 2 Concerto Energy mỗi giây.
+          <t>Hiệu ứng Đội II: Mọi thành viên trong đội hồi phục thêm 2 Năng Lượng Giao Hưởng mỗi giây.
 Hiệu ứng Kẻ Địch:
-- Hào Quang Cháy Bỏng: Một số kẻ địch gây Sát Thương Hệ Fusion theo thời gian lên Resonators gần đó.
-- Hạ gục những kẻ địch này sẽ tăng 20% Tấn Công cho tất cả thành viên trong đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
+- Hào Quang Cháy Bỏng: Một số kẻ địch gây Sát Thương Hệ Fusion theo thời gian lên các Resonator gần đó.
+- Hạ gục những kẻ địch này sẽ tăng 20% ATK cho tất cả thành viên trong đội trong 30 giây và tăng khả năng chống gián đoạn trong 60 giây.</t>
         </is>
       </c>
     </row>
@@ -27198,7 +27198,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Dùng {0}/{1} để kích hoạt Ultra Flight và &lt;color=#ffd12f&gt;fly freely&lt;/color&gt; bất chấp trọng lực. Tiêu hao nhiều Flight STA hơn.</t>
+          <t>Dùng {0}/{1} để kích hoạt Ultra Flight và &lt;color=#ffd12f&gt;bay tự do&lt;/color&gt; bất chấp trọng lực. Tiêu hao nhiều Flight STA hơn.</t>
         </is>
       </c>
     </row>
@@ -27263,7 +27263,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Dùng Dash để vào chế độ Ultra Flight: Chế độ này giúp bạn thách thức trọng lực và &lt;color=#ffd12f&gt;fly freely&lt;/color&gt;, nhưng tiêu hao nhiều STA hơn.</t>
+          <t>Dùng Dash để vào chế độ Ultra Flight: Chế độ này giúp bạn thách thức trọng lực và &lt;color=#ffd12f&gt;bay tự do&lt;/color&gt;, nhưng tiêu hao nhiều STA hơn.</t>
         </is>
       </c>
     </row>
@@ -27328,7 +27328,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Dùng Dash để vào chế độ Ultra Flight: Chế độ này giúp bạn thách thức trọng lực và &lt;color=#ffd12f&gt;fly freely&lt;/color&gt;, nhưng tiêu hao nhiều STA hơn.</t>
+          <t>Dùng Dash để vào chế độ Ultra Flight: Chế độ này giúp bạn thách thức trọng lực và &lt;color=#ffd12f&gt;bay tự do&lt;/color&gt;, nhưng tiêu hao nhiều STA hơn.</t>
         </is>
       </c>
     </row>
@@ -27409,7 +27409,7 @@
 Quyết tâm đòi lại công bằng và trả thù cho người bạn cũ, ông đã quay trở lại cuộc chơi để khiến những kẻ thủ ác phải trả giá.
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 14 và mở khóa Resonance Nexus tại Thành phố Ragunna trong Nhiệm Vụ Chính: "Ngọn Gió Thiêng Thường Thổi".
-[Event Rules]
+[Quy Tắc Sự Kiện]
 1. Trong sự kiện, bạn sẽ bước vào một không gian đặc biệt để chiến đấu với các làn sóng kẻ địch trong thời gian giới hạn, với sự hỗ trợ của các hiệu ứng đặc biệt.
 2. Bạn sẽ thu thập Xu bằng cách gây sát thương lên kẻ địch, nhưng bị tấn công sẽ khiến bạn mất Xu.
 3. Vượt qua các làn sóng kẻ địch sẽ mở khóa thêm các hiệu ứng đặc biệt để hỗ trợ bạn.
@@ -27488,9 +27488,9 @@
       <c r="M396" t="inlineStr">
         <is>
           <t>Về sự kiện
-Hỡi Rover được thủy triều dẫn lối, ngươi đã xua tan bóng tối chiến tranh ở Jinzhou và vượt qua ranh giới thời gian trên Núi Firmament. Khi đứng trên bờ biển cô tịch, ngươi có nghe thấy lời tiên tri vang trên cơn gió bão, vọng qua Biển Storm không? Ngươi có thoáng thấy vẻ huy hoàng vô song ẩn giấu trong vùng đất huyền thoại của những Echoes không? Giờ đây, hãy tôi rèn ý chí và dấn thân vào hành trình chưa biết, đương đầu với bão tố, và mở đường đến Rinascita.
+Hỡi Vận Mệnh Giả được thủy triều dẫn lối, ngươi đã xua tan bóng tối chiến tranh ở Jinzhou và vượt qua ranh giới thời gian trên Núi Firmament. Khi đứng trên bờ biển cô tịch, ngươi có nghe thấy lời tiên tri vang trên cơn gió bão, vọng qua Biển Bão Tố không? Ngươi có thoáng thấy vẻ huy hoàng vô song ẩn giấu trong vùng đất huyền thoại của những Echo không? Giờ đây, hãy tôi rèn ý chí và dấn thân vào hành trình chưa biết, đương đầu với bão tố, và mở đường đến Rinascita.
 Điều kiện tham gia
-Đến Resonance Nexus ở Jinzhou và mở khóa Terminal trong Nhiệm Vụ Chính "First Resonance."
+Đến Resonance Nexus ở Jinzhou và mở khóa Thiết bị đầu cuối trong Nhiệm Vụ Chính "First Resonance."
 Quy tắc sự kiện
 Chương II của Nhiệm Vụ Chính hiện đã mở, người chơi đủ điều kiện có thể trải nghiệm chương này sớm.
 Tiến độ Chương II được lưu riêng biệt với tiến độ Chương I. Trải nghiệm Chương II sớm không ảnh hưởng đến tiến độ Chương I của bạn.
@@ -27570,7 +27570,7 @@
       <c r="M397" t="inlineStr">
         <is>
           <t>Về sự kiện
-Sau khi vượt qua màn sương biển nguy hiểm và những con sóng dữ dội, cuối cùng bạn cũng đặt chân đến Rinascita, Land Của Những Âm Vang.
+Sau khi vượt qua màn sương biển nguy hiểm và những con sóng dữ dội, cuối cùng bạn cũng đặt chân đến Rinascita, Vùng Đất Của Những Âm Vang.
 Những ánh sáng rực rỡ trải dài khắp chân trời, trong khi những giai điệu vui tươi vang vọng qua vịnh và những đóa hoa nở rộ.
 Lễ hội Carnevale sắp bắt đầu. Mong rằng hành trình của bạn sẽ là một kỷ niệm khó quên.
 Đây là Sự Kiện Thường Xuyên. Hoàn thành các nhiệm vụ sự kiện để nhận thưởng.</t>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Vô hiệu hóa hệ thống an ninh hoặc đánh bại kẻ địch tuần tra sẽ làm giảm Mức Alertness. Khi Mức Alertness đạt 100, các Echoes canh giữ Kho Tàng sẽ truy đuổi kẻ xâm nhập.</t>
+          <t>Vô hiệu hóa hệ thống an ninh hoặc đánh bại kẻ địch tuần tra sẽ làm giảm Mức Cảnh Giác. Khi Mức Cảnh Giác đạt 100, các Echo canh giữ Kho Tàng sẽ truy đuổi kẻ xâm nhập.</t>
         </is>
       </c>
     </row>
@@ -27716,12 +27716,12 @@
 Bên cạnh một bức tranh biến dạng bí ẩn, cậu gặp Claudia, một họa sĩ bị mắc kẹt trong những cơn ác mộng của chính mình.
 Claudia nhờ cậu điều tra thế giới bên trong bức tranh và trao cho cậu một lá bùa hộ mệnh.
 Điều kiện tham gia
-Đạt Cấp Liên minh 22, mở khóa chế độ Đồng đội và kích hoạt Điểm Cộng hưởng tại Thành phố Ragunna trong Nhiệm vụ Main "Làn Gió Thiêng Thường Xuyên Thổi".
+Đạt Cấp Liên minh 22, mở khóa chế độ Đồng đội và kích hoạt Điểm Cộng hưởng tại Thành phố Ragunna trong Nhiệm vụ Chính "Làn Gió Thiêng Thường Xuyên Thổi".
 Quy tắc sự kiện
-Claudia nhờ cậu điều tra thế giới trong bức tranh và trao cho cậu một lá bùa hộ mệnh. Trong thế giới tranh, lá bùa biến thành các Echoes khác nhau để hỗ trợ cậu.
-Tiêu diệt tất cả kẻ địch trong khu vực điều tra để tiến lên. Các Echoes được biến đổi từ lá bùa sẽ tăng cường sức mạnh cho Resonators của cậu khi tiến độ tăng lên.
-Tiêu diệt kẻ địch trước khi hết thời gian sẽ nhận thêm điểm thưởng. Đạt số điểm giai đoạn yêu cầu để nhận Rewards Giai đoạn và số điểm tổng yêu cầu để nhận Rewards Điểm. Tính năng Ghép trận khả dụng cho tất cả thử thách, cho phép cậu kết hợp với những người chơi khác.
-※Chỉ các Echoes được chỉ định mới có thể trang bị trong sự kiện này. Echoes sẽ thay thế Skill Echoes chính của cậu, nhưng các Sonata đã kích hoạt vẫn có hiệu lực.</t>
+Claudia nhờ cậu điều tra thế giới trong bức tranh và trao cho cậu một lá bùa hộ mệnh. Trong thế giới tranh, lá bùa biến thành các Echo khác nhau để hỗ trợ cậu.
+Tiêu diệt tất cả kẻ địch trong khu vực điều tra để tiến lên. Các Echo được biến đổi từ lá bùa sẽ tăng cường sức mạnh cho Resonator của cậu khi tiến độ tăng lên.
+Tiêu diệt kẻ địch trước khi hết thời gian sẽ nhận thêm điểm thưởng. Đạt số điểm giai đoạn yêu cầu để nhận Phần thưởng Giai đoạn và số điểm tổng yêu cầu để nhận Phần thưởng Điểm. Tính năng Ghép trận khả dụng cho tất cả thử thách, cho phép cậu kết hợp với những người chơi khác.
+※Chỉ các Echo được chỉ định mới có thể trang bị trong sự kiện này. Echo sẽ thay thế Kỹ năng Echo chính của cậu, nhưng các Sonata đã kích hoạt vẫn có hiệu lực.</t>
         </is>
       </c>
     </row>
@@ -27786,7 +27786,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Một Terminal đặc biệt do Fisalias và Hội phát triển, có khả năng mô phỏng những kẻ địch mạnh mẽ. Đồng Xu Trial thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa hàng Trial.</t>
+          <t>Một Thiết bị đầu cuối đặc biệt do Fisalias và Hội phát triển, có khả năng mô phỏng những kẻ địch mạnh mẽ. Đồng Xu Thử Thách thu được từ trận chiến này có thể đổi lấy nhiều phần thưởng khác nhau tại Cửa Hàng Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -27851,7 +27851,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Negative Status bao gồm: &lt;color=#ffd12f&gt;Aero Erosion&lt;/color&gt;, &lt;color=#ffd12f&gt;Electro Flare&lt;/color&gt;, &lt;color=#ffd12f&gt;Spectro Frazzle&lt;/color&gt;, &lt;color=#ffd12f&gt;Fusion Burst&lt;/color&gt;, &lt;color=#ffd12f&gt;Glacio Chafe&lt;/color&gt; và &lt;color=#ffd12f&gt;Havoc Bane&lt;/color&gt;.</t>
+          <t>Trạng thái Tiêu cực bao gồm: &lt;color=#ffd12f&gt;Xói mòn Aero&lt;/color&gt;, &lt;color=#ffd12f&gt;Bùng nổ Electro&lt;/color&gt;, &lt;color=#ffd12f&gt;Rối loạn Spectro&lt;/color&gt;, &lt;color=#ffd12f&gt;Vụ nổ Fusion&lt;/color&gt;, &lt;color=#ffd12f&gt;Trầy xước Glacio&lt;/color&gt; và &lt;color=#ffd12f&gt;Tai ương Havoc&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -27919,10 +27919,10 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>1. Sau khi mở khóa Fishing Ability: Wonder Bubble, bạn có thể mua Wonder Bubble của khu vực từ Planck, thương nhân ở bến tàu. Sau khi mua, một Wonder Bubble sẽ tự động xuất hiện gần bến tàu hiện tại, dần dần bắt cua và nhím biển trong khu vực.
-2. Wonder Bubble có sức chứa hạn chế. Khi đầy, nó sẽ ngừng bắt cá. Hãy thu hoạch kịp thời.
-3. Steer Rachel đến Wonder Bubble và tương tác với nó để thu hoạch.
-4. Nâng cấp Fishing Ability để tăng sức chứa của Wonder Bubble và cải thiện chất lượng thu hoạch.</t>
+          <t>1. Sau khi mở khóa Kỹ Năng Câu Cá: Bong Bóng Kỳ Diệu, bạn có thể mua Bong Bóng Kỳ Diệu của khu vực từ Planck, thương nhân ở bến tàu. Sau khi mua, một Bong Bóng Kỳ Diệu sẽ tự động xuất hiện gần bến tàu hiện tại, dần dần bắt cua và nhím biển trong khu vực.
+2. Bong Bóng Kỳ Diệu có sức chứa hạn chế. Khi đầy, nó sẽ ngừng bắt cá. Hãy thu hoạch kịp thời.
+3. Điều khiển Rachel đến Bong Bóng Kỳ Diệu và tương tác với nó để thu hoạch.
+4. Nâng cấp Kỹ Năng Câu Cá để tăng sức chứa của Bong Bóng Kỳ Diệu và cải thiện chất lượng thu hoạch.</t>
         </is>
       </c>
     </row>
@@ -27992,8 +27992,8 @@
         <is>
           <t>1. Sau khi mở khóa Trawl, nó sẽ tự động được trang bị cho Rachel và giúp cậu bắt được các loài cá đã từng câu được trong khu vực.
 2. Trawl có sức chứa giới hạn. Khi đầy, nó sẽ ngừng bắt cá. Hãy thu hoạch cá kịp thời nhé.
-3. Trawl chỉ có thể truy cập tại giao diện Dock, nơi cậu có thể quản lý cá đã bắt được từ Trawl.
-4. Nâng cấp Kỹ Năng Fishing để tăng sức chứa của Trawl và cải thiện chất lượng cá bắt được.</t>
+3. Trawl chỉ có thể truy cập tại giao diện Bến Tàu, nơi cậu có thể quản lý cá đã bắt được từ Trawl.
+4. Nâng cấp Kỹ Năng Câu Cá để tăng sức chứa của Trawl và cải thiện chất lượng cá bắt được.</t>
         </is>
       </c>
     </row>
@@ -28064,8 +28064,8 @@
         <is>
           <t>1. Bạn có thể lưu trữ chiến lợi phẩm câu được trong Hàng Hóa của Rachel.
 2. Hàng Hóa có giới hạn dung lượng. Những chiến lợi phẩm vượt quá giới hạn sẽ không thể lưu trữ và không được xếp chồng.
-3. Nâng cấp Kỹ Năng Fishing để tăng dung lượng Hàng Hóa.
-4. Khi lưu trữ chiến lợi phẩm, bạn có thể Place, Rotate, Loại Bỏ hoặc Trả Lại chúng khi cần.
+3. Nâng cấp Kỹ Năng Câu Cá để tăng dung lượng Hàng Hóa.
+4. Khi lưu trữ chiến lợi phẩm, bạn có thể Đặt, Xoay, Loại Bỏ hoặc Trả Lại chúng khi cần.
 5. Khi cập bến, Coast Flax, Palm Tree Log, Metal Debris và Bampuff sẽ tự động chuyển đổi thành các vật phẩm thông thường.</t>
         </is>
       </c>
@@ -28150,10 +28150,10 @@
 Quy tắc sự kiện
 1. Trong Tactical Simulacra III, hãy đối đầu với các đợt kẻ địch mạnh mẽ bằng cách sử dụng các hiệu ứng tăng cường đặc biệt trong các miền mô phỏng khác nhau.
 2. Khi hoàn thành nhiều thử thách hơn, bạn sẽ mở khóa thêm các hiệu ứng tăng cường đặc biệt để hỗ trợ vượt qua các thử thách tiếp theo. Sử dụng các hiệu ứng khác nhau để đánh bại kẻ địch, hoàn thành mục tiêu trong Thử thách Phụ và nhận thêm phần thưởng.
-3. Kết quả của mỗi thử thách bao gồm ba phần: Points Quái Vật, Time Points và Technical Points.
-i. Points Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
-ii. Time Points được tính dựa trên thời gian còn lại khi hoàn thành thử thách. Càng đánh bại nhiều kẻ địch, hệ số chuyển đổi điểm càng cao.
-iii. Technical Points được tính cho mỗi lần Phản Công và Dodge thành công.
+3. Kết quả của mỗi thử thách bao gồm ba phần: Điểm Quái Vật, Điểm Thời Gian và Điểm Kỹ Thuật.
+i. Điểm Quái Vật được tính khi đánh bại kẻ địch trong thử thách.
+ii. Điểm Thời Gian được tính dựa trên thời gian còn lại khi hoàn thành thử thách. Càng đánh bại nhiều kẻ địch, hệ số chuyển đổi điểm càng cao.
+iii. Điểm Kỹ Thuật được tính cho mỗi lần Phản Công và Né Tránh thành công.
 Xếp hạng Chiến đấu
 Đánh trúng kẻ địch sẽ cải thiện Xếp hạng Chiến đấu của bạn. Đánh bại chúng sẽ mang lại một bước tiến đáng kể.</t>
         </is>
@@ -28220,7 +28220,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Dodge đòn kẻ địch và phản công tiêu diệt chúng.</t>
+          <t>Né đòn kẻ địch và phản công tiêu diệt chúng.</t>
         </is>
       </c>
     </row>
@@ -28285,7 +28285,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Dodge đòn kẻ địch và phản công tiêu diệt chúng.</t>
+          <t>Né đòn kẻ địch và phản công tiêu diệt chúng.</t>
         </is>
       </c>
     </row>
@@ -28350,7 +28350,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Dodge đòn kẻ địch và phản công tiêu diệt chúng.</t>
+          <t>Né đòn kẻ địch và phản công tiêu diệt chúng.</t>
         </is>
       </c>
     </row>
@@ -28417,9 +28417,9 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Prism Aero miễn nhiễm với sát thương &lt;color=#ffd12f&gt;Aero&lt;/color&gt;.
-Nó nhắm vào một Resonator đồng minh gần đó, tự kích hoạt hiệu ứng tăng cường liên tục để tiếp tục tấn công. Khi mục tiêu đã chọn bị đánh bại, Prism Aero sẽ ngừng tấn công.
-Prism Aero có thể bị Cò Xanh và Cò Tím hấp thụ, mang lại hiệu ứng tăng cường vĩnh viễn cho chúng sau khi hấp thụ.</t>
+          <t>Lăng Kính Aero miễn nhiễm với DMG &lt;color=#ffd12f&gt;Aero&lt;/color&gt;.
+Nó nhắm vào một Cộng Hưởng Giả đồng minh gần đó, tự kích hoạt hiệu ứng tăng cường liên tục để tiếp tục tấn công. Khi mục tiêu đã chọn bị đánh bại, Lăng Kính Aero sẽ ngừng tấn công.
+Lăng Kính Aero có thể bị Cò Xanh và Cò Tím hấp thụ, mang lại hiệu ứng tăng cường vĩnh viễn cho chúng sau khi hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -28555,7 +28555,7 @@
         <is>
           <t>Dưới làn nước đảo Riccioli hội tụ đủ loại tần số. Ban đêm, Ghost Medusa sẽ xuất hiện.
 Khi cậu chèo thuyền và câu cá, Mức Đe Dọa của cậu với vùng nước này sẽ tăng lên. Mức Đe Dọa càng cao, Ghost Medusa càng hung dữ.
-Tuy nhiên, ở Mức Đe Dọa cao, &lt;color=#ffd12f&gt;catch quality&lt;/color&gt; sẽ tốt hơn, và cơ hội bắt được &lt;color=#ffd12f&gt;Mutants&lt;/color&gt; cũng tăng lên.</t>
+Tuy nhiên, ở Mức Đe Dọa cao, &lt;color=#ffd12f&gt;chất lượng mẻ câu&lt;/color&gt; sẽ tốt hơn, và cơ hội bắt được &lt;color=#ffd12f&gt;Biến Dị&lt;/color&gt; cũng tăng lên.</t>
         </is>
       </c>
     </row>
@@ -28623,8 +28623,8 @@
       <c r="M412" t="inlineStr">
         <is>
           <t>Dưới ảnh hưởng của Sentinel hay Threnodian, các đột biến có thể xuất hiện ở nhiều loài sinh vật dưới biển.
-Những cá thể đột biến luôn có thể tìm thấy tại các Fishing Spots Cá của loài gốc.
-Nâng cao Khả Năng Fishing của Phoebe hoặc câu cá ở những khu vực Ghost Medusa xuất hiện vào ban đêm có thể tăng cơ hội bắt được đột biến.</t>
+Những cá thể đột biến luôn có thể tìm thấy tại các Điểm Câu Cá của loài gốc.
+Nâng cao Khả Năng Câu Cá của Phoebe hoặc câu cá ở những khu vực Ghost Medusa xuất hiện vào ban đêm có thể tăng cơ hội bắt được đột biến.</t>
         </is>
       </c>
     </row>
@@ -28691,9 +28691,9 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Dùng Thiết Bị Giải Mã để &lt;color=#ffd12f&gt;shoot the target mechanisms&lt;/color&gt;. Điều này sẽ thay đổi trạng thái của chúng, cho phép cậu bật/tắt camera, đổi hướng đường ray và điều khiển các cơ chế an ninh trong kho.
+          <t>Dùng Thiết Bị Giải Mã để &lt;color=#ffd12f&gt;bắn vào các cơ chế mục tiêu&lt;/color&gt;. Điều này sẽ thay đổi trạng thái của chúng, cho phép cậu bật/tắt camera, đổi hướng đường ray và điều khiển các cơ chế an ninh trong kho.
 Nâng cấp Cấp Độ Giải Mã để mở khóa thêm chức năng.
-Board Echo, điều khiển đường đi và kiểm soát các cơ chế trên đường.</t>
+Lên tàu Echo, điều khiển đường đi và kiểm soát các cơ chế trên đường.</t>
         </is>
       </c>
     </row>
@@ -28825,7 +28825,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Dùng Thiết Bị Giải Mã để &lt;color=#ffd12f&gt;shoot the target mechanisms&lt;/color&gt;. Điều này sẽ thay đổi trạng thái của chúng, cho phép cậu bật/tắt camera, đổi hướng đường ray và điều khiển các cơ chế an ninh trong kho.
+          <t>Dùng Thiết Bị Giải Mã để &lt;color=#ffd12f&gt;bắn vào các cơ chế mục tiêu&lt;/color&gt;. Điều này sẽ thay đổi trạng thái của chúng, cho phép cậu bật/tắt camera, đổi hướng đường ray và điều khiển các cơ chế an ninh trong kho.
 Nâng cấp Cấp Độ Giải Mã để mở khóa thêm chức năng.
 Cậu có thể điều khiển nhiều cơ chế khác nhau trong kho bằng thiết bị này.</t>
         </is>
@@ -28894,9 +28894,9 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Thiết bị Thanh Tẩy chỉ có thể điều khiển số lượng Echoes nhất định. Khi đạt đến giới hạn, cậu sẽ không thể điều khiển thêm bất kỳ Echoes nào nữa.
-Nâng cấp Cấp Độ Thanh Tẩy để tăng số lượng Echoes có thể điều khiển đồng thời.
-*Các Echoes có thể điều khiển sẽ được đánh dấu bằng quầng sáng vàng.</t>
+          <t>Thiết bị Thanh Tẩy chỉ có thể điều khiển số lượng Echo nhất định. Khi đạt đến giới hạn, cậu sẽ không thể điều khiển thêm bất kỳ Echo nào nữa.
+Nâng cấp Cấp Độ Thanh Tẩy để tăng số lượng Echo có thể điều khiển đồng thời.
+*Các Echo có thể điều khiển sẽ được đánh dấu bằng quầng sáng vàng.</t>
         </is>
       </c>
     </row>
@@ -28968,10 +28968,10 @@
         <is>
           <t>Nâng cấp Cấp Độ Giải Mã để mở khóa thêm chức năng.
 Lệnh Giải Mã - Cơ Chế Bảo Mật: Nâng cấp Cấp Độ Giải Mã để truy cập vào nhiều cơ chế bảo mật hơn.
-Lệnh Ủy Quyền - Kiểm Soát Echoes:
-Cấp 1: Chuyển đổi mục tiêu thành đồng minh, ưu tiên bảo vệ người sở hữu Thiết Bị Giải Mã trên hết. Tuy nhiên, hiệu ứng sẽ bị hủy và Echoes trở về trạng thái mặc định nếu không có Echoes đồng minh trong phạm vi hiệu quả của Thiết Bị Giải Mã hoặc khi Thiết Bị Giải Mã không được trang bị làm Công Cụ.
-Cấp 2: Các Echoes bị kiểm soát sẽ chủ động thu hút tấn công của kẻ địch.
-Cấp 3: Số lượng Echoes bạn có thể kiểm soát tăng lên 2.</t>
+Lệnh Ủy Quyền - Kiểm Soát Echo:
+Cấp 1: Chuyển đổi mục tiêu thành đồng minh, ưu tiên bảo vệ người sở hữu Thiết Bị Giải Mã trên hết. Tuy nhiên, hiệu ứng sẽ bị hủy và Echo trở về trạng thái mặc định nếu không có Echo đồng minh trong phạm vi hiệu quả của Thiết Bị Giải Mã hoặc khi Thiết Bị Giải Mã không được trang bị làm Công Cụ.
+Cấp 2: Các Echo bị kiểm soát sẽ chủ động thu hút tấn công của kẻ địch.
+Cấp 3: Số lượng Echo bạn có thể kiểm soát tăng lên 2.</t>
         </is>
       </c>
     </row>
@@ -29052,19 +29052,19 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Trợ Thủ Giấc Mơ]
-Resonators Trợ Thủ Giấc Mơ hiện tại: Phoebe, Jinhsi, Shorekeeper, Verina. Sử dụng ít nhất một Resonators Trợ Thủ Giấc Mơ để nhận thưởng 150% Points Ảo Ảnh!
+Resonator Trợ Thủ Giấc Mơ hiện tại: Phoebe, Jinhsi, Shorekeeper, Verina. Sử dụng ít nhất một Resonator Trợ Thủ Giấc Mơ để nhận thưởng 150% Điểm Ảo Ảnh!
 Hiệu ứng Trợ Thủ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Spectro DMG.
-- Attack cơ bản trúng mục tiêu sẽ nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Skill sẽ nhận 50 Năng Lượng Giấc Mơ, và hồi máu cho Resonators bằng Resonance Skill sẽ nhận thêm 50 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây sát thương lên mục tiêu bị ảnh hưởng bởi Spectro Frazzle sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Spectro.
+- Tấn Công cơ bản trúng mục tiêu sẽ nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Skill sẽ nhận 50 Năng Lượng Giấc Mơ, và hồi máu cho Resonator bằng Resonance Skill sẽ nhận thêm 50 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây DMG lên mục tiêu bị ảnh hưởng bởi Spectro Frazzle sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh. Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh. Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Trợ Thủ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong lãnh địa, một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức. Sử dụng Waveplates để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 càng cao, Khám Phá trong Ảo Cảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh làm phần thưởng. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 khi Ảo Cảnh được thiết lập lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, Khám Phá trong Ảo Cảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh làm phần thưởng. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 khi Ảo Cảnh được thiết lập lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -29145,19 +29145,19 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Carlotta, Zhezhi, Lingyang, Sanhua, Youhu. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points Ảo Ảnh gấp 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Carlotta, Zhezhi, Lingyang, Sanhua, Youhu. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm Ảo Ảnh gấp 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Glacio DMG.
-- Đánh trúng mục tiêu bằng Basic Attack sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Liberation sẽ nhận được 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Glacio DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Táo. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Táo kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Glacio.
+- Đánh trúng mục tiêu bằng Đòn Cơ Bản sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Liberation sẽ nhận được 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Glacio sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Táo. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Táo kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Illusive Realm. Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
-- Trong Illusive Realm, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có đánh dấu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh Táo thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Illusive Realm sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Cõi Ảo Ảnh. Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
+- Trong Cõi Ảo Ảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có đánh dấu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh Táo thông qua Hỗ Trợ Giấc Mơ.
+- Mỗi trận chiến trong Cõi Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong lãnh địa, một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Illusive Realm, cùng với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh hơn làm phần thưởng. Difficulty của Illusive Realm phụ thuộc vào Pha SOL3 mà cậu đang ở khi Illusive Realm được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Cõi Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh hơn làm phần thưởng. Độ khó của Cõi Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Cõi Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -29238,19 +29238,19 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Camellya, Roccia, Danjin, Baizhi. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng 150% Points Ảo Ảnh!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Camellya, Roccia, Danjin, Baizhi. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng 150% Điểm Ảo Ảnh!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Havoc DMG.
-- Basic Attack trúng mục tiêu sẽ nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Attack mạnh trúng mục tiêu sẽ nhận 10 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Havoc DMG sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Thức. Trong trạng thái này, một số Ảo Ảnh sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Havoc.
+- Basic Attack trúng mục tiêu sẽ nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Tấn công mạnh trúng mục tiêu sẽ nhận 10 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Havoc sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Thức. Trong trạng thái này, một số Ảo Ảnh sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo Ảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ảo Ảnh. Những Ảo Ảnh có đánh dấu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh Thức thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong Thế Giới Ảo Ảnh, một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 càng cao, Thế Giới Ảo Ảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh làm phần thưởng. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, Thế Giới Ảo Ảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh làm phần thưởng. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -29331,19 +29331,19 @@
         <is>
           <t>Ký ức quá khứ chôn sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Brant, Changli, Encore, Chixia, Mortefi. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points Ảo Ảnh tăng 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Brant, Changli, Encore, Chixia, Mortefi. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm Ảo Ảnh tăng 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Fusion DMG.
-- Khi tấn công mục tiêu bằng Basic Attack, nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Intro Skill nhận 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Fusion DMG nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, bước vào Lucid Dream. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Fusion.
+- Khi tấn công mục tiêu bằng Đòn Cơ Bản, nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Kỹ Năng Khởi Động nhận 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Fusion nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, bước vào Giấc Mơ Sáng Suốt. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
-- Trong Thế Giới Ảo Ảnh, cậu có thể nhận được sức mạnh tăng cường từ các Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Lucid Dream thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
+- Trong Thế Giới Ảo Ảnh, cậu có thể nhận được sức mạnh tăng cường từ các Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Sáng Suốt thông qua Hỗ Trợ Giấc Mơ.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại kẻ địch mạnh nhất ở sâu nhất trong lãnh địa, một Tinh Thể Tàn Dư sẽ xuất hiện trong Vùng Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Thế Giới Ảo Ảnh với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh làm phần thưởng. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Thế Giới Ảo Ảnh với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh làm phần thưởng. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -29424,19 +29424,19 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Jinhsi, Phoebe, Shorekeeper, Verina. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng 150% Points Ảo Ảnh!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Jinhsi, Phoebe, Shorekeeper, Verina. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng 150% Điểm Ảo Ảnh!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Spectro DMG Bonus.
-- Attack cơ bản trúng mục tiêu sẽ hồi 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Skill sẽ hồi 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Spectro DMG sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Thức. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Energy Regen của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Tăng Sát Thương Spectro.
+- Tấn Công cơ bản trúng mục tiêu sẽ hồi 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Skill sẽ hồi 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Spectro sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Thức. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo Ảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có đánh dấu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh Thức thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đưa cậu đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đưa cậu đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong Thế Giới Ảo Ảnh, một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 càng cao, Khám Phá trong Thế Giới Ảo Ảnh càng thử thách hơn, đồng thời mang lại nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh hơn. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, Khám Phá trong Thế Giới Ảo Ảnh càng thử thách hơn, đồng thời mang lại nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh hơn. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -29517,19 +29517,19 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Jiyan, Jianxin, Mortefi, Yangyang, Aalto. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng 150% Points Ảo Ảnh!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Jiyan, Jianxin, Mortefi, Yangyang, Aalto. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng 150% Điểm Ảo Ảnh!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Aero DMG.
-- Đánh trúng mục tiêu bằng Basic Attack sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Liberation sẽ nhận được 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Aero DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Lucid Dream. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Aero.
+- Đánh trúng mục tiêu bằng Đòn Cơ Bản sẽ nhận được 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Liberation sẽ nhận được 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Aero sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Sáng Suốt. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
-- Trong Thế Giới Ảo Ảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có đánh dấu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Lucid Dream thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
+- Trong Thế Giới Ảo Ảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có đánh dấu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Sáng Suốt thông qua Hỗ Trợ Giấc Mơ.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong vương quốc. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh làm phần thưởng. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh làm phần thưởng. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -29610,19 +29610,19 @@
         <is>
           <t>Ký ức quá khứ chôn sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Xiangli Yao, Yinlin, Calcharo, Yuanwu. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thêm 150% Points Ảo Ảnh!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Xiangli Yao, Yinlin, Calcharo, Yuanwu. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thêm 150% Điểm Ảo Ảnh!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Electro DMG.
-- Khi đánh trúng mục tiêu bằng Basic Attack, nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Intro Skill nhận 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Electro DMG nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, tiến vào Trạng Thái Giấc Mơ Tỉnh Táo. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Trạng Thái Giấc Mơ Tỉnh Táo kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Electro.
+- Khi đánh trúng mục tiêu bằng Đòn Cơ Bản, nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Kỹ Năng Khởi Động nhận 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Electro nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, tiến vào Trạng Thái Giấc Mơ Tỉnh Táo. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Trạng Thái Giấc Mơ Tỉnh Táo kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và tham gia những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và tham gia những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo Ảnh, cậu có thể nhận được sức mạnh tăng cường từ các Ẩn Dụ. Những Ẩn Dụ có sức mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Trạng Thái Giấc Mơ Tỉnh Táo thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong Thế Giới Ảo Ảnh, một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 càng cao, việc Khám Phá trong Thế Giới Ảo Ảnh càng thử thách hơn, với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh làm phần thưởng. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong chu kỳ khám phá hiện tại sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ đó.</t>
+Pha SOL3 càng cao, việc Khám Phá trong Thế Giới Ảo Ảnh càng thử thách hơn, với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh làm phần thưởng. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong chu kỳ khám phá hiện tại sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ đó.</t>
         </is>
       </c>
     </row>
@@ -29703,19 +29703,19 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Camellya, Roccia, Danjin, Baizhi, Cantarella. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points Ảo Ảnh gấp 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Camellya, Roccia, Danjin, Baizhi, Cantarella. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm Ảo Ảnh gấp 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Havoc DMG.
-- Basic Attack trúng mục tiêu sẽ nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần. Heavy Attack trúng mục tiêu sẽ nhận 10 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi 10 giây một lần. Gây Havoc DMG sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Havoc.
+- Basic Attack trúng mục tiêu sẽ nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần. Heavy Attack trúng mục tiêu sẽ nhận 10 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi 10 giây một lần. Gây Sát Thương Havoc sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Illusive Realm. Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
-- Trong Illusive Realm, cậu có thể nhận được sức mạnh tăng cường từ các Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Illusive Realm sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Cõi Ảo Ảnh. Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
+- Trong Cõi Ảo Ảnh, cậu có thể nhận được sức mạnh tăng cường từ các Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
+- Mỗi trận chiến trong Cõi Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong lãnh địa, một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Illusive Realm, cùng với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh làm phần thưởng. Difficulty của Illusive Realm phụ thuộc vào Pha SOL3 mà cậu đang ở khi Illusive Realm được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Cõi Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh làm phần thưởng. Độ khó của Cõi Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Cõi Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -29782,7 +29782,7 @@
       <c r="M426" t="inlineStr">
         <is>
           <t>Càng khám phá sâu, bạn sẽ càng gặp nhiều sinh vật biển với hình dạng kỳ lạ.
-Nâng cấp Khả Năng Fishing trong Hàng Hóa để tăng số lượng ô lưu trữ cho chiến lợi phẩm.</t>
+Nâng cấp Khả Năng Câu Cá trong Hàng Hóa để tăng số lượng ô lưu trữ cho chiến lợi phẩm.</t>
         </is>
       </c>
     </row>
@@ -29862,14 +29862,14 @@
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 30.
 [Khám phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Illusive Realm.
-- Skills Echo, chỉ số, cấp độ, Chuỗi Resonance và vũ khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Illusive Realm.
+- Kỹ năng Echo, chỉ số, cấp độ, Resonance Chain và vũ khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Tại Illusive Realm, cậu có thể nhận được những tăng cường mạnh mẽ từ Metaphor. Những Metaphor có đánh dấu Dreamscape Power sẽ mang lại hiệu ứng bổ sung khi kích hoạt Divined Dream thông qua Dreamscape Aid.
 - Mỗi trận chiến trong Illusive Realm sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Illusive Points và đạt các mốc để nhận những phần thưởng hậu hĩnh.
 [Tinh thể Tàn Dư]
 Sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong Illusive Realm, một Tinh thể Tàn Dư sẽ xuất hiện tại Memory Zone. Sử dụng Waveplate để thu thập phần thưởng từ nó.
-[Difficulty]
-Pha SOL3 càng cao, việc khám phá Illusive Realm càng thử thách hơn, đồng thời phần thưởng từ Tinh thể Tàn Dư và Illusive Points cũng nhiều hơn. Difficulty của Illusive Realm phụ thuộc vào Pha SOL3 hiện tại khi Illusive Realm được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong chu kỳ khám phá không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+[Độ khó]
+Pha SOL3 càng cao, việc khám phá Illusive Realm càng thử thách hơn, đồng thời phần thưởng từ Tinh thể Tàn Dư và Illusive Points cũng nhiều hơn. Độ khó của Illusive Realm phụ thuộc vào Pha SOL3 hiện tại khi Illusive Realm được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong chu kỳ khám phá không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -29942,14 +29942,14 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Rules Fishing Spots:
-1. Có hai loại Fishing Spots: Fishing Spots Sinh Vật Biển và Fishing Spots Nguyên Liệu, mỗi loại cung cấp tài nguyên khác nhau.
-2. Mỗi Fishing Spots yêu cầu một Khả Năng Fishing cụ thể để truy cập. Xem chi tiết tại trang Khả Năng Fishing.
-3. Mỗi Fishing Spots có số lần thu hoạch giới hạn. Khi cạn kiệt, điểm sẽ biến mất và tự động tái tạo sau một khoảng thời gian, có thể ở vị trí khác.
-Fishing Rules:
-1. Khi lao móc câu rơi vào vùng phát sáng, {Cus:Ipt,Touch=tap PC=click Gamepad=press} nút để tăng Tiến Độ Fishing. Vùng sáng càng mạnh, tốc độ tăng càng nhanh.
-2. Khi Tiến Độ Fishing đạt 100%, một Fishing Attempts sẽ bị tiêu hao, và bạn có cơ hội bắt được mục tiêu.
-3. Khi dùng hết tất cả Fishing Attempts, bạn không thể câu tiếp và sẽ tiến hành xử lý kho chứa chiến lợi phẩm.
+          <t>Quy Tắc Điểm Câu:
+1. Có hai loại Điểm Câu: Điểm Câu Sinh Vật Biển và Điểm Câu Nguyên Liệu, mỗi loại cung cấp tài nguyên khác nhau.
+2. Mỗi Điểm Câu yêu cầu một Khả Năng Câu Cá cụ thể để truy cập. Xem chi tiết tại trang Khả Năng Câu Cá.
+3. Mỗi Điểm Câu có số lần thu hoạch giới hạn. Khi cạn kiệt, điểm sẽ biến mất và tự động tái tạo sau một khoảng thời gian, có thể ở vị trí khác.
+Quy Tắc Câu Cá:
+1. Khi lao móc câu rơi vào vùng phát sáng, {Cus:Ipt,Touch=tap PC=click Gamepad=press} nút để tăng Tiến Độ Câu Cá. Vùng sáng càng mạnh, tốc độ tăng càng nhanh.
+2. Khi Tiến Độ Câu Cá đạt 100%, một Lượt Câu sẽ bị tiêu hao, và bạn có cơ hội bắt được mục tiêu.
+3. Khi dùng hết tất cả Lượt Câu, bạn không thể câu tiếp và sẽ tiến hành xử lý kho chứa chiến lợi phẩm.
 4. Trong quá trình câu, bạn có thể mở trang Hàng Hóa để quản lý chiến lợi phẩm. Làm vậy sẽ làm gián đoạn lượt câu hiện tại.</t>
         </is>
       </c>
@@ -30019,9 +30019,9 @@
       <c r="M429" t="inlineStr">
         <is>
           <t>Trong thử thách này:
-&lt;color=Highlight&gt;Roccia's&lt;/color&gt; của Roccia không có Cooldown.
-Chi phí STA khi bay được giảm.
-Buff chính: &lt;color=Highlight&gt;Dash and Plunge Attack&lt;/color&gt; triệu hồi Cyclone gây Havoc DMG.</t>
+&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của &lt;color=Highlight&gt;Roccia&lt;/color&gt; không có thời gian hồi chiêu.
+Chi phí STA khi bay giảm.
+Tăng cường chính: &lt;color=Highlight&gt;Lao và Tấn Công Hạ Bay&lt;/color&gt; sẽ triệu hồi Lốc Xoáy gây DMG Havoc.</t>
         </is>
       </c>
     </row>
@@ -30090,9 +30090,9 @@
       <c r="M430" t="inlineStr">
         <is>
           <t>Trong thử thách này:
-&lt;color=Highlight&gt;Roccia's&lt;/color&gt; của Roccia không có Cooldown.
-Chi phí STA khi bay được giảm.
-Buff chính: &lt;color=Highlight&gt;Dash and Plunge Attack&lt;/color&gt; triệu hồi Cyclone gây Havoc DMG.</t>
+&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của &lt;color=Highlight&gt;Roccia&lt;/color&gt; không có thời gian hồi chiêu.
+Chi phí STA khi bay giảm.
+Tăng cường chính: &lt;color=Highlight&gt;Lao và Tấn Công Hạ Bay&lt;/color&gt; sẽ triệu hồi Lốc Xoáy gây DMG Havoc.</t>
         </is>
       </c>
     </row>
@@ -30161,9 +30161,9 @@
       <c r="M431" t="inlineStr">
         <is>
           <t>Trong thử thách này:
-&lt;color=Highlight&gt;Phoebe&lt;/color&gt; có thể sử dụng Đòn Tấn Công Nặng giữa không trung không giới hạn.
+&lt;color=Highlight&gt;Phoebe&lt;/color&gt; có thể sử dụng Đòn Heavy Attack giữa không trung không giới hạn.
 Chi phí STA khi bay giảm.
-Tăng cường chính: &lt;color=Highlight&gt;Casting intro Skill&lt;/color&gt; cũng sẽ gây Aero Erosion và Spectro Frazzle lên mục tiêu.</t>
+Tăng cường chính: &lt;color=Highlight&gt;Kích hoạt Kỹ Năng giới thiệu&lt;/color&gt; cũng sẽ gây Aero Erosion và Spectro Frazzle lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -30232,9 +30232,9 @@
       <c r="M432" t="inlineStr">
         <is>
           <t>Trong thử thách này:
-&lt;color=Highlight&gt;Changli&lt;/color&gt; duy trì trạng thái &lt;color=Highlight&gt;True Sight&lt;/color&gt;.
-Chi phí STA khi bay được giảm.
-Buff chính: &lt;color=Highlight&gt;Mid-air Attack&lt;/color&gt; triệu hồi Thiên Thạch khi trúng đích, gây Fusion DMG.</t>
+&lt;color=Highlight&gt;Changli&lt;/color&gt; duy trì trạng thái &lt;color=Highlight&gt;Thị Giác Chân Thực&lt;/color&gt;.
+Chi phí STA khi bay giảm.
+Tăng cường chính: &lt;color=Highlight&gt;Tấn Công giữa không trung&lt;/color&gt; sẽ triệu hồi Thiên Thạch khi trúng mục tiêu, gây DMG Fusion.</t>
         </is>
       </c>
     </row>
@@ -30303,9 +30303,9 @@
       <c r="M433" t="inlineStr">
         <is>
           <t>Trong thử thách này:
-&lt;color=Highlight&gt;Lumi's&lt;/color&gt; của &lt;color=Highlight&gt;Yellow Light: Zoom&lt;/color&gt; không tiêu hao STA.
-Chi phí STA khi bay được giảm.
-Buff chính: &lt;color=Highlight&gt;Hitting a target with Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;dealing Basic Attack DMG&lt;/color&gt; sẽ triệu hồi thêm Starfall gây Electro DMG.</t>
+&lt;color=Highlight&gt;Yellow Light: Zoom&lt;/color&gt; của &lt;color=Highlight&gt;Lumi&lt;/color&gt; không tiêu hao STA.
+Chi phí STA khi bay giảm.
+Tăng cường chính: &lt;color=Highlight&gt;Đánh trúng mục tiêu bằng Đòn Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;gây DMG Đòn Basic Attack&lt;/color&gt; sẽ bổ sung thêm Sao Băng gây DMG Electro.</t>
         </is>
       </c>
     </row>
@@ -30566,8 +30566,8 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại kẻ địch trong Khu Vực Ký Ức, Tinh Thể Tàn Dư sẽ xuất hiện. Tiêu hao Waveplate để nhận thưởng. Pha SOL3 càng cao, Exploration càng thử thách nhưng phần thưởng Tinh Thể Tàn Dư cũng phong phú hơn.
-Rewards Tinh Thể Tàn Dư: Ống Niêm Phong, Bộ Điều Tần và Supply Chest chứa Echo từ Tacet Field đã chọn. Chi phí Waveplate để nhận thưởng tương đương với chi phí nhận thưởng Tacet Field.</t>
+          <t>Sau khi đánh bại kẻ địch trong Khu Vực Ký Ức, Tinh Thể Tàn Dư sẽ xuất hiện. Tiêu hao Waveplate để nhận thưởng. Pha SOL3 càng cao, Thám Hiểm càng thử thách nhưng phần thưởng Tinh Thể Tàn Dư cũng phong phú hơn.
+Phần thưởng Tinh Thể Tàn Dư: Ống Niêm Phong, Bộ Điều Tần và Rương Vật Tư chứa Tiếng Vọng từ Tổ Tacet đã chọn. Chi phí Waveplate để nhận thưởng tương đương với chi phí nhận thưởng Tổ Tacet.</t>
         </is>
       </c>
     </row>
@@ -30779,12 +30779,12 @@
 Điều Kiện Mở Khóa]
 Đạt Cấp Liên Minh 14 và hoàn thành Chương II Lời Mở Đầu của Nhiệm Vụ Chính.
 [
-Event Rules]
-1. Thu thập càng nhiều Tactic Points càng tốt trong Infinite Battle Simulation.
-2. Mỗi khu vực trong mô phỏng chứa nhiều Points Dẫn Đường.
-Đánh bại kẻ địch tại mỗi Points Dẫn Đường sẽ mang lại cho cậu một lượng lớn Tactic Points.
-3. Mở Rương Cung Ứng sau khi đánh bại kẻ địch để nhận Tactic Points và các hiệu ứng Biến Số Công Suất Low.
-4. Khi đã thu thập đủ Biến Số Công Suất Low, cậu có thể mở khóa các hiệu ứng mới mạnh mẽ hơn – Biến Số Công Suất High, giúp tăng cường đáng kể sức chiến đấu của cậu trong Infinite Battle Simulation.</t>
+Quy Tắc Sự Kiện]
+1. Thu thập càng nhiều Điểm Chiến Thuật càng tốt trong Mô Phỏng Chiến Đấu Vô Tận.
+2. Mỗi khu vực trong mô phỏng chứa nhiều Điểm Dẫn Đường.
+Đánh bại kẻ địch tại mỗi Điểm Dẫn Đường sẽ mang lại cho cậu một lượng lớn Điểm Chiến Thuật.
+3. Mở Rương Cung Ứng sau khi đánh bại kẻ địch để nhận Điểm Chiến Thuật và các hiệu ứng Biến Số Công Suất Thấp.
+4. Khi đã thu thập đủ Biến Số Công Suất Thấp, cậu có thể mở khóa các hiệu ứng mới mạnh mẽ hơn – Biến Số Công Suất Cao, giúp tăng cường đáng kể sức chiến đấu của cậu trong Mô Phỏng Chiến Đấu Vô Tận.</t>
         </is>
       </c>
     </row>
@@ -30856,12 +30856,12 @@
       <c r="M441" t="inlineStr">
         <is>
           <t>Về sự kiện
-Explore khu vực mới này để thu thập Astrites.
+Khám phá khu vực mới này để thu thập Astrites.
 Điều kiện tham gia
-Đạt Cấp Liên minh 14 và hoàn thành Nhiệm vụ Main "Vượt Qua Biển Cả" để mở khóa.
+Đạt Cấp Liên minh 14 và hoàn thành Nhiệm vụ Chính "Vượt Qua Biển Cả" để mở khóa.
 Quy tắc sự kiện
-Increase Progress Explore để nhận phần thưởng tại các mốc quan trọng.
-Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ vẫn khả dụng trong 30 ngày và sẽ được gửi lại qua Mail khi cậu đăng nhập trong khoảng thời gian này.</t>
+Tăng Tiến độ Khám phá để nhận phần thưởng tại các mốc quan trọng.
+Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ vẫn khả dụng trong 30 ngày và sẽ được gửi lại qua Thư khi cậu đăng nhập trong khoảng thời gian này.</t>
         </is>
       </c>
     </row>
@@ -30933,14 +30933,14 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Septimont Travel Atlas
+          <t>Bản Đồ Du Hành Septimont
 [Giới Thiệu]
-Explore khu vực mới này để thu thập Astrites.
+Khám phá khu vực mới này để thu thập Astrites.
 [Điều Kiện Mở Khóa]
 Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Vượt Biển Tới Bờ" để mở khóa.
-[Event Rules]
-Increase Exploration Progress để nhận phần thưởng tại các mốc nhất định.
-Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được giữ lại trong 30 ngày và sẽ được gửi lại qua Mail khi bạn đăng nhập trong thời gian này.</t>
+[Quy Tắc Sự Kiện]
+Tăng Tiến Độ Thám Hiểm để nhận phần thưởng tại các mốc nhất định.
+Sau khi sự kiện kết thúc, phần thưởng chưa nhận sẽ được giữ lại trong 30 ngày và sẽ được gửi lại qua Thư khi bạn đăng nhập trong thời gian này.</t>
         </is>
       </c>
     </row>
@@ -31009,7 +31009,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>1. Tính năng Global Filter cho phép bạn điều chỉnh hiệu ứng hình ảnh trong game. Lưu ý rằng các cảnh cắt và thành phần giao diện sẽ không bị ảnh hưởng bởi bộ lọc.</t>
+          <t>1. Tính năng Bộ Lọc Toàn Cục cho phép bạn điều chỉnh hiệu ứng hình ảnh trong game. Lưu ý rằng các cảnh cắt và thành phần giao diện sẽ không bị ảnh hưởng bởi bộ lọc.</t>
         </is>
       </c>
     </row>
@@ -31089,12 +31089,12 @@
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 22.
 [Quy tắc sự kiện]
-1. Trong thử thách này, bạn có thể chọn "Bạn Companions Của Dorothy" làm Echoes hỗ trợ trong trận chiến, giúp tăng cường đáng kể sức mạnh chiến đấu của Resonators.
-2. Resonators bị hạ gục sẽ tự động hồi sinh sau một thời gian.
+1. Trong thử thách này, bạn có thể chọn "Bạn Đồng Hành Của Dorothy" làm Echo hỗ trợ trong trận chiến, giúp tăng cường đáng kể sức mạnh chiến đấu của Resonator.
+2. Resonator bị hạ gục sẽ tự động hồi sinh sau một thời gian.
 3. Bạn có thể hoàn thành nhiệm vụ cùng Bạn bè.
-4. Trong chế độ này, chỉ được sử dụng Echoes được chỉ định (Sonata vẫn có hiệu lực và chỉ Skill Echoes chính bị thay thế).
-5. Cách tính điểm: Points Hoàn Thành + (Thời Gian Còn Lại x Hệ Số Thời Gian).
-Total điểm sẽ là tổng điểm cao nhất đạt được ở các màn thông thường. (Không tính điểm cho các màn thử thách).</t>
+4. Trong chế độ này, chỉ được sử dụng Echo được chỉ định (Sonata vẫn có hiệu lực và chỉ Skill Echo chính bị thay thế).
+5. Cách tính điểm: Điểm Hoàn Thành + (Thời Gian Còn Lại x Hệ Số Thời Gian).
+Tổng điểm sẽ là tổng điểm cao nhất đạt được ở các màn thông thường. (Không tính điểm cho các màn thử thách).</t>
         </is>
       </c>
     </row>
@@ -31185,23 +31185,23 @@
 [Điều kiện tham gia]
 Đạt Cấp Liên Minh 30.
 [Thử thách Khủng hoảng]
-Với tư cách thành viên Bờ Đen, bạn sẽ đối mặt với các thử thách dưới nhiều Stress Modules khác nhau.
+Với tư cách thành viên Bờ Đen, bạn sẽ đối mặt với các thử thách dưới nhiều Mô-đun Áp Lực khác nhau.
 Chọn Mức Độ Áp Lực cho mỗi thử thách. Mức Độ Áp Lực phải đáp ứng yêu cầu để hoàn thành thử thách.
-Mỗi thử thách có một Stress Modules mặc định. Các Hỗ Trợ Mô-đun có thể được sử dụng để giảm độ khó của thử thách.
-Sau khi hoàn thành một Thử thách Khủng hoảng, Thử thách Thảm họa tương ứng cùng Stress Modules và Hỗ Trợ Mô-đun sẽ được mở khóa.
+Mỗi thử thách có một Mô-đun Áp Lực mặc định. Các Mô-đun Hỗ trợ có thể được sử dụng để giảm độ khó của thử thách.
+Sau khi hoàn thành một Thử thách Khủng hoảng, Thử thách Thảm họa tương ứng cùng Mô-đun Áp Lực và Mô-đun Hỗ trợ sẽ được mở khóa.
 [Thử thách Thảm họa]
 Để thu thập thêm dữ liệu chiến đấu và cải thiện kế hoạch ứng phó khủng hoảng của Bờ Đen, chương trình huấn luyện này còn bao gồm Chế độ Khó.
-Với tư cách thành viên Bờ Đen, bạn sẽ đối mặt với &lt;color=#c89a45&gt;hard challenges&lt;/color&gt; với nhiều tổ hợp Stress Modules khác nhau.
+Với tư cách thành viên Bờ Đen, bạn sẽ đối mặt với &lt;color=#c89a45&gt;những thử thách cam go&lt;/color&gt; với nhiều tổ hợp Mô-đun Áp Lực khác nhau.
 Thử thách Thảm họa không yêu cầu Mức Độ Áp Lực cụ thể. Dữ liệu sẽ được thu thập từ những người tham gia khi họ đẩy giới hạn của bản thân.
-Tham gia Thử thách Thảm họa sẽ tiêu hao Hỗ Trợ Mô-đun, vì vậy hãy lựa chọn cẩn thận trước khi bắt đầu.
-Một số Stress Modules có độ khó cao chỉ có thể mở khóa sau khi vượt qua Thử thách Thảm họa.
-&lt;color=#c89a45&gt;Warning: Equipping too many Stress Modules may make the trial excessively challenging.&lt;/color&gt;
+Tham gia Thử thách Thảm họa sẽ tiêu hao Mô-đun Hỗ trợ, vì vậy hãy lựa chọn cẩn thận trước khi bắt đầu.
+Một số Mô-đun Áp Lực có độ khó cao chỉ có thể mở khóa sau khi vượt qua Thử thách Thảm họa.
+&lt;color=#c89a45&gt;Cảnh báo: Trang bị quá nhiều Mô-đun Áp Lực có thể khiến thử thách trở nên cực kỳ khó khăn.&lt;/color&gt;
 [Cơ chế hồi sinh]
 Nếu người tham gia bị đánh bại trong thử thách, họ có thể tiêu hao Mức Độ Áp Lực để hồi sinh. Điều này cũng mang lại hiệu ứng tăng cường tương ứng.
-Lưu ý rằng việc tiêu hao Mức Độ Áp Lực sẽ ảnh hưởng đến việc hoàn thành và kết quả cuối cùng của Challenge Goals.
+Lưu ý rằng việc tiêu hao Mức Độ Áp Lực sẽ ảnh hưởng đến việc hoàn thành và kết quả cuối cùng của Mục tiêu Thử thách.
 [Tinh thể Ma trận]
-Nhận Tinh thể Ma trận bằng cách hoàn thành Challenge Goals trong Thử thách Khủng hoảng và Thảm họa. Tinh thể Ma trận có thể được đổi lấy phần thưởng tại Supply Station. Hoàn thành một số thử thách Mức Độ Áp Lực nhất định trong Thử thách Thảm họa sẽ nhận được &lt;color=#c89a45&gt;event-exclusive Title reward&lt;/color&gt;.
-&lt;color=#c89a45&gt;The Supply Station closes when this event ends. Tất cả remaining Matrix Crystals will expire and will not be reserved after the event ends. Please exchange your Matrix Crystals in time.&lt;/color&gt;</t>
+Nhận Tinh thể Ma trận bằng cách hoàn thành Mục tiêu Thử thách trong Thử thách Khủng hoảng và Thảm họa. Tinh thể Ma trận có thể được đổi lấy phần thưởng tại Trạm Cung ứng. Hoàn thành một số thử thách Mức Độ Áp Lực nhất định trong Thử thách Thảm họa sẽ nhận được &lt;color=#c89a45&gt;Danh hiệu độc quyền sự kiện&lt;/color&gt;.
+&lt;color=#c89a45&gt;Trạm Cung ứng sẽ đóng cửa khi sự kiện kết thúc. Tất cả Tinh thể Ma trận còn lại sẽ hết hạn và không được bảo lưu sau khi sự kiện kết thúc. Hãy đổi Tinh thể Ma trận của bạn kịp thời.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -31266,7 +31266,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>{0} Dùng đèn để xua tan bóng tối bao phủ kẻ địch.</t>
+          <t>Dùng đèn để xua tan bóng tối che phủ kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -31333,9 +31333,9 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Mũi tên truy đuổi độc nhất của Sagittario sẽ đánh dấu Resonators trong một khoảng thời gian nhất định sau khi trúng đích.
-Khi dấu hiệu còn hiệu lực, Sagittario sẽ bắn một mũi tên truy đuổi vào Resonators mỗi khi họ chịu sát thương.
-Việc chuyển đổi Resonators sẽ xóa dấu hiệu này.</t>
+          <t>Mũi tên truy đuổi độc nhất của Sagittario sẽ đánh dấu Resonator trong một khoảng thời gian nhất định sau khi trúng đích.
+Khi dấu hiệu còn hiệu lực, Sagittario sẽ bắn một mũi tên truy đuổi vào Resonator mỗi khi họ chịu sát thương.
+Việc chuyển đổi Resonator sẽ xóa dấu hiệu này.</t>
         </is>
       </c>
     </row>
@@ -31403,7 +31403,7 @@
       <c r="M448" t="inlineStr">
         <is>
           <t>Sacerdos có thể thiết lập liên kết với kẻ địch đồng minh.
-Khi kẻ địch bị liên kết chịu sát thương, một vùng gió sẽ được tạo ra, đẩy lùi Resonators ở gần. Vùng gió có độ trễ giữa các lần kích hoạt.
+Khi kẻ địch bị liên kết chịu sát thương, một vùng gió sẽ được tạo ra, đẩy lùi các Resonator ở gần. Vùng gió có độ trễ giữa các lần kích hoạt.
 Cùng một kẻ địch không thể bị liên kết bởi nhiều Sacerdos.</t>
         </is>
       </c>
@@ -31471,8 +31471,8 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Rover học được kỹ năng mới. Thi triển &lt;color=#ffd12f&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=#ffd12f&gt;holding Basic Attack&lt;/color&gt; để nhảy lên không.
-Các đòn Mid-air Attack, Intro Skill và Basic Attack được tăng cường sẽ tích lũy Sợi Gió.
+          <t>Rover học được kỹ năng mới. Thi triển &lt;color=#ffd12f&gt;Resonance Skill&lt;/color&gt; hoặc &lt;color=#ffd12f&gt;giữ Đòn Basic Attack&lt;/color&gt; để nhảy lên không.
+Các đòn Mid-air Attack, Kỹ Năng Khởi Động và Đòn Basic Attack được tăng cường sẽ tích lũy Sợi Gió.
 Khi đạt Sợi Gió tối đa, có thể thi triển Resonance Skill được tăng cường.</t>
         </is>
       </c>
@@ -31539,8 +31539,8 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Kẻ địch đến từ chiều không gian khác bị bao phủ bởi bóng tối, khiến chúng &lt;color=#ffd12f&gt;immunity to all forms of attack&lt;/color&gt;.
-Hãy dùng đèn và &lt;color=#ffd12f&gt;switch to their respective dimensions&lt;/color&gt; để xóa bóng tối và khiến chúng dễ bị tổn thương trở lại.</t>
+          <t>Kẻ địch đến từ chiều không gian khác bị bao phủ bởi bóng tối, khiến chúng &lt;color=#ffd12f&gt;miễn nhiễm với mọi hình thức tấn công&lt;/color&gt;.
+Hãy dùng đèn và &lt;color=#ffd12f&gt;chuyển sang chiều không gian tương ứng&lt;/color&gt; để xóa bóng tối và khiến chúng dễ bị tổn thương trở lại.</t>
         </is>
       </c>
     </row>
@@ -31607,8 +31607,8 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Vật thể ám ảnh của vị tộc trưởng quá cố của Fisalia đang ở trong trạng thái bóng tối đặc biệt, khiến chúng &lt;color=#ffd12f&gt;immune to all forms of attack&lt;/color&gt;.
-Trong trận chiến, năng lượng của chiếc đèn có thể được nạp &lt;color=#ffd12f&gt;by performing Dodge and Counterattack&lt;/color&gt;.
+          <t>Vật thể ám ảnh của vị tộc trưởng quá cố của Fisalia đang ở trong trạng thái bóng tối đặc biệt, khiến chúng &lt;color=#ffd12f&gt;miễn nhiễm với mọi hình thức tấn công&lt;/color&gt;.
+Trong trận chiến, năng lượng của chiếc đèn có thể được nạp &lt;color=#ffd12f&gt;bằng cách né tránh và phản công&lt;/color&gt;.
 Khi nạp đầy, chiếc đèn sẽ phát ra luồng sáng mạnh mẽ để xua tan bóng tối, khiến kẻ địch trở nên dễ tổn thương trước các đòn tấn công.</t>
         </is>
       </c>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Khi bắt đầu thử thách, nhận một lá chắn tương đương 20% HP tối đa. Sau khi không nhận sát thương trong 3 giây, nhận thêm một lá chắn tương đương 20% HP tối đa.</t>
+          <t>Khi bắt đầu thử thách, nhận một lá chắn tương đương 20% HP tối đa. Sau khi không nhận DMG trong 3 giây, nhận thêm một lá chắn tương đương 20% HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -31739,7 +31739,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Đánh trúng mục tiêu sẽ tăng Tấn Công của bạn thêm 20%, tối đa 80%.</t>
+          <t>Đánh trúng mục tiêu sẽ tăng ATK của bạn thêm 20%, tối đa 80%.</t>
         </is>
       </c>
     </row>
@@ -31804,7 +31804,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Tấn Công tăng 30% trong 5 giây khi đồng đội ở trong phạm vi 15 mét quanh bạn.</t>
+          <t>ATK tăng 30% trong 5 giây khi đồng đội ở trong phạm vi 15 mét quanh bạn.</t>
         </is>
       </c>
     </row>
@@ -31937,8 +31937,8 @@
       <c r="M456" t="inlineStr">
         <is>
           <t>Trong trận đấu, kết quả tung xúc xắc sẽ quyết định Cube nào di chuyển trước và đi được bao xa.
-Các Cube trên cùng một bệ sẽ &lt;color=#ffd12f&gt;stack&lt;/color&gt;. Khi Cube ở dưới di chuyển, nó sẽ &lt;color=#ffd12f&gt;carry along&lt;/color&gt; tất cả các Cube chồng phía trên.
-Trong một lượt, &lt;color=#ffd12f&gt;there is a chance&lt;/color&gt; một Cube kích hoạt &lt;color=#ffd12f&gt;Ability&lt;/color&gt; đặc biệt của riêng nó.</t>
+Các Cube trên cùng một bệ sẽ &lt;color=#ffd12f&gt;chồng lên nhau&lt;/color&gt;. Khi Cube ở dưới di chuyển, nó sẽ &lt;color=#ffd12f&gt;kéo theo&lt;/color&gt; tất cả các Cube chồng phía trên.
+Trong một lượt, &lt;color=#ffd12f&gt;có xác suất&lt;/color&gt; một Cube kích hoạt &lt;color=#ffd12f&gt;Khả Năng&lt;/color&gt; đặc biệt của riêng nó.</t>
         </is>
       </c>
     </row>
@@ -32020,20 +32020,20 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Zani, Jinhsi, Phoebe, Shorekeeper và Verina. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points Ảo Ảnh gấp 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Zani, Jinhsi, Phoebe, Shorekeeper và Verina. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm Ảo Ảnh gấp 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Spectro DMG.
-- Khi Basic Attack trúng mục tiêu, nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Skill sẽ nhận 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Spectro DMG sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, bước vào Trạng Thái Lucid Dream. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Trạng Thái Lucid Dream kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Spectro.
+- Khi Basic Attack trúng mục tiêu, nhận 20 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần. Sử dụng Resonance Skill sẽ nhận 100 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi 10 giây một lần. Gây Sát Thương Spectro sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, bước vào Trạng Thái Giấc Mơ Sáng Suốt. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Trạng Thái Giấc Mơ Sáng Suốt kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
-- Trong Thế Giới Ảo Ảnh, cậu có thể nhận được sức mạnh gia tăng từ các Ẩn Dụ. Những Ẩn Dụ có đánh dấu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Trạng Thái Lucid Dream thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
+- Trong Thế Giới Ảo Ảnh, cậu có thể nhận được sức mạnh gia tăng từ các Ẩn Dụ. Những Ẩn Dụ có đánh dấu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Trạng Thái Giấc Mơ Sáng Suốt thông qua Hỗ Trợ Giấc Mơ.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong vương quốc, một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức. Sử dụng Waveplates để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 càng cao, Exploration trong Thế Giới Ảo Ảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh làm phần thưởng. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, Thám Hiểm trong Thế Giới Ảo Ảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh làm phần thưởng. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -32115,20 +32115,20 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên nhé, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Brant, Changli, Encore, Chixia, Mortefi. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng 150% Points Ảo Ảnh!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Brant, Changli, Encore, Chixia, Mortefi. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng 150% Điểm Ảo Ảnh!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Sát Thương Hệ.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Hệ.
 - Gây Sát Thương Hệ sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo Ảnh, cậu có thể nhận được sức mạnh gia tăng từ các Ẩn Dụ. Những Ẩn Dụ có sức mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong vương quốc, một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh hơn làm phần thưởng. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh hơn làm phần thưởng. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -32210,20 +32210,20 @@
         <is>
           <t>Những ký ức quá khứ chôn sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Camellya, Roccia, Danjin, Baizhi, Cantarella. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points Ảo Ảnh 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Camellya, Roccia, Danjin, Baizhi, Cantarella. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm Ảo Ảnh 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Havoc DMG.
-- Gây Havoc DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Havoc.
+- Gây Sát Thương Havoc sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo Ảnh, cậu có thể nhận được sức mạnh gia tăng từ các Ẩn Dụ. Những Ẩn Dụ có sức mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong thế giới, một Tinh Thể Tàn Dư sẽ xuất hiện tại Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng phần thưởng là nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh hơn. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng phần thưởng là nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh hơn. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -32305,20 +32305,20 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên nhé, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang, Aalto. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thêm 150% Points Ảo Ảnh!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang, Aalto. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thêm 150% Điểm Ảo Ảnh!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Aero DMG.
-- Gây Aero DMG sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Táo. Trong trạng thái này, một số Ảo Ảnh sẽ được tăng cường, Crit. Rate và Energy Regen của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Táo kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Aero.
+- Gây Sát Thương Aero sẽ hồi 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Táo. Trong trạng thái này, một số Ảo Ảnh sẽ được tăng cường, Crit. Rate và Hồi Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Táo kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo Ảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ảo Ảnh. Những Ảo Ảnh có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh Táo thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong Thế Giới Ảo Ảnh, một Tinh Thể Tàn Dư sẽ xuất hiện tại Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng từ nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh hơn làm phần thưởng. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh hơn làm phần thưởng. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -32400,20 +32400,20 @@
         <is>
           <t>Ký ức quá khứ chôn sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Xiangli Yao, Yinlin, Calcharo, Yuanwu. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng 150% Points Ảo Ảnh!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Xiangli Yao, Yinlin, Calcharo, Yuanwu. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng 150% Điểm Ảo Ảnh!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Electro DMG.
-- Gây Electro DMG sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, tiến vào Trạng Thái Mơ Thức. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Trạng Thái Mơ Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Electro.
+- Gây Sát Thương Electro sẽ nhận 30 Năng Lượng Giấc Mơ. Hiệu ứng này kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, tiến vào Trạng Thái Mơ Thức. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Trạng Thái Mơ Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo Ảnh, cậu có thể nhận được sức mạnh gia tăng từ các Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Trạng Thái Mơ Thức thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong lãnh địa, một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng phần thưởng là nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh hơn. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng phần thưởng là nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh hơn. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -32494,19 +32494,19 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên nhé, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Carlotta, Zhezhi, Lingyang, Sanhua, Youhu. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng 150% Points Ảo Ảnh!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Carlotta, Zhezhi, Lingyang, Sanhua, Youhu. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng 150% Điểm Ảo Ảnh!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Glacio DMG.
-- Gây Glacio DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Thức. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Glacio.
+- Gây Sát Thương Glacio sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Thức. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo Ảnh. Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo Ảnh, cậu có thể nhận được sức mạnh gia tăng từ các Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh Thức thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong Thế Giới Ảo Ảnh, một Tinh Thể Tàn Dư sẽ xuất hiện tại Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh hơn làm phần thưởng. Difficulty của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh hơn làm phần thưởng. Độ khó của Thế Giới Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -32585,11 +32585,11 @@
       <c r="M463" t="inlineStr">
         <is>
           <t>Về sự kiện
-Lễ hội sắp bắt đầu. Invite bạn bè trở lại cùng tham gia vui chơi tại Rinascita. Hoàn thành nhiệm vụ cùng nhau để nhận Astrites và những phần thưởng khác!
+Lễ hội sắp bắt đầu. Mời bạn bè trở lại cùng tham gia vui chơi tại Rinascita. Hoàn thành nhiệm vụ cùng nhau để nhận Astrites và những phần thưởng khác!
 Điều kiện tham gia
 Đạt Cấp Liên Minh 8 trở lên trong thời gian diễn ra sự kiện.
 Thể lệ
-1. Share mã mời của bạn với tối đa 3 người chơi quay lại trong cùng máy chủ, hoàn thành nhiệm vụ trong game để nhận Bong Bóng Lễ Hội và đổi lấy tối đa Astrite x480 cùng Shell Credit x300.000.
+1. Chia sẻ mã mời của bạn với tối đa 3 người chơi quay lại trong cùng máy chủ, hoàn thành nhiệm vụ trong game để nhận Bong Bóng Lễ Hội và đổi lấy tối đa Astrite x480 cùng Shell Credit x300.000.
 2. Người chơi quay lại có thể liên kết tài khoản với người chơi đã mời bằng mã mời tương ứng. Việc liên kết chỉ thực hiện được một lần và không thể thay đổi sau đó. Sau khi liên kết, người chơi quay lại đủ điều kiện nhận phần thưởng gồm Astrite x50, Advanced Enclosure Tank x5 và Shell Credit x50.000.
 Điều kiện người chơi quay lại
 1. Cấp Liên Minh 8 trở lên.
@@ -32662,7 +32662,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Dùng {0} Kỹ Năng Cube để đánh bại tay sai của Abbowser!</t>
+          <t>{0} Dùng Kỹ Năng Khối để đánh bại tay sai của Abbowser!</t>
         </is>
       </c>
     </row>
@@ -32730,7 +32730,7 @@
       <c r="M465" t="inlineStr">
         <is>
           <t>Trong trận đấu, kết quả tung xúc xắc sẽ quyết định Cube nào di chuyển trước và đi được bao xa.
-&lt;color=#ffd12f&gt;There is a chance&lt;/color&gt; một Cube kích hoạt &lt;color=#ffd12f&gt;Ability&lt;/color&gt; đặc biệt của riêng nó để cố gắng về đích trước.
+&lt;color=#ffd12f&gt;Có xác suất&lt;/color&gt; một Cube kích hoạt &lt;color=#ffd12f&gt;Khả Năng&lt;/color&gt; đặc biệt của riêng nó để cố gắng về đích trước.
 Những Cube đến sau sẽ chồng lên những Cube đã đến trước trên bệ đích.</t>
         </is>
       </c>
@@ -32796,7 +32796,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Synergy Burst khiến tất cả kẻ địch bất động, cung cấp nhiều hiệu ứng tăng cường chiến đấu và kích hoạt Synergy Burst bổ sung từ Liên Kết của Synergy Giả chủ động.</t>
+          <t>Cộng Hưởng Bùng Nổ khiến tất cả kẻ địch bất động, cung cấp nhiều hiệu ứng tăng cường chiến đấu và kích hoạt Cộng Hưởng Bùng Nổ bổ sung từ Liên Kết của Resonator chủ động.</t>
         </is>
       </c>
     </row>
@@ -32867,11 +32867,11 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>1. Tham gia Abbowser Castle cùng tối đa 3 Đồng Minh Cube. Đồng Minh Cube sẽ chủ động hỗ trợ bạn trong trận chiến. Ngoài ra, khi sử dụng Kỹ Năng Dội Âm, kỹ năng chủ động của Đồng Minh Cube cũng sẽ được kích hoạt.
-2. Mỗi tầng của Abbowser Castle cung cấp Mô-đun Data, giúp tăng cường sức mạnh chiến đấu cho Cube của bạn một cách đáng kể. Một số mô-đun còn đi kèm hiệu ứng kỹ năng bổ sung.
+          <t>1. Tham gia Lâu Đài Abbowser cùng tối đa 3 Đồng Minh Khối Lập Phương. Đồng Minh Khối Lập Phương sẽ chủ động hỗ trợ bạn trong trận chiến. Ngoài ra, khi sử dụng Kỹ Năng Dội Âm, kỹ năng chủ động của Đồng Minh Khối Lập Phương cũng sẽ được kích hoạt.
+2. Mỗi tầng của Lâu Đài Abbowser cung cấp Mô-đun Dữ Liệu, giúp tăng cường sức mạnh chiến đấu cho Khối Lập Phương của bạn một cách đáng kể. Một số mô-đun còn đi kèm hiệu ứng kỹ năng bổ sung.
 3. Tiến độ tăng cấp bằng cách đánh bại kẻ địch. Kẻ địch có sức mạnh khác nhau sẽ đóng góp lượng tiến độ khác nhau. Khi thanh tiến độ kích hoạt rương, bạn sẽ nhận được phần thưởng sau khi kết thúc.
-4. Các Resonators trên cùng một tầng sẽ chia sẻ lượt Hồi sinh. Khi tất cả lượt Hồi sinh đã cạn kiệt, Resonators sẽ không thể hồi phục sau khi bị hạ gục.
-5. Khi đạt 100% tiến độ, thời gian còn lại về 0 hoặc lượt Hồi sinh về 0, tầng sẽ được hoàn tất.
+4. Các Resonator trên cùng một tầng sẽ chia sẻ lượt Hồi Sinh. Khi tất cả lượt Hồi Sinh đã cạn kiệt, Resonator sẽ không thể hồi phục sau khi bị hạ gục.
+5. Khi đạt 100% tiến độ, thời gian còn lại về 0 hoặc lượt Hồi Sinh về 0, tầng sẽ được hoàn tất.
 6. Vật phẩm chưa nhặt hoặc rương chưa mở sẽ tự động được chuyển vào Hành Trang sau khi kết thúc.
 7. Các tầng 5, 10 và từ 15 đến 21 có thể thách đấu ở chế độ Đồng Đội.</t>
         </is>
@@ -32957,18 +32957,18 @@
 14/05/2025 08:00 - 26/05/2025 03:59 (giờ máy chủ)
 *Từ 14/05/2025 08:00 đến 23/05/2025 19:30 (giờ máy chủ), các cậu có thể ủng hộ Cube yêu thích mỗi ngày. Từ 23/05/2025 19:30 đến 26/05/2025 03:59 (giờ máy chủ), chức năng ủng hộ sẽ đóng lại. Trong thời gian này, các cậu có thể xem kết quả cuộc đua, kiểm tra Bảng Bảo Trợ, xem lại các trận đấu và nhận phần thưởng sự kiện.
 [Giới Thiệu]
-Giải Race Cube đầu tiên do Pioneer Association tổ chức chính thức khởi tranh! Mười hai ngôi sao Cube sẽ thể hiện tài năng trên đường đua, gác lại địa vị và danh tính, dốc sức tranh tài để giành lấy danh hiệu Cube nhanh nhất!
-Với những ai không thể trực tiếp tham gia cuộc đua, đừng lo! Chúng tôi đã chuẩn bị sẵn sàng! Các cậu có thể ủng hộ những ứng cử viên tiềm năng thông qua các kênh chính thức! Ngoài ra, Pioneer Association sẽ cung cấp toàn bộ chương trình truyền hình trực tiếp, mời tất cả mọi người cùng theo dõi và cổ vũ cho thí sinh mình yêu thích!
-(Chương trình được tài trợ bởi Chi Nhánh Montelli - Second Coming of Solaris, hợp tác cùng Black Shores New.)
+Giải Đua Cube đầu tiên do Hiệp Hội Tiên Phong tổ chức chính thức khởi tranh! Mười hai ngôi sao Cube sẽ thể hiện tài năng trên đường đua, gác lại địa vị và danh tính, dốc sức tranh tài để giành lấy danh hiệu Cube nhanh nhất!
+Với những ai không thể trực tiếp tham gia cuộc đua, đừng lo! Chúng tôi đã chuẩn bị sẵn sàng! Các cậu có thể ủng hộ những ứng cử viên tiềm năng thông qua các kênh chính thức! Ngoài ra, Hiệp Hội Tiên Phong sẽ cung cấp toàn bộ chương trình truyền hình trực tiếp, mời tất cả mọi người cùng theo dõi và cổ vũ cho thí sinh mình yêu thích!
+(Chương trình được tài trợ bởi Chi Nhánh Montelli - Sự Trở Lại Của Solaris, hợp tác cùng Bờ Biển Đen Mới.)
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 8.
 [Thể Lệ]
 1. Trong sự kiện, 12 Cube sẽ tham gia các trận đấu loại theo 2 Bảng, mỗi ngày diễn ra 1 trận, tổng cộng 10 trận để quyết định Nhà Vô Địch Chung Kết.
 2. Từ 08:00 đến 19:30 giờ máy chủ, các cậu có thể ủng hộ Cube yêu thích bằng cách dự đoán Đội Thắng trong trận đấu hôm đó.
 3. Mỗi trận đấu bắt đầu vào 20:00 giờ máy chủ. Từ trang sự kiện, các cậu có thể xem trực tiếp cuộc đua và cổ vũ cho Cube mình yêu thích trong khung chat trực tuyến.
-4. Sau trận đấu, các cậu phải vào trang sự kiện để hoàn tất tính toán phần thưởng Popularity dựa trên thứ hạng cuối cùng của các Cube và kết quả dự đoán.
+4. Sau trận đấu, các cậu phải vào trang sự kiện để hoàn tất tính toán phần thưởng Độ Phổ Biến dựa trên thứ hạng cuối cùng của các Cube và kết quả dự đoán.
 5. Bảng Bảo Trợ sẽ được cập nhật vào 04:00 ngày hôm sau. Các cậu có thể xem thứ hạng của mình trên Bảng Bảo Trợ.
-6. Sau nửa sau của Chung Kết, một vật phẩm kỷ niệm sẽ được gửi đến tất cả Rover đã mở khóa sự kiện này. Hãy nhận trước khi sự kiện kết thúc.</t>
+6. Sau nửa sau của Chung Kết, một vật phẩm kỷ niệm sẽ được gửi đến tất cả Vận Mệnh Giả đã mở khóa sự kiện này. Hãy nhận trước khi sự kiện kết thúc.</t>
         </is>
       </c>
     </row>
@@ -33045,15 +33045,15 @@
       <c r="M469" t="inlineStr">
         <is>
           <t>Về sự kiện
-Anniversary Ngày Trở Lại của Solaris sắp đến, nhưng rắc rối đã ập đến Thế Giới Cube. Vua quỷ bí ẩn Abbowser đã bắt giữ tất cả các Cube và đưa ra thử thách hùng hồn cho Chiến Binh Black Cat huyền thoại: "Ngươi xuất hiện ở vùng đất lạ, đánh bại tay sai của ta, giải cứu đồng đội, rồi đối đầu với ta trong trận chiến trùm kinh điển! Tuyệt vời! Sẽ rất thú vị đấy!"
+Kỷ niệm Ngày Trở Lại của Solaris sắp đến, nhưng rắc rối đã ập đến Thế Giới Khối Lập Phương. Vua quỷ bí ẩn Abbowser đã bắt giữ tất cả các Khối Lập Phương và đưa ra thử thách hùng hồn cho Chiến Binh Mèo Đen huyền thoại: "Ngươi xuất hiện ở vùng đất lạ, đánh bại tay sai của ta, giải cứu đồng đội, rồi đối đầu với ta trong trận chiến trùm kinh điển! Tuyệt vời! Sẽ rất thú vị đấy!"
 Điều kiện tham gia
 Đạt Cấp Liên Minh 22.
 Quy tắc
-1. Enter Abbowser Castle cùng tối đa 3 đồng minh Cube. Đồng minh Cube sẽ chủ động hỗ trợ bạn trong trận chiến. Ngoài ra, sử dụng Kỹ Năng Echo sẽ kích hoạt kỹ năng chủ động của đồng minh Cube.
-2. Mỗi tầng trong Abbowser Castle cung cấp Mô-đun Data, tăng sức mạnh chiến đấu cho Cube của bạn một cách đáng kể. Một số mô-đun còn đi kèm hiệu ứng kỹ năng bổ sung.
+1. Vào Lâu Đài Abbowser cùng tối đa 3 đồng minh Khối Lập Phương. Đồng minh Khối Lập Phương sẽ chủ động hỗ trợ bạn trong trận chiến. Ngoài ra, sử dụng Kỹ Năng Echo sẽ kích hoạt kỹ năng chủ động của đồng minh Khối Lập Phương.
+2. Mỗi tầng trong Lâu Đài Abbowser cung cấp Mô-đun Dữ Liệu, tăng sức mạnh chiến đấu cho Khối Lập Phương của bạn một cách đáng kể. Một số mô-đun còn đi kèm hiệu ứng kỹ năng bổ sung.
 3. Tiến độ tăng cấp bằng cách đánh bại kẻ địch. Kẻ địch có sức mạnh khác nhau sẽ đóng góp lượng tiến độ khác nhau. Khi thanh tiến độ kích hoạt rương, bạn sẽ nhận được phần thưởng sau khi kết thúc.
-4. Resonators trên cùng một tầng chia sẻ Cơ Hội Hồi sinh. Sau khi hết Cơ Hội Hồi sinh, Resonators sẽ không thể hồi phục khi bị hạ gục.
-5. Tầng sẽ kết thúc khi đạt 100% tiến độ, hết thời gian hoặc hết Cơ Hội Hồi sinh.
+4. Resonator trên cùng một tầng chia sẻ Cơ Hội Hồi Sinh. Sau khi hết Cơ Hội Hồi Sinh, Resonator sẽ không thể hồi phục khi bị hạ gục.
+5. Tầng sẽ kết thúc khi đạt 100% tiến độ, hết thời gian hoặc hết Cơ Hội Hồi Sinh.
 6. Vật phẩm không nhặt hoặc rương chưa mở sẽ tự động chuyển vào Hành Trang sau khi kết thúc.
 7. Các tầng 5, 10 và từ 15 đến 21 có thể thách đấu ở chế độ Hợp Tác.</t>
         </is>
@@ -33219,17 +33219,17 @@
       <c r="M471" t="inlineStr">
         <is>
           <t>Về sự kiện
-"Xin chào, Rover, chào mừng đến với Triển Lãm Chụp ảnh Solaris!"
+"Xin chào, Vận Mệnh Giả, chào mừng đến với Triển Lãm Ảnh Solaris!"
 Hành trình của cậu trong thế giới hoàn toàn mới này sẽ diễn ra như thế nào? Những cảnh sắc mơ ước, những người bạn mong gặp, những câu chuyện sắp viết nên... tất cả ký ức sẽ hiện lên rực rỡ sắc màu, bắt đầu từ đây, từ chính cậu.
 Điều kiện tham gia
 Tạo hồ sơ nhân vật sau bản cập nhật Phiên bản 2.4 và đạt Cấp Liên Minh 5.
 Thời gian diễn ra
-Lễ kỷ niệm Hành Trình New Solaris sẽ mở khóa khi đạt đủ điều kiện. Event kéo dài 30 ngày.
+Lễ kỷ niệm Hành Trình Mới Solaris sẽ mở khóa khi đạt đủ điều kiện. Sự kiện kéo dài 30 ngày.
 Quy tắc sự kiện
-Event gồm bốn loại nhiệm vụ: Tidal Memories, Combat Scenes, Scenic Wonders và Lộ Trình Trưởng Thành. Hoàn thành nhiệm vụ để nhận phần thưởng vật phẩm và Points Hoạt Náo Kỷ Niệm.
-Tích lũy Points Hoạt Náo để mở khóa những phần thưởng giá trị. Tiếp tục cố gắng để nhận được &lt;color=#ffd12f&gt;standard 5-star Resonator of your choice&lt;/color&gt;!
+Sự kiện gồm bốn loại nhiệm vụ: Ký Ức Thủy Triều, Cảnh Chiến Đấu, Kỳ Quan Phong Cảnh và Lộ Trình Trưởng Thành. Hoàn thành nhiệm vụ để nhận phần thưởng vật phẩm và Điểm Hoạt Náo Kỷ Niệm.
+Tích lũy Điểm Hoạt Náo để mở khóa những phần thưởng giá trị. Tiếp tục cố gắng để nhận được &lt;color=#ffd12f&gt;Resonator 5 sao tiêu chuẩn theo lựa chọn của cậu&lt;/color&gt;!
 Nếu sự kiện kết thúc mà cậu vẫn còn phần thưởng chưa nhận, hãy đăng nhập trong vòng 30 ngày sau đó để nhận qua thư.
-Nếu trong sự kiện cậu không chọn Resonator 5 sao ưa thích làm Quà Kỷ Niệm, phần thưởng này sẽ không được cấp lại. Nếu đã đạt điều kiện và chọn xong, phần thưởng Resonator 5 sao tiêu chuẩn tương ứng sẽ được gửi lại qua Mail.
+Nếu trong sự kiện cậu không chọn Resonator 5 sao ưa thích làm Quà Kỷ Niệm, phần thưởng này sẽ không được cấp lại. Nếu đã đạt điều kiện và chọn xong, phần thưởng Resonator 5 sao tiêu chuẩn tương ứng sẽ được gửi lại qua Thư.
 Lưu ý: Một số nội dung sự kiện không khả dụng khi ở chế độ Hợp Tác. Theo dõi Nhiệm Vụ không khả dụng ở một số khu vực.</t>
         </is>
       </c>
@@ -33296,7 +33296,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Cờ Chinh Phục: Cấp Trung và Cờ Chinh Phục: Cấp Cao đang bị các Tacet Discord mạnh mẽ với Cấp Glory cao chiếm giữ. Đánh bại chúng sẽ giúp ngươi chiếm lĩnh lá cờ và nhận được lượng lớn Points Săn lớn. Đánh bại các kẻ địch mạnh khác trong khu vực cũng sẽ mang lại phần thưởng bổ sung.
+          <t>Cờ Chinh Phục: Cấp Trung và Cờ Chinh Phục: Cấp Cao đang bị các Tacet Discord mạnh mẽ với Cấp Vinh Quang cao chiếm giữ. Đánh bại chúng sẽ giúp ngươi chiếm lĩnh lá cờ và nhận được lượng lớn Điểm Săn lớn. Đánh bại các kẻ địch mạnh khác trong khu vực cũng sẽ mang lại phần thưởng bổ sung.
 Sau khi chiếm lĩnh, ngươi có thể tương tác với Cờ Chinh Phục: Cấp Trung và Cờ Chinh Phục: Cấp Cao. Hành động này sẽ làm hồi sinh tất cả Tacet Discord trong khu vực, nhưng không làm mất trạng thái chiếm lĩnh của lá cờ.</t>
         </is>
       </c>
@@ -33380,21 +33380,21 @@
         <is>
           <t>Ký ức quá khứ chôn giấu sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên nhé, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang, Aalto. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng 150% Points Ảo Ảnh!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang, Aalto. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng 150% Điểm Ảo Ảnh!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Aero DMG.
-- Gây Aero DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Aero.
+- Gây Sát Thương Aero sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có sức mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
 - Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau.
-Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ địch mạnh mẽ ở sâu nhất trong Ảo Cảnh, một Tinh Thể Tàn Dư sẽ xuất hiện tại Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng từ nó.
 [Độ Khó]
-Pha SOL3 càng cao, Khám Phá trong Ảo Cảnh càng thử thách hơn, đồng thời mang lại nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh hơn. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 của cậu khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong chu kỳ khám phá không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, Khám Phá trong Ảo Cảnh càng thử thách hơn, đồng thời mang lại nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh hơn. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 của cậu khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong chu kỳ khám phá không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -33477,21 +33477,21 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mộng, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mộng]
-Resonators Hỗ Trợ Giấc Mộng hiện tại: Lupa, Brant, Changli, Encore, Chixia, Mortefi. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mộng để nhận thưởng Points Ảo Ảnh gấp 150%!
+Resonator Hỗ Trợ Giấc Mộng hiện tại: Lupa, Brant, Changli, Encore, Chixia, Mortefi. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mộng để nhận thưởng Điểm Ảo Ảnh gấp 150%!
 Hiệu ứng Hỗ Trợ Giấc Mộng hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Fusion DMG.
-- Gây Fusion DMG sẽ nhận được 30 Năng Lượng Giấc Mộng. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mộng đạt 500, cậu sẽ bước vào Giấc Mộng Tỉnh Thức. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mộng Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mộng khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Fusion.
+- Gây Sát Thương Fusion sẽ nhận được 30 Năng Lượng Giấc Mộng. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mộng đạt 500, cậu sẽ bước vào Giấc Mộng Tỉnh Thức. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mộng Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mộng khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Illusive Realm.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
-- Tại Illusive Realm, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có sức mạnh Giấc Mộng sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mộng Tỉnh Thức thông qua Hỗ Trợ Giấc Mộng.
-- Mỗi trận chiến trong Illusive Realm sẽ đối đầu với những kẻ địch khác nhau.
-Hoàn thành những thử thách này để kiếm Points Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Cõi Ảo Ảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
+- Tại Cõi Ảo Ảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có sức mạnh Giấc Mộng sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mộng Tỉnh Thức thông qua Hỗ Trợ Giấc Mộng.
+- Mỗi trận chiến trong Cõi Ảo Ảnh sẽ đối đầu với những kẻ địch khác nhau.
+Hoàn thành những thử thách này để kiếm Điểm Ảo Ảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện tại Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong cõi. Sử dụng Waveplate để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Illusive Realm, cùng với nhiều Tinh Thể Tàn Dư và Points Ảo Ảnh hơn làm phần thưởng. Difficulty của Illusive Realm phụ thuộc vào Pha SOL3 mà cậu đang ở khi Illusive Realm được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Cõi Ảo Ảnh, cùng với nhiều Tinh Thể Tàn Dư và Điểm Ảo Ảnh hơn làm phần thưởng. Độ khó của Cõi Ảo Ảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Cõi Ảo Ảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -33557,8 +33557,8 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Core Echoes&lt;/color&gt; có 8 Sát Thương và là Echo Class Overlord hoặc Calamity ở Solaris-3. Mỗi bộ bài phải chứa đúng một Echo Cốt Core. Sức mạnh áp đảo của nó biến nó thành nền tảng của một bộ bài mạnh.
-&lt;color=#ffd12f&gt;Thường Echoes&lt;/color&gt; có 1 đến 3 Sát Thương và là Echo Class Common hoặc Elite ở Solaris-3. Bạn phải có 20 Echo Thường trong bộ bài để bắt đầu trận đấu.</t>
+          <t>&lt;color=#ffd12f&gt;Tiếng Vọng Cốt Lõi&lt;/color&gt; có 8 Sát Thương và là Tiếng Vọng Hạng Overlord hoặc Calamity ở Solaris-3. Mỗi bộ bài phải chứa đúng một Tiếng Vọng Cốt Lõi. Sức mạnh áp đảo của nó biến nó thành nền tảng của một bộ bài mạnh.
+&lt;color=#ffd12f&gt;Tiếng Vọng Thường&lt;/color&gt; có 1 đến 3 Sát Thương và là Tiếng Vọng Hạng Common hoặc Elite ở Solaris-3. Bạn phải có 20 Tiếng Vọng Thường trong bộ bài để bắt đầu trận đấu.</t>
         </is>
       </c>
     </row>
@@ -33708,14 +33708,14 @@
       <c r="M477" t="inlineStr">
         <is>
           <t>["Giới Thiệu"]
-Một cánh cổng kỳ lạ dẫn vào Somnoire hiện ra. Qua đó, một Conductor tò mò thoáng thấy một Xứ Giấc Mơ bị bỏ hoang. Nơi ấy, vô số Echoes kỳ dị đã tụ họp, nỗ lực khôi phục vẻ huy hoàng ngày nào. Người Conductor quyết định nán lại, lặng lẽ chờ đợi giấc mơ này hé lộ...
+Một cánh cổng kỳ lạ dẫn vào Somnoire hiện ra. Qua đó, một Nhạc trưởng tò mò thoáng thấy một Xứ Giấc Mơ bị bỏ hoang. Nơi ấy, vô số Echo kỳ dị đã tụ họp, nỗ lực khôi phục vẻ huy hoàng ngày nào. Người Nhạc trưởng quyết định nán lại, lặng lẽ chờ đợi giấc mơ này hé lộ...
 [Điều kiện tham gia]
-Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm vụ Main "Vượt Qua Biển Khơi" để mở khóa (hoàn thành nhiệm vụ "Thợ Bắt Giấc Mơ Trong Vườn Bí Mật" để có trải nghiệm tốt nhất).
+Đạt Cấp Liên Minh 14 và hoàn thành Nhiệm vụ Chính "Vượt Qua Biển Khơi" để mở khóa (hoàn thành nhiệm vụ "Thợ Bắt Giấc Mơ Trong Vườn Bí Mật" để có trải nghiệm tốt nhất).
 [Quy tắc sự kiện]
-Trong sự kiện này, Phrolova sẽ đảm nhiệm công việc quản lý một công viên giải trí bị bỏ hoang từ lâu trong Somnoire, điều phối Echoes để duy trì hoạt động của công viên. Hãy phân bổ Echoes một cách chiến lược để giữ vững sự ổn định và kéo dài sự tồn tại của công viên.
-Trong số ngày quy định, hãy dẫn dắt Echoes và thu thập đủ Phiếu Xứ Giấc Mơ để hoàn thành mục tiêu từng giai đoạn và duy trì hoạt động của công viên.
+Trong sự kiện này, Phrolova sẽ đảm nhiệm công việc quản lý một công viên giải trí bị bỏ hoang từ lâu trong Somnoire, điều phối Echo để duy trì hoạt động của công viên. Hãy phân bổ Echo một cách chiến lược để giữ vững sự ổn định và kéo dài sự tồn tại của công viên.
+Trong số ngày quy định, hãy dẫn dắt Echo và thu thập đủ Phiếu Xứ Giấc Mơ để hoàn thành mục tiêu từng giai đoạn và duy trì hoạt động của công viên.
 Trong thời gian nhận thưởng giới hạn, bạn có thể kiếm được Huy Hiệu Xứ Giấc Mơ bằng cách hoàn thành các mục tiêu đặc biệt. Thu thập đủ Huy Hiệu Xứ Giấc Mơ để mở khóa Ấn: Mộng Ảo Xứ Giấc Mơ.
-Nếu bạn bỏ lỡ phần thưởng giới hạn, chúng sẽ được gửi qua Mail trong game với điều kiện bạn đăng nhập trong vòng 30 ngày sau khi sự kiện kết thúc.
+Nếu bạn bỏ lỡ phần thưởng giới hạn, chúng sẽ được gửi qua Thư trong game với điều kiện bạn đăng nhập trong vòng 30 ngày sau khi sự kiện kết thúc.
 Phần thưởng giới hạn sẽ không thể nhận được sau khi thời gian nhận thưởng kết thúc, nhưng bạn vẫn có thể tiếp tục chơi để kiếm phần thưởng vĩnh viễn.</t>
         </is>
       </c>
@@ -33789,8 +33789,8 @@
           <t>Chọn Giai Đoạn
 1. Hoàn thành chỉ tiêu doanh thu để vượt qua các Giai Đoạn và nhận thưởng.
 2. Một số Giai Đoạn có nhiều cấp độ khó. Vượt qua độ khó cao sẽ mở khóa Thành viên Dreamland và Đạo cụ đặc biệt.
-3. Ở một số Giai Đoạn, bạn có thể chọn Attributes Giấc Mộng Hưởng ứng với Môi trường Giai Đoạn, giúp quản lý hiệu quả hơn.
-4. Trước khi bắt đầu Giai Đoạn, bạn có thể trang bị Blessing Phantasma. Những phước lành này mang lại nhiều hiệu ứng tăng cường hỗ trợ Phrolova đạt mục tiêu.
+3. Ở một số Giai Đoạn, bạn có thể chọn Thuộc tính Giấc Mộng Hưởng ứng với Môi trường Giai Đoạn, giúp quản lý hiệu quả hơn.
+4. Trước khi bắt đầu Giai Đoạn, bạn có thể trang bị Phước Lành Phantasma. Những phước lành này mang lại nhiều hiệu ứng tăng cường hỗ trợ Phrolova đạt mục tiêu.
 5. Một số Giai Đoạn có Chế độ Vô Hạn. Hoàn thành chỉ tiêu doanh thu của Pha 5 trong các Giai Đoạn này sẽ tính là hoàn thành. Sau đó, bạn có thể tiếp tục chơi để đối mặt với các Pha ngày càng khó và hướng tới kỷ lục Pha cao nhất.</t>
         </is>
       </c>
@@ -33881,24 +33881,24 @@
 Giai Đoạn &amp; Ngày]
  - Trong mỗi giai đoạn, bạn phải đạt mục tiêu doanh thu yêu cầu trong thời gian quy định để tiến vào giai đoạn tiếp theo.
  - Khi bước vào giai đoạn mới, độ khó của Mục Tiêu Giai Đoạn sẽ tăng lên.
- - &lt;color=#c79f49&gt;Completing all Giai đoạn Goals&lt;/color&gt; để vượt qua màn chơi.
- - Mỗi giai đoạn mới sẽ tặng một số Tinh Thể Tần Số và sẽ &lt;color=#c79f49&gt;automatically deduct the required Dreamland Coupons for the previous phase&lt;/color&gt;.
- [Echo Dreamland]
- - Số Dreamland Coupons kiếm được mỗi ngày bị ảnh hưởng bởi Echo, đạo cụ và loại Dream Block.
- - Tối đa 20 Echo có thể đặt trên chiến trường cùng lúc. Tổng cộng có thể chứa &lt;color=#c79f49&gt;100&lt;/color&gt; Echo cả trên và ngoài chiến trường.
- - Khi bắt đầu mỗi ngày mới, vị trí của Echo trên chiến trường sẽ thay đổi ngẫu nhiên.
- - Nếu chiến trường đã đầy khi có Echo mới đến, kẻ mới đến sẽ bị ẩn đi và có thể xuất hiện trên chiến trường vào ngày hôm sau.
- - Khi các giai đoạn tiến triển, độ hiếm của Echo có thể chiêu mộ sẽ tăng dần lên đến độ hiếm Vàng.
- - Echo thuộc tính Mơ Kết Nối sẽ được thêm vào danh sách chiêu mộ sau khi mở khóa.
+ - &lt;color=#c79f49&gt;Hoàn thành tất cả Mục Tiêu Giai Đoạn&lt;/color&gt; để vượt qua màn chơi.
+ - Mỗi giai đoạn mới sẽ tặng một số Tinh Thể Tần Số và sẽ &lt;color=#c79f49&gt;tự động trừ số Dreamland Coupon cần thiết cho giai đoạn trước&lt;/color&gt;.
+ [Tiếng Vọng Dreamland]
+ - Số Dreamland Coupon kiếm được mỗi ngày bị ảnh hưởng bởi Tiếng Vọng, đạo cụ và loại Dream Block.
+ - Tối đa 20 Tiếng Vọng có thể đặt trên chiến trường cùng lúc. Tổng cộng có thể chứa &lt;color=#c79f49&gt;100&lt;/color&gt; Tiếng Vọng cả trên và ngoài chiến trường.
+ - Khi bắt đầu mỗi ngày mới, vị trí của Tiếng Vọng trên chiến trường sẽ thay đổi ngẫu nhiên.
+ - Nếu chiến trường đã đầy khi có Tiếng Vọng mới đến, kẻ mới đến sẽ bị ẩn đi và có thể xuất hiện trên chiến trường vào ngày hôm sau.
+ - Khi các giai đoạn tiến triển, độ hiếm của Tiếng Vọng có thể chiêu mộ sẽ tăng dần lên đến độ hiếm Vàng.
+ - Tiếng Vọng thuộc tính Mơ Kết Nối sẽ được thêm vào danh sách chiêu mộ sau khi mở khóa.
  [Phúc Lành Phantasma]
  - Phúc Lành Phantasma mang lại nhiều hiệu ứng khác nhau hỗ trợ quản lý Dreamland.
  - Mỗi lần sử dụng sẽ tiêu tốn một lượt Phúc Lành. Khi hết lượt, không thể kích hoạt Phúc Lành nữa.
- [Details Dreamland]
- - Trong trang Details Dreamland, bạn có thể xem tất cả Echo hiện có trên và ngoài chiến trường, cũng như sản lượng hàng ngày.
- - Trong trang Details Dreamland, bạn cũng có thể &lt;color=#c79f49&gt;Dismiss&lt;/color&gt; bất kỳ Echo nào trên chiến trường.
- [Infinite Mode]
- - Một số màn chơi sẽ mở khóa Infinite Mode sau khi vượt qua.
- - Trong Infinite Mode, Mục Tiêu Giai Đoạn sẽ khó đạt được hơn nhiều, và thời gian của các Giai Đoạn sẽ là &lt;color=#c79f49&gt;infinite&lt;/color&gt;. Thử thách của bạn được coi là thành công khi đạt giới hạn doanh thu của hệ thống.
+ [Chi Tiết Dreamland]
+ - Trong trang Chi Tiết Dreamland, bạn có thể xem tất cả Tiếng Vọng hiện có trên và ngoài chiến trường, cũng như sản lượng hàng ngày.
+ - Trong trang Chi Tiết Dreamland, bạn cũng có thể &lt;color=#c79f49&gt;Sa Thải&lt;/color&gt; bất kỳ Tiếng Vọng nào trên chiến trường.
+ [Chế Độ Vô Tận]
+ - Một số màn chơi sẽ mở khóa Chế Độ Vô Tận sau khi vượt qua.
+ - Trong Chế Độ Vô Tận, Mục Tiêu Giai Đoạn sẽ khó đạt được hơn nhiều, và thời gian của các Giai Đoạn sẽ là &lt;color=#c79f49&gt;vô tận&lt;/color&gt;. Thử thách của bạn được coi là thành công khi đạt giới hạn doanh thu của hệ thống.
  - Bạn có thể chọn kết thúc lượt chơi bất cứ lúc nào, và nó vẫn sẽ được tính là hoàn thành thử thách.</t>
         </is>
       </c>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Nếu không thể tạo ra Echo Dư Dả, Sự Trừng Phạt sẽ gây sát thương cực lớn lên bất kỳ Resonator nào đang hoạt động.</t>
+          <t>Nếu không thể tạo ra Tổ Tacet Dư Dả, Sự Trừng Phạt sẽ gây sát thương cực lớn lên bất kỳ Resonator nào đang hoạt động.</t>
         </is>
       </c>
     </row>
@@ -34029,7 +34029,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Orchestration là một trong những khả năng Resonance của Phrolova. Nó có thể khai thác bản chất của một vật thể và thay đổi trạng thái của nó. Sau khi Orchestration, hành vi của các vật thể gần đó sẽ bị ảnh hưởng trong một khoảng thời gian. Có thể kết thúc Orchestration sớm.</t>
+          <t>Phối Khí là một trong những khả năng Cộng Hưởng của Phrolova. Nó có thể khai thác bản chất của một vật thể và thay đổi trạng thái của nó. Sau khi Phối Khí, hành vi của các vật thể gần đó sẽ bị ảnh hưởng trong một khoảng thời gian. Có thể kết thúc Phối Khí sớm.</t>
         </is>
       </c>
     </row>
@@ -34293,7 +34293,7 @@
         <is>
           <t>Trong mỗi Giai Đoạn, bạn phải đạt doanh thu yêu cầu trong thời gian quy định để tiến vào Giai Đoạn tiếp theo.
 Vào Giai Đoạn mới đồng nghĩa với mục tiêu khó khăn hơn. Hoàn thành tất cả Mục Tiêu Giai Đoạn sẽ vượt qua Cấp Độ.
-Mỗi Giai Đoạn mới sẽ nhận được một số Tinh Thể Tần Số và tự động trừ số Dreamland Coupons cần thiết của Giai Đoạn trước đó.</t>
+Mỗi Giai Đoạn mới sẽ nhận được một số Tinh Thể Tần Số và tự động trừ số Dreamland Coupon cần thiết của Giai Đoạn trước đó.</t>
         </is>
       </c>
     </row>
@@ -34433,9 +34433,9 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy &lt;color=#ffd12f&gt;Gradation&lt;/color&gt; làm khả năng cốt lõi.
-Một số Resonator sẽ &lt;color=#ffd12f&gt;trigger Gradation once and obtain buffs after staying on the field for a set number of days&lt;/color&gt;.
-Để tối đa hóa lợi ích, &lt;color=#ffd12f&gt;try placing as many Gradation Echoes in the early days as possible&lt;/color&gt; nếu bạn chọn Giấc Mơ Tiến Hóa.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy &lt;color=#ffd12f&gt;Sự Tiến Hóa&lt;/color&gt; làm khả năng cốt lõi.
+Một số Cộng Hưởng Giả sẽ &lt;color=#ffd12f&gt;kích hoạt Tiến Hóa một lần và nhận được hiệu ứng tăng cường sau khi ở lại chiến trường trong một số ngày nhất định&lt;/color&gt;.
+Để tối đa hóa lợi ích, &lt;color=#ffd12f&gt;hãy cố gắng đặt càng nhiều Cộng Hưởng Giả Tiến Hóa vào những ngày đầu càng tốt&lt;/color&gt; nếu bạn chọn Giấc Mơ Tiến Hóa.</t>
         </is>
       </c>
     </row>
@@ -34502,9 +34502,9 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Những Resonator mang thuộc tính Giấc Mơ này lấy &lt;color=#ffd12f&gt;Exchange&lt;/color&gt; làm khả năng cốt lõi. Sau khi ở lại chiến trường đủ số ngày nhất định, một số Resonator sẽ tự loại bỏ và để lại nhiều hiệu ứng tăng cường khác nhau.
-&lt;color=#ffd12f&gt;Certain Dream of Exchange Echoes can produce Echoes with the ability to Exchange. Whenever Exchange is triggered, this type of Echo becomes buffed.&lt;/color&gt;
-Để tối đa hóa lợi ích, &lt;color=#ffd12f&gt;make sure you can produce enough Echoes with the ability to Exchange&lt;/color&gt; nếu bạn chọn Giấc Mơ Trao đổi.</t>
+          <t>Những Cộng Hưởng Giả mang thuộc tính Giấc Mơ này lấy &lt;color=#ffd12f&gt;Sự Trao Đổi&lt;/color&gt; làm khả năng cốt lõi. Sau khi ở lại chiến trường đủ số ngày nhất định, một số Cộng Hưởng Giả sẽ tự loại bỏ và để lại nhiều hiệu ứng tăng cường khác nhau.
+&lt;color=#ffd12f&gt;Một số Cộng Hưởng Giả trong Giấc Mơ Trao Đổi có thể tạo ra Cộng Hưởng Giả có khả năng Trao Đổi. Mỗi khi Trao Đổi được kích hoạt, loại Cộng Hưởng Giả này sẽ được tăng cường.&lt;/color&gt;
+Để tối đa hóa lợi ích, &lt;color=#ffd12f&gt;hãy đảm bảo bạn có thể tạo ra đủ Cộng Hưởng Giả có khả năng Trao Đổi&lt;/color&gt; nếu bạn chọn Giấc Mơ Trao Đổi.</t>
         </is>
       </c>
     </row>
@@ -34570,8 +34570,8 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Các Echoes thuộc thuộc tính Giấc Mộng này lấy &lt;color=#ffd12f&gt;Integration&lt;/color&gt; làm khả năng cốt lõi. Một số Echoes có thể tái tạo Echo thông qua Integration. &lt;color=#ffd12f&gt;When conditions are met, certain Echoes will merge with another Echo on the same row into a brand-new Echo and grant various buff effects.&lt;/color&gt;
-&lt;color=#ffd12f&gt;Try Integrating many Echoes of the same rarity&lt;/color&gt; để tạo ra những Echoes mạnh mẽ nếu bạn chọn Giấc Mộng Integration.</t>
+          <t>Các Echo thuộc thuộc tính Giấc Mộng này lấy &lt;color=#ffd12f&gt;Hợp Nhất&lt;/color&gt; làm khả năng cốt lõi. Một số Echo có thể tái tạo Tổ Tacet thông qua Hợp Nhất. &lt;color=#ffd12f&gt;Khi điều kiện được đáp ứng, một số Echo sẽ hòa làm một với Echo khác cùng hàng, tạo thành Echo hoàn toàn mới và mang lại nhiều hiệu ứng tăng cường.&lt;/color&gt;
+&lt;color=#ffd12f&gt;Hãy thử Hợp Nhất nhiều Echo cùng cấp hiếm&lt;/color&gt; để tạo ra những Echo mạnh mẽ nếu bạn chọn Giấc Mộng Hợp Nhất.</t>
         </is>
       </c>
     </row>
@@ -34649,16 +34649,16 @@
         <is>
           <t>Ký ức quá khứ chôn sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Khi Năng Lượng Giấc Mơ đạt 500 điểm, kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu của Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Khi Năng Lượng Giấc Mơ đạt 500 điểm, kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu của Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo.
-- Skills Vọng Âm, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo.
+- Kỹ Năng Vọng Âm, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Ấn và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tiên Tri thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo sẽ đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo sẽ đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong lãnh địa, một Tinh Thể Tàn Dư sẽ xuất hiện tại Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng.
 [Độ Khó]
-Pha SOL3 càng cao, Exploration trong Thế Giới Ảo càng thử thách hơn, với nhiều Tinh Thể Tàn Dư và Points Ảo làm phần thưởng. Difficulty của Thế Giới Ảo phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo được đặt lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, Thám Hiểm trong Thế Giới Ảo càng thử thách hơn, với nhiều Tinh Thể Tàn Dư và Điểm Ảo làm phần thưởng. Độ khó của Thế Giới Ảo phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo được đặt lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -34736,16 +34736,16 @@
         <is>
           <t>Ký ức quá khứ chôn sâu trong giấc mơ, và chìa khóa khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Khi Năng Lượng Giấc Mơ đạt 500 điểm, kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu của Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Khi Năng Lượng Giấc Mơ đạt 500 điểm, kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu của Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo.
-- Skills Vọng Âm, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo.
+- Kỹ Năng Vọng Âm, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Ấn và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tiên Tri thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo sẽ đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo sẽ đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong lãnh địa, một Tinh Thể Tàn Dư sẽ xuất hiện tại Khu Vực Ký Ức. Sử dụng Waveplate để thu thập phần thưởng.
 [Độ Khó]
-Pha SOL3 càng cao, Exploration trong Thế Giới Ảo càng thử thách hơn, với nhiều Tinh Thể Tàn Dư và Points Ảo làm phần thưởng. Difficulty của Thế Giới Ảo phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo được đặt lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, Thám Hiểm trong Thế Giới Ảo càng thử thách hơn, với nhiều Tinh Thể Tàn Dư và Điểm Ảo làm phần thưởng. Độ khó của Thế Giới Ảo phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo được đặt lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -34823,16 +34823,16 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên nhé, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Echo, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Ấn và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi Giấc Mơ Tiên Tri được kích hoạt thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong Ảo Cảnh. Sử dụng Bản Năng Lượng để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 càng cao, việc Khám Phá trong Ảo Cảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Points Ảo Cảnh làm phần thưởng. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, việc Khám Phá trong Ảo Cảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Điểm Ảo Cảnh làm phần thưởng. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -34910,16 +34910,16 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên nhé, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Echo, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Ấn và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi Giấc Mơ Tiên Tri được kích hoạt thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong Ảo Cảnh. Sử dụng Bản Năng Lượng để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 càng cao, việc Khám Phá trong Ảo Cảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Points Ảo Cảnh làm phần thưởng. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, việc Khám Phá trong Ảo Cảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Điểm Ảo Cảnh làm phần thưởng. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -34997,16 +34997,16 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên nhé, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Ấn và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Echo, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Ấn và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi Giấc Mơ Tiên Tri được kích hoạt thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong Ảo Cảnh. Sử dụng Bản Năng Lượng để thu thập phần thưởng của nó.
 [Độ Khó]
-Pha SOL3 càng cao, việc Khám Phá trong Ảo Cảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Points Ảo Cảnh làm phần thưởng. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 càng cao, việc Khám Phá trong Ảo Cảnh càng thử thách hơn với nhiều Tinh Thể Tàn Dư và Điểm Ảo Cảnh làm phần thưởng. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -35080,11 +35080,11 @@
         <is>
           <t>Về sự kiện
 Tại Tấn Châu, bạn bắt gặp một người đàn ông có vẻ đang gặp khó khăn. Ông ta kể rằng mình vừa sống sót sau một cuộc tấn công bí ẩn…
-Hãy giúp nhà thiết kế giải quyết những bất thường kỳ lạ đang nổi lên trong Second Coming of Solaris, và tìm ra thủ phạm đứng sau tất cả.
+Hãy giúp nhà thiết kế giải quyết những bất thường kỳ lạ đang nổi lên trong Sự Trở Lại Của Solaris, và tìm ra thủ phạm đứng sau tất cả.
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14.
 Quy tắc sự kiện
-Một số bất thường có thể được tìm thấy trong các cảnh của trò chơi. Sau khi xác định vị trí những bất thường này, hãy sử dụng Công cụ: Thu Phóng Máy Ảnh để chụp lại, rồi cùng Bertolt chỉnh sửa chúng.
+Một số bất thường có thể được tìm thấy trong các cảnh của trò chơi. Sau khi xác định vị trí những bất thường này, hãy sử dụng Tiện Ích: Thu Phóng Máy Ảnh để chụp lại, rồi cùng Bertolt chỉnh sửa chúng.
 Bạn có thể chọn khôi phục các bất thường về trạng thái bình thường hoặc cố tình làm méo mó chúng thêm.</t>
         </is>
       </c>
@@ -35159,10 +35159,10 @@
           <t>[Giới thiệu]
 Để ngăn chặn một Hiện Tượng Sóng Tàn Phá khác với quy mô của Trận Thủy Triều Đen, Black Shores và Rinascita đã hợp tác trong một dự án chung: tiến hành mô phỏng bằng thiết bị hologram tại những khu vực dễ bị ảnh hưởng bởi sức mạnh của Threnodian. Vì vậy, cậu và những người đồng hành đáng tin cậy đã được mời tham gia thử nghiệm thiết bị đặc biệt này.
 [Điều kiện tham gia]
-Đạt Cấp Liên Minh 14 và mở khóa Resonance Nexus tại Thành phố Ragunna trong Nhiệm Vụ Chính "Ngọn Gió Thiêng Mailờng Xuyên Thổi".
+Đạt Cấp Liên Minh 14 và mở khóa Resonance Nexus tại Thành phố Ragunna trong Nhiệm Vụ Chính "Ngọn Gió Thiêng Thường Xuyên Thổi".
 [Quy tắc sự kiện]
 Chọn một Resonator tham gia và bước vào các bài tập chiến đấu mô phỏng! Dưới góc nhìn chiến thuật đặc biệt, cậu sẽ điều khiển họ chống lại làn sóng kẻ địch với những vũ khí hoàn toàn mới. Trong trận chiến, hãy sử dụng Enhancement Modules thu được để nâng cấp Resonator hoặc cải tiến vũ khí của họ. Để hoàn thành một bài tập, cậu phải sống sót qua mọi đợt tấn công.
-Nếu còn phần thưởng chưa nhận khi sự kiện kết thúc, cậu có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.</t>
+Nếu còn phần thưởng chưa nhận khi sự kiện kết thúc, cậu có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.</t>
         </is>
       </c>
     </row>
@@ -35236,10 +35236,10 @@
           <t>[Giới thiệu]
 Để ngăn chặn một Hiện Tượng Sóng Tàn Phá khác với quy mô của Trận Thủy Triều Đen, Black Shores và Rinascita đã hợp tác trong một dự án chung: tiến hành mô phỏng bằng thiết bị hologram tại những khu vực dễ bị ảnh hưởng bởi sức mạnh của Threnodian. Vì vậy, cậu và những người đồng hành đáng tin cậy đã được mời tham gia thử nghiệm thiết bị đặc biệt này.
 [Điều kiện tham gia]
-Đạt Cấp Liên Minh 14 và mở khóa Resonance Nexus tại Thành phố Ragunna trong Nhiệm Vụ Chính "Ngọn Gió Thiêng Mailờng Xuyên Thổi".
+Đạt Cấp Liên Minh 14 và mở khóa Resonance Nexus tại Thành phố Ragunna trong Nhiệm Vụ Chính "Ngọn Gió Thiêng Thường Xuyên Thổi".
 [Quy tắc sự kiện]
 Chọn một Resonator tham gia và bước vào các bài tập chiến đấu mô phỏng! Dưới góc nhìn chiến thuật đặc biệt, cậu sẽ điều khiển họ chống lại làn sóng kẻ địch với những vũ khí hoàn toàn mới. Trong trận chiến, hãy sử dụng Enhancement Modules thu được để nâng cấp Resonator hoặc cải tiến vũ khí của họ. Để hoàn thành một bài tập, cậu phải sống sót qua mọi đợt tấn công.
-Nếu còn phần thưởng chưa nhận khi sự kiện kết thúc, cậu có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Mail.</t>
+Nếu còn phần thưởng chưa nhận khi sự kiện kết thúc, cậu có thể đăng nhập trong vòng 30 ngày sau đó để nhận chúng qua Thư.</t>
         </is>
       </c>
     </row>
@@ -35304,7 +35304,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Mở Thiết bị đầu cuối Resonance ở Thành phố Ragunna trong Nhiệm vụ Main "Làn Gió Thiêng Thường Xuyên Thổi"</t>
+          <t>Mở Thiết bị đầu cuối Cộng Hưởng ở Thành phố Ragunna trong Nhiệm vụ Chính "Làn Gió Thiêng Thường Xuyên Thổi"</t>
         </is>
       </c>
     </row>
@@ -35369,7 +35369,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Hãy để ý xung quanh. Khi xuất hiện &lt;color=#ffd12f&gt;Grapple Point&lt;/color&gt; gần tảng đá lớn, ngươi có thể dùng &lt;color=#ffd12f&gt;Grapple&lt;/color&gt; đúng lúc để kéo nó đổ xuống và choáng kẻ địch bên dưới.</t>
+          <t>Hãy để ý xung quanh. Khi xuất hiện &lt;color=#ffd12f&gt;Điểm Móc Treo&lt;/color&gt; gần tảng đá lớn, ngươi có thể dùng &lt;color=#ffd12f&gt;Móc Treo&lt;/color&gt; đúng lúc để kéo nó đổ xuống và choáng kẻ địch bên dưới.</t>
         </is>
       </c>
     </row>
@@ -35435,8 +35435,8 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Trong chiến đấu, Augusta dần tích lũy Đà. Khi &lt;color=#ffd12f&gt;Momentum Bar&lt;/color&gt; đầy và chuyển sang &lt;color=#ffd12f&gt;yellow&lt;/color&gt;, cô bước vào giai đoạn &lt;color=#ffd12f&gt;Attack Preparation stage&lt;/color&gt;. Sau một lúc ở trạng thái vàng, &lt;color=#ffd12f&gt;Momentum Bar&lt;/color&gt; sẽ chuyển sang &lt;color=#ffd12f&gt;red&lt;/color&gt;, và Augusta sẽ &lt;color=#ffd12f&gt;launch her attack&lt;/color&gt;.
-Sử dụng &lt;color=#ffd12f&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=#ffd12f&gt;interrupts&lt;/color&gt; đòn tấn công của Augusta, và cô sẽ phải tích lũy Đà lại từ đầu.</t>
+          <t>Trong chiến đấu, Augusta dần tích lũy Đà. Khi &lt;color=#ffd12f&gt;Thanh Đà&lt;/color&gt; đầy và chuyển sang &lt;color=#ffd12f&gt;màu vàng&lt;/color&gt;, cô bước vào giai đoạn &lt;color=#ffd12f&gt;Chuẩn Bị Tấn Công&lt;/color&gt;. Sau một lúc ở trạng thái vàng, &lt;color=#ffd12f&gt;Thanh Đà&lt;/color&gt; sẽ chuyển sang &lt;color=#ffd12f&gt;màu đỏ&lt;/color&gt;, và Augusta sẽ &lt;color=#ffd12f&gt;phát động tấn công&lt;/color&gt;.
+Sử dụng &lt;color=#ffd12f&gt;Resonance Liberation&lt;/color&gt; sẽ &lt;color=#ffd12f&gt;làm gián đoạn&lt;/color&gt; đòn tấn công của Augusta, và cô sẽ phải tích lũy Đà lại từ đầu.</t>
         </is>
       </c>
     </row>
@@ -35502,8 +35502,8 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Trong Mô phỏng Phòng thủ Thủy Triều, cậu cần triển khai Combat Machines để chống lại các đợt tấn công của Tacet Discord nhằm phá hủy Energy Matrix.
-Tacet Discord tấn công theo đợt. Trong giai đoạn &lt;color=#ffd12f&gt;Preparation&lt;/color&gt; trước mỗi đợt, cậu có thể tiêu tốn Sim Creditss để triển khai các loại Combat Machines khác nhau.</t>
+          <t>Trong Mô phỏng Phòng thủ Thủy Triều, cậu cần triển khai Máy Chiến Đấu để chống lại các đợt tấn công của Tacet Discord nhằm phá hủy Ma Trận Năng Lượng.
+Tacet Discord tấn công theo đợt. Trong giai đoạn &lt;color=#ffd12f&gt;Chuẩn bị&lt;/color&gt; trước mỗi đợt, cậu có thể tiêu tốn Sim Credits để triển khai các loại Máy Chiến Đấu khác nhau.</t>
         </is>
       </c>
     </row>
